--- a/Другое/2026/study_chart.xlsx
+++ b/Другое/2026/study_chart.xlsx
@@ -919,12 +919,40 @@
         </r>
       </text>
     </comment>
+    <comment ref="AI22" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Сел за KPI 
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AI23" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Много времени посвятил разработке KPI, так что еще + 1 на след ячейке
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="92">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -9114,7 +9142,9 @@
       <c r="C20" s="22">
         <v>46282</v>
       </c>
-      <c r="D20" s="69"/>
+      <c r="D20" s="69" t="s">
+        <v>62</v>
+      </c>
       <c r="E20" s="70"/>
       <c r="F20" s="70"/>
       <c r="G20" s="70" t="s">
@@ -9207,7 +9237,9 @@
       <c r="N21" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="O21" s="71"/>
+      <c r="O21" s="71" t="s">
+        <v>12</v>
+      </c>
       <c r="P21" s="71"/>
       <c r="Q21" s="71"/>
       <c r="R21" s="72"/>
@@ -9216,13 +9248,19 @@
       <c r="U21" s="73"/>
       <c r="V21" s="73"/>
       <c r="W21" s="73"/>
-      <c r="X21" s="73"/>
+      <c r="X21" s="73" t="s">
+        <v>12</v>
+      </c>
       <c r="Y21" s="73"/>
       <c r="Z21" s="74"/>
       <c r="AA21" s="74"/>
       <c r="AB21" s="74"/>
-      <c r="AC21" s="74"/>
-      <c r="AD21" s="74"/>
+      <c r="AC21" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD21" s="74" t="s">
+        <v>12</v>
+      </c>
       <c r="AE21" s="75"/>
       <c r="AF21" s="75"/>
       <c r="AG21" s="75"/>
@@ -9231,7 +9269,7 @@
       <c r="AJ21" s="76"/>
       <c r="AK21" s="93">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:37">
@@ -9244,13 +9282,23 @@
       <c r="C22" s="22">
         <v>46284</v>
       </c>
-      <c r="D22" s="30"/>
+      <c r="D22" s="30" t="s">
+        <v>62</v>
+      </c>
       <c r="E22" s="62"/>
       <c r="F22" s="62"/>
-      <c r="G22" s="62"/>
-      <c r="H22" s="62"/>
-      <c r="I22" s="62"/>
-      <c r="J22" s="62"/>
+      <c r="G22" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="H22" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="I22" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="J22" s="62" t="s">
+        <v>12</v>
+      </c>
       <c r="K22" s="62"/>
       <c r="L22" s="63"/>
       <c r="M22" s="63"/>
@@ -9264,22 +9312,28 @@
       <c r="U22" s="64"/>
       <c r="V22" s="64"/>
       <c r="W22" s="64"/>
-      <c r="X22" s="64"/>
+      <c r="X22" s="64" t="s">
+        <v>12</v>
+      </c>
       <c r="Y22" s="64"/>
       <c r="Z22" s="65"/>
       <c r="AA22" s="65"/>
       <c r="AB22" s="65"/>
-      <c r="AC22" s="65"/>
+      <c r="AC22" s="65" t="s">
+        <v>12</v>
+      </c>
       <c r="AD22" s="65"/>
       <c r="AE22" s="66"/>
       <c r="AF22" s="66"/>
       <c r="AG22" s="66"/>
       <c r="AH22" s="67"/>
-      <c r="AI22" s="67"/>
+      <c r="AI22" s="67" t="s">
+        <v>12</v>
+      </c>
       <c r="AJ22" s="67"/>
       <c r="AK22" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:37">
@@ -9292,7 +9346,9 @@
       <c r="C23" s="22">
         <v>46285</v>
       </c>
-      <c r="D23" s="85"/>
+      <c r="D23" s="85" t="s">
+        <v>62</v>
+      </c>
       <c r="E23" s="86"/>
       <c r="F23" s="86"/>
       <c r="G23" s="86"/>
@@ -9302,7 +9358,9 @@
       <c r="K23" s="86"/>
       <c r="L23" s="87"/>
       <c r="M23" s="87"/>
-      <c r="N23" s="87"/>
+      <c r="N23" s="87" t="s">
+        <v>12</v>
+      </c>
       <c r="O23" s="87"/>
       <c r="P23" s="87"/>
       <c r="Q23" s="87"/>
@@ -9312,22 +9370,30 @@
       <c r="U23" s="89"/>
       <c r="V23" s="89"/>
       <c r="W23" s="89"/>
-      <c r="X23" s="89"/>
+      <c r="X23" s="89" t="s">
+        <v>12</v>
+      </c>
       <c r="Y23" s="89"/>
       <c r="Z23" s="90"/>
       <c r="AA23" s="90"/>
       <c r="AB23" s="90"/>
-      <c r="AC23" s="90"/>
+      <c r="AC23" s="90" t="s">
+        <v>12</v>
+      </c>
       <c r="AD23" s="90"/>
       <c r="AE23" s="91"/>
       <c r="AF23" s="91"/>
       <c r="AG23" s="91"/>
       <c r="AH23" s="92"/>
-      <c r="AI23" s="92"/>
-      <c r="AJ23" s="92"/>
+      <c r="AI23" s="92" t="s">
+        <v>12</v>
+      </c>
+      <c r="AJ23" s="92" t="s">
+        <v>12</v>
+      </c>
       <c r="AK23" s="95">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:37">
@@ -9340,7 +9406,9 @@
       <c r="C24" s="22">
         <v>46286</v>
       </c>
-      <c r="D24" s="96"/>
+      <c r="D24" s="96" t="s">
+        <v>62</v>
+      </c>
       <c r="E24" s="97"/>
       <c r="F24" s="97"/>
       <c r="G24" s="97"/>
@@ -9388,7 +9456,9 @@
       <c r="C25" s="22">
         <v>46287</v>
       </c>
-      <c r="D25" s="69"/>
+      <c r="D25" s="69" t="s">
+        <v>62</v>
+      </c>
       <c r="E25" s="70"/>
       <c r="F25" s="70"/>
       <c r="G25" s="70"/>
@@ -9397,15 +9467,21 @@
       <c r="J25" s="70"/>
       <c r="K25" s="70"/>
       <c r="L25" s="71"/>
-      <c r="M25" s="71"/>
-      <c r="N25" s="71"/>
+      <c r="M25" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="N25" s="71" t="s">
+        <v>12</v>
+      </c>
       <c r="O25" s="71"/>
       <c r="P25" s="71"/>
       <c r="Q25" s="71"/>
       <c r="R25" s="72"/>
       <c r="S25" s="72"/>
       <c r="T25" s="72"/>
-      <c r="U25" s="73"/>
+      <c r="U25" s="73" t="s">
+        <v>12</v>
+      </c>
       <c r="V25" s="73"/>
       <c r="W25" s="73"/>
       <c r="X25" s="73"/>
@@ -9423,7 +9499,7 @@
       <c r="AJ25" s="76"/>
       <c r="AK25" s="93">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:37">
@@ -9436,7 +9512,9 @@
       <c r="C26" s="22">
         <v>46288</v>
       </c>
-      <c r="D26" s="69"/>
+      <c r="D26" s="69" t="s">
+        <v>62</v>
+      </c>
       <c r="E26" s="70"/>
       <c r="F26" s="70"/>
       <c r="G26" s="70"/>
@@ -9445,8 +9523,12 @@
       <c r="J26" s="70"/>
       <c r="K26" s="70"/>
       <c r="L26" s="71"/>
-      <c r="M26" s="71"/>
-      <c r="N26" s="71"/>
+      <c r="M26" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="N26" s="71" t="s">
+        <v>12</v>
+      </c>
       <c r="O26" s="71"/>
       <c r="P26" s="71"/>
       <c r="Q26" s="71"/>
@@ -9471,7 +9553,7 @@
       <c r="AJ26" s="76"/>
       <c r="AK26" s="93">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:37">
@@ -9827,19 +9909,19 @@
       </c>
       <c r="G34" s="106">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H34" s="106">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I34" s="106">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J34" s="106">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K34" s="106">
         <f t="shared" si="1"/>
@@ -9851,15 +9933,15 @@
       </c>
       <c r="M34" s="63">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N34" s="63">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="O34" s="63">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P34" s="63">
         <f t="shared" si="1"/>
@@ -9883,7 +9965,7 @@
       </c>
       <c r="U34" s="64">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V34" s="64">
         <f t="shared" si="1"/>
@@ -9895,7 +9977,7 @@
       </c>
       <c r="X34" s="64">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y34" s="64">
         <f t="shared" si="1"/>
@@ -9915,11 +9997,11 @@
       </c>
       <c r="AC34" s="65">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD34" s="65">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE34" s="66">
         <f t="shared" si="1"/>
@@ -9939,11 +10021,11 @@
       </c>
       <c r="AI34" s="67">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AJ34" s="67">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK34" s="25"/>
     </row>
@@ -9956,7 +10038,7 @@
       <c r="AJ35" s="144"/>
       <c r="AK35" s="107">
         <f>ROUND(AVERAGE(AK4:AK33),0)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:37" ht="30" customHeight="1">
@@ -9992,7 +10074,7 @@
       <c r="AJ38" s="144"/>
       <c r="AK38" s="107">
         <f>COUNTIF(AK4:AK33, "&gt;"&amp;AK35)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:37" ht="30" customHeight="1">
@@ -10004,7 +10086,7 @@
       <c r="AJ39" s="144"/>
       <c r="AK39" s="107">
         <f>COUNTIF(AK4:AK33, "&lt;"&amp;AK35)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="40" spans="1:37" ht="30" customHeight="1">

--- a/Другое/2026/study_chart.xlsx
+++ b/Другое/2026/study_chart.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4507"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="10380" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="10380" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Июнь" sheetId="1" r:id="rId1"/>
     <sheet name="Июль" sheetId="4" r:id="rId2"/>
     <sheet name="Август" sheetId="5" r:id="rId3"/>
     <sheet name="Сентябрь" sheetId="6" r:id="rId4"/>
+    <sheet name="Октябрь" sheetId="7" r:id="rId5"/>
   </sheets>
   <calcPr calcId="125725"/>
   <extLst>
@@ -952,7 +953,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="94">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -1228,6 +1229,12 @@
   </si>
   <si>
     <t>Заявление в суд и в МТС</t>
+  </si>
+  <si>
+    <t>Встать до 6:30</t>
+  </si>
+  <si>
+    <t>Формирование других привычек</t>
   </si>
 </sst>
 </file>
@@ -2104,7 +2111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="151">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2461,6 +2468,24 @@
     <xf numFmtId="0" fontId="19" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2515,24 +2540,6 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2540,13 +2547,64 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="23">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFB6EA86"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFB6EA86"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFB6EA86"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFB6EA86"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFB6EA86"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFB6EA86"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -3314,12 +3372,12 @@
     <mergeCell ref="H22:J22"/>
   </mergeCells>
   <conditionalFormatting sqref="K22:Q22">
-    <cfRule type="expression" dxfId="16" priority="1">
+    <cfRule type="expression" dxfId="22" priority="1">
       <formula>Q22="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11:Q21">
-    <cfRule type="expression" dxfId="15" priority="2">
+    <cfRule type="expression" dxfId="21" priority="2">
       <formula>Q11="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5185,12 +5243,12 @@
     <mergeCell ref="H42:J42"/>
   </mergeCells>
   <conditionalFormatting sqref="AL42">
-    <cfRule type="expression" dxfId="14" priority="10">
+    <cfRule type="expression" dxfId="20" priority="10">
       <formula>AU42="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11:AK41">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>K11&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5236,66 +5294,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="129"/>
-      <c r="B1" s="130"/>
-      <c r="C1" s="131"/>
+      <c r="A1" s="135"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="137"/>
       <c r="D1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="135" t="s">
+      <c r="E1" s="141" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="135"/>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
-      <c r="I1" s="135"/>
-      <c r="J1" s="135"/>
-      <c r="K1" s="135"/>
-      <c r="L1" s="136" t="s">
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="142" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="136"/>
-      <c r="N1" s="136"/>
-      <c r="O1" s="136"/>
-      <c r="P1" s="136"/>
-      <c r="Q1" s="136"/>
-      <c r="R1" s="136"/>
-      <c r="S1" s="137" t="s">
+      <c r="M1" s="142"/>
+      <c r="N1" s="142"/>
+      <c r="O1" s="142"/>
+      <c r="P1" s="142"/>
+      <c r="Q1" s="142"/>
+      <c r="R1" s="142"/>
+      <c r="S1" s="143" t="s">
         <v>39</v>
       </c>
-      <c r="T1" s="137"/>
-      <c r="U1" s="138" t="s">
+      <c r="T1" s="143"/>
+      <c r="U1" s="144" t="s">
         <v>40</v>
       </c>
-      <c r="V1" s="139"/>
-      <c r="W1" s="139"/>
-      <c r="X1" s="139"/>
-      <c r="Y1" s="140"/>
-      <c r="Z1" s="141" t="s">
+      <c r="V1" s="145"/>
+      <c r="W1" s="145"/>
+      <c r="X1" s="145"/>
+      <c r="Y1" s="146"/>
+      <c r="Z1" s="147" t="s">
         <v>41</v>
       </c>
-      <c r="AA1" s="141"/>
-      <c r="AB1" s="141"/>
-      <c r="AC1" s="141"/>
-      <c r="AD1" s="141"/>
-      <c r="AE1" s="124" t="s">
+      <c r="AA1" s="147"/>
+      <c r="AB1" s="147"/>
+      <c r="AC1" s="147"/>
+      <c r="AD1" s="147"/>
+      <c r="AE1" s="130" t="s">
         <v>42</v>
       </c>
-      <c r="AF1" s="124"/>
-      <c r="AG1" s="124"/>
-      <c r="AH1" s="125" t="s">
+      <c r="AF1" s="130"/>
+      <c r="AG1" s="130"/>
+      <c r="AH1" s="131" t="s">
         <v>43</v>
       </c>
-      <c r="AI1" s="125"/>
-      <c r="AJ1" s="125"/>
-      <c r="AK1" s="126" t="s">
+      <c r="AI1" s="131"/>
+      <c r="AJ1" s="131"/>
+      <c r="AK1" s="132" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:37" s="2" customFormat="1" ht="30" customHeight="1">
-      <c r="A2" s="132"/>
-      <c r="B2" s="133"/>
-      <c r="C2" s="134"/>
+      <c r="A2" s="138"/>
+      <c r="B2" s="139"/>
+      <c r="C2" s="140"/>
       <c r="D2" s="5" t="s">
         <v>44</v>
       </c>
@@ -5389,7 +5447,7 @@
       <c r="AH2" s="12"/>
       <c r="AI2" s="12"/>
       <c r="AJ2" s="12"/>
-      <c r="AK2" s="127"/>
+      <c r="AK2" s="133"/>
     </row>
     <row r="3" spans="1:37">
       <c r="A3" s="13" t="s">
@@ -5500,7 +5558,7 @@
       <c r="AJ3" s="20">
         <v>2</v>
       </c>
-      <c r="AK3" s="128"/>
+      <c r="AK3" s="134"/>
     </row>
     <row r="4" spans="1:37">
       <c r="A4" s="21">
@@ -7551,12 +7609,12 @@
       </c>
     </row>
     <row r="35" spans="1:37" ht="30" customHeight="1">
-      <c r="A35" s="145" t="s">
+      <c r="A35" s="127" t="s">
         <v>77</v>
       </c>
-      <c r="B35" s="146"/>
-      <c r="C35" s="146"/>
-      <c r="D35" s="147"/>
+      <c r="B35" s="128"/>
+      <c r="C35" s="128"/>
+      <c r="D35" s="129"/>
       <c r="E35" s="106">
         <f>COUNTA(E4:E34)</f>
         <v>14</v>
@@ -7688,84 +7746,84 @@
       <c r="AK35" s="25"/>
     </row>
     <row r="36" spans="1:37" ht="30" customHeight="1">
-      <c r="AG36" s="142" t="s">
+      <c r="AG36" s="124" t="s">
         <v>78</v>
       </c>
-      <c r="AH36" s="143"/>
-      <c r="AI36" s="143"/>
-      <c r="AJ36" s="144"/>
+      <c r="AH36" s="125"/>
+      <c r="AI36" s="125"/>
+      <c r="AJ36" s="126"/>
       <c r="AK36" s="107">
         <f>ROUND(AVERAGE(AK4:AK34),0)</f>
         <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:37" ht="30" customHeight="1">
-      <c r="AG37" s="142" t="s">
+      <c r="AG37" s="124" t="s">
         <v>79</v>
       </c>
-      <c r="AH37" s="143"/>
-      <c r="AI37" s="143"/>
-      <c r="AJ37" s="144"/>
+      <c r="AH37" s="125"/>
+      <c r="AI37" s="125"/>
+      <c r="AJ37" s="126"/>
       <c r="AK37" s="107">
         <f>MAX(AK4:AK34)</f>
         <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:37" ht="30" customHeight="1">
-      <c r="AG38" s="142" t="s">
+      <c r="AG38" s="124" t="s">
         <v>80</v>
       </c>
-      <c r="AH38" s="143"/>
-      <c r="AI38" s="143"/>
-      <c r="AJ38" s="144"/>
+      <c r="AH38" s="125"/>
+      <c r="AI38" s="125"/>
+      <c r="AJ38" s="126"/>
       <c r="AK38" s="107">
         <f>MIN(AK4:AK34)</f>
         <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:37" ht="30" customHeight="1">
-      <c r="AG39" s="142" t="s">
+      <c r="AG39" s="124" t="s">
         <v>81</v>
       </c>
-      <c r="AH39" s="143"/>
-      <c r="AI39" s="143"/>
-      <c r="AJ39" s="144"/>
+      <c r="AH39" s="125"/>
+      <c r="AI39" s="125"/>
+      <c r="AJ39" s="126"/>
       <c r="AK39" s="107">
         <f>COUNTIF(AK4:AK34, "&gt;"&amp;AK36)</f>
         <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:37" ht="30" customHeight="1">
-      <c r="AG40" s="142" t="s">
+      <c r="AG40" s="124" t="s">
         <v>82</v>
       </c>
-      <c r="AH40" s="143"/>
-      <c r="AI40" s="143"/>
-      <c r="AJ40" s="144"/>
+      <c r="AH40" s="125"/>
+      <c r="AI40" s="125"/>
+      <c r="AJ40" s="126"/>
       <c r="AK40" s="107">
         <f>COUNTIF(AK4:AK34, "&lt;"&amp;AK36)</f>
         <v>18</v>
       </c>
     </row>
     <row r="41" spans="1:37" ht="30" customHeight="1">
-      <c r="AG41" s="142" t="s">
+      <c r="AG41" s="124" t="s">
         <v>83</v>
       </c>
-      <c r="AH41" s="143"/>
-      <c r="AI41" s="143"/>
-      <c r="AJ41" s="144"/>
+      <c r="AH41" s="125"/>
+      <c r="AI41" s="125"/>
+      <c r="AJ41" s="126"/>
       <c r="AK41" s="107">
         <f>COUNTIF(AK4:AK34, "&gt;"&amp;20)</f>
         <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:37" ht="30" customHeight="1">
-      <c r="AG42" s="142" t="s">
+      <c r="AG42" s="124" t="s">
         <v>84</v>
       </c>
-      <c r="AH42" s="143"/>
-      <c r="AI42" s="143"/>
-      <c r="AJ42" s="144"/>
+      <c r="AH42" s="125"/>
+      <c r="AI42" s="125"/>
+      <c r="AJ42" s="126"/>
       <c r="AK42" s="107">
         <f>COUNTIF(AK4:AK34, "&lt;"&amp;20)</f>
         <v>21</v>
@@ -7776,14 +7834,6 @@
     <row r="45" spans="1:37" ht="30" customHeight="1"/>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="AG40:AJ40"/>
-    <mergeCell ref="AG41:AJ41"/>
-    <mergeCell ref="AG42:AJ42"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="AG36:AJ36"/>
-    <mergeCell ref="AG37:AJ37"/>
-    <mergeCell ref="AG38:AJ38"/>
-    <mergeCell ref="AG39:AJ39"/>
     <mergeCell ref="AE1:AG1"/>
     <mergeCell ref="AH1:AJ1"/>
     <mergeCell ref="AK1:AK3"/>
@@ -7793,39 +7843,47 @@
     <mergeCell ref="S1:T1"/>
     <mergeCell ref="U1:Y1"/>
     <mergeCell ref="Z1:AD1"/>
+    <mergeCell ref="AG40:AJ40"/>
+    <mergeCell ref="AG41:AJ41"/>
+    <mergeCell ref="AG42:AJ42"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="AG36:AJ36"/>
+    <mergeCell ref="AG37:AJ37"/>
+    <mergeCell ref="AG38:AJ38"/>
+    <mergeCell ref="AG39:AJ39"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:AJ34">
-    <cfRule type="expression" dxfId="12" priority="7">
+    <cfRule type="expression" dxfId="18" priority="7">
       <formula>E4="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L35:R35">
-    <cfRule type="expression" dxfId="11" priority="6">
+    <cfRule type="expression" dxfId="17" priority="6">
       <formula>L35="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S35:T35">
-    <cfRule type="expression" dxfId="10" priority="5">
+    <cfRule type="expression" dxfId="16" priority="5">
       <formula>S35="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U35:Y35">
-    <cfRule type="expression" dxfId="9" priority="4">
+    <cfRule type="expression" dxfId="15" priority="4">
       <formula>U35="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z35:AD35">
-    <cfRule type="expression" dxfId="8" priority="3">
+    <cfRule type="expression" dxfId="14" priority="3">
       <formula>Z35="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE35:AG35">
-    <cfRule type="expression" dxfId="7" priority="2">
+    <cfRule type="expression" dxfId="13" priority="2">
       <formula>AE35="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH35:AJ35">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>AH35="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7870,66 +7928,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="129"/>
-      <c r="B1" s="130"/>
-      <c r="C1" s="131"/>
+      <c r="A1" s="135"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="137"/>
       <c r="D1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="135" t="s">
+      <c r="E1" s="141" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="135"/>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
-      <c r="I1" s="135"/>
-      <c r="J1" s="135"/>
-      <c r="K1" s="135"/>
-      <c r="L1" s="136" t="s">
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="142" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="136"/>
-      <c r="N1" s="136"/>
-      <c r="O1" s="136"/>
-      <c r="P1" s="136"/>
-      <c r="Q1" s="136"/>
+      <c r="M1" s="142"/>
+      <c r="N1" s="142"/>
+      <c r="O1" s="142"/>
+      <c r="P1" s="142"/>
+      <c r="Q1" s="142"/>
       <c r="R1" s="148" t="s">
         <v>39</v>
       </c>
       <c r="S1" s="149"/>
       <c r="T1" s="150"/>
-      <c r="U1" s="138" t="s">
+      <c r="U1" s="144" t="s">
         <v>40</v>
       </c>
-      <c r="V1" s="139"/>
-      <c r="W1" s="139"/>
-      <c r="X1" s="139"/>
-      <c r="Y1" s="140"/>
-      <c r="Z1" s="141" t="s">
+      <c r="V1" s="145"/>
+      <c r="W1" s="145"/>
+      <c r="X1" s="145"/>
+      <c r="Y1" s="146"/>
+      <c r="Z1" s="147" t="s">
         <v>41</v>
       </c>
-      <c r="AA1" s="141"/>
-      <c r="AB1" s="141"/>
-      <c r="AC1" s="141"/>
-      <c r="AD1" s="141"/>
-      <c r="AE1" s="124" t="s">
+      <c r="AA1" s="147"/>
+      <c r="AB1" s="147"/>
+      <c r="AC1" s="147"/>
+      <c r="AD1" s="147"/>
+      <c r="AE1" s="130" t="s">
         <v>42</v>
       </c>
-      <c r="AF1" s="124"/>
-      <c r="AG1" s="124"/>
-      <c r="AH1" s="125" t="s">
+      <c r="AF1" s="130"/>
+      <c r="AG1" s="130"/>
+      <c r="AH1" s="131" t="s">
         <v>43</v>
       </c>
-      <c r="AI1" s="125"/>
-      <c r="AJ1" s="125"/>
-      <c r="AK1" s="126" t="s">
+      <c r="AI1" s="131"/>
+      <c r="AJ1" s="131"/>
+      <c r="AK1" s="132" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:37" s="2" customFormat="1" ht="45" customHeight="1">
-      <c r="A2" s="132"/>
-      <c r="B2" s="133"/>
-      <c r="C2" s="134"/>
+      <c r="A2" s="138"/>
+      <c r="B2" s="139"/>
+      <c r="C2" s="140"/>
       <c r="D2" s="5" t="s">
         <v>44</v>
       </c>
@@ -8025,7 +8083,7 @@
       </c>
       <c r="AI2" s="12"/>
       <c r="AJ2" s="12"/>
-      <c r="AK2" s="127"/>
+      <c r="AK2" s="133"/>
     </row>
     <row r="3" spans="1:37">
       <c r="A3" s="13" t="s">
@@ -8136,7 +8194,7 @@
       <c r="AJ3" s="20">
         <v>1</v>
       </c>
-      <c r="AK3" s="128"/>
+      <c r="AK3" s="134"/>
     </row>
     <row r="4" spans="1:37">
       <c r="A4" s="30">
@@ -9893,12 +9951,12 @@
       </c>
     </row>
     <row r="34" spans="1:37" ht="30" customHeight="1">
-      <c r="A34" s="145" t="s">
+      <c r="A34" s="127" t="s">
         <v>77</v>
       </c>
-      <c r="B34" s="146"/>
-      <c r="C34" s="146"/>
-      <c r="D34" s="147"/>
+      <c r="B34" s="128"/>
+      <c r="C34" s="128"/>
+      <c r="D34" s="129"/>
       <c r="E34" s="106">
         <f t="shared" ref="E34:AJ34" si="1">COUNTA(E4:E33)</f>
         <v>2</v>
@@ -10030,84 +10088,84 @@
       <c r="AK34" s="25"/>
     </row>
     <row r="35" spans="1:37" ht="30" customHeight="1">
-      <c r="AG35" s="142" t="s">
+      <c r="AG35" s="124" t="s">
         <v>78</v>
       </c>
-      <c r="AH35" s="143"/>
-      <c r="AI35" s="143"/>
-      <c r="AJ35" s="144"/>
+      <c r="AH35" s="125"/>
+      <c r="AI35" s="125"/>
+      <c r="AJ35" s="126"/>
       <c r="AK35" s="107">
         <f>ROUND(AVERAGE(AK4:AK33),0)</f>
         <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:37" ht="30" customHeight="1">
-      <c r="AG36" s="142" t="s">
+      <c r="AG36" s="124" t="s">
         <v>79</v>
       </c>
-      <c r="AH36" s="143"/>
-      <c r="AI36" s="143"/>
-      <c r="AJ36" s="144"/>
+      <c r="AH36" s="125"/>
+      <c r="AI36" s="125"/>
+      <c r="AJ36" s="126"/>
       <c r="AK36" s="107">
         <f>MAX(AK4:AK33)</f>
         <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:37" ht="30" customHeight="1">
-      <c r="AG37" s="142" t="s">
+      <c r="AG37" s="124" t="s">
         <v>80</v>
       </c>
-      <c r="AH37" s="143"/>
-      <c r="AI37" s="143"/>
-      <c r="AJ37" s="144"/>
+      <c r="AH37" s="125"/>
+      <c r="AI37" s="125"/>
+      <c r="AJ37" s="126"/>
       <c r="AK37" s="107">
         <f>MIN(AK4:AK33)</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:37" ht="30" customHeight="1">
-      <c r="AG38" s="142" t="s">
+      <c r="AG38" s="124" t="s">
         <v>81</v>
       </c>
-      <c r="AH38" s="143"/>
-      <c r="AI38" s="143"/>
-      <c r="AJ38" s="144"/>
+      <c r="AH38" s="125"/>
+      <c r="AI38" s="125"/>
+      <c r="AJ38" s="126"/>
       <c r="AK38" s="107">
         <f>COUNTIF(AK4:AK33, "&gt;"&amp;AK35)</f>
         <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:37" ht="30" customHeight="1">
-      <c r="AG39" s="142" t="s">
+      <c r="AG39" s="124" t="s">
         <v>82</v>
       </c>
-      <c r="AH39" s="143"/>
-      <c r="AI39" s="143"/>
-      <c r="AJ39" s="144"/>
+      <c r="AH39" s="125"/>
+      <c r="AI39" s="125"/>
+      <c r="AJ39" s="126"/>
       <c r="AK39" s="107">
         <f>COUNTIF(AK4:AK33, "&lt;"&amp;AK35)</f>
         <v>14</v>
       </c>
     </row>
     <row r="40" spans="1:37" ht="30" customHeight="1">
-      <c r="AG40" s="142" t="s">
+      <c r="AG40" s="124" t="s">
         <v>83</v>
       </c>
-      <c r="AH40" s="143"/>
-      <c r="AI40" s="143"/>
-      <c r="AJ40" s="144"/>
+      <c r="AH40" s="125"/>
+      <c r="AI40" s="125"/>
+      <c r="AJ40" s="126"/>
       <c r="AK40" s="107">
         <f>COUNTIF(AK4:AK33, "&gt;"&amp;20)</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:37" ht="30" customHeight="1">
-      <c r="AG41" s="142" t="s">
+      <c r="AG41" s="124" t="s">
         <v>84</v>
       </c>
-      <c r="AH41" s="143"/>
-      <c r="AI41" s="143"/>
-      <c r="AJ41" s="144"/>
+      <c r="AH41" s="125"/>
+      <c r="AI41" s="125"/>
+      <c r="AJ41" s="126"/>
       <c r="AK41" s="107">
         <f>COUNTIF(AK4:AK33, "&lt;"&amp;20)</f>
         <v>30</v>
@@ -10118,51 +10176,51 @@
     <row r="44" spans="1:37" ht="30" customHeight="1"/>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="AE1:AG1"/>
+    <mergeCell ref="AH1:AJ1"/>
+    <mergeCell ref="AG40:AJ40"/>
+    <mergeCell ref="AG41:AJ41"/>
+    <mergeCell ref="AK1:AK3"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="AG37:AJ37"/>
+    <mergeCell ref="AG38:AJ38"/>
+    <mergeCell ref="AG39:AJ39"/>
+    <mergeCell ref="AG35:AJ35"/>
+    <mergeCell ref="AG36:AJ36"/>
     <mergeCell ref="A1:C2"/>
     <mergeCell ref="E1:K1"/>
     <mergeCell ref="L1:Q1"/>
     <mergeCell ref="U1:Y1"/>
     <mergeCell ref="Z1:AD1"/>
     <mergeCell ref="R1:T1"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="AG37:AJ37"/>
-    <mergeCell ref="AG38:AJ38"/>
-    <mergeCell ref="AG39:AJ39"/>
-    <mergeCell ref="AG35:AJ35"/>
-    <mergeCell ref="AG36:AJ36"/>
-    <mergeCell ref="AE1:AG1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="AG40:AJ40"/>
-    <mergeCell ref="AG41:AJ41"/>
-    <mergeCell ref="AK1:AK3"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:AJ33 L34:Q34">
-    <cfRule type="expression" dxfId="5" priority="7">
+    <cfRule type="expression" dxfId="11" priority="7">
       <formula>E4="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R34:T34">
-    <cfRule type="expression" dxfId="4" priority="5">
+    <cfRule type="expression" dxfId="10" priority="5">
       <formula>R34="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U34:Y34">
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="9" priority="4">
       <formula>U34="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z34:AD34">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="8" priority="3">
       <formula>Z34="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE34:AG34">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="7" priority="2">
       <formula>AE34="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH34:AJ34">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>AH34="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10170,4 +10228,1236 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AK27"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="3" width="15.7109375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="26" style="3" customWidth="1"/>
+    <col min="5" max="6" width="15.7109375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="21.140625" style="3" customWidth="1"/>
+    <col min="8" max="11" width="15.7109375" style="3" customWidth="1"/>
+    <col min="12" max="12" width="20.28515625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="20.42578125" style="3" customWidth="1"/>
+    <col min="14" max="14" width="33.42578125" style="3" customWidth="1"/>
+    <col min="15" max="15" width="26.7109375" style="3" customWidth="1"/>
+    <col min="16" max="16" width="32.28515625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="21.140625" style="3" customWidth="1"/>
+    <col min="18" max="20" width="15.7109375" style="3" customWidth="1"/>
+    <col min="21" max="21" width="23.7109375" style="3" customWidth="1"/>
+    <col min="22" max="22" width="21.5703125" style="3" customWidth="1"/>
+    <col min="23" max="25" width="15.7109375" style="3" customWidth="1"/>
+    <col min="26" max="26" width="21.42578125" style="3" customWidth="1"/>
+    <col min="27" max="27" width="15.7109375" style="3" customWidth="1"/>
+    <col min="28" max="28" width="27.140625" style="3" customWidth="1"/>
+    <col min="29" max="29" width="15.7109375" style="3" customWidth="1"/>
+    <col min="30" max="30" width="29.28515625" style="3" customWidth="1"/>
+    <col min="31" max="31" width="24.42578125" style="3" customWidth="1"/>
+    <col min="32" max="32" width="33.7109375" style="3" customWidth="1"/>
+    <col min="33" max="33" width="34.28515625" style="3" customWidth="1"/>
+    <col min="34" max="36" width="15.7109375" style="3" customWidth="1"/>
+    <col min="37" max="37" width="24.5703125" style="3" customWidth="1"/>
+    <col min="38" max="38" width="20.7109375" style="3" customWidth="1"/>
+    <col min="39" max="16384" width="9" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:37" s="1" customFormat="1" ht="30" customHeight="1">
+      <c r="A1" s="135"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="137"/>
+      <c r="D1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="141" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="142" t="s">
+        <v>38</v>
+      </c>
+      <c r="M1" s="142"/>
+      <c r="N1" s="142"/>
+      <c r="O1" s="142"/>
+      <c r="P1" s="142"/>
+      <c r="Q1" s="142"/>
+      <c r="R1" s="148" t="s">
+        <v>39</v>
+      </c>
+      <c r="S1" s="149"/>
+      <c r="T1" s="150"/>
+      <c r="U1" s="144" t="s">
+        <v>40</v>
+      </c>
+      <c r="V1" s="145"/>
+      <c r="W1" s="145"/>
+      <c r="X1" s="145"/>
+      <c r="Y1" s="146"/>
+      <c r="Z1" s="147" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA1" s="147"/>
+      <c r="AB1" s="147"/>
+      <c r="AC1" s="147"/>
+      <c r="AD1" s="147"/>
+      <c r="AE1" s="130" t="s">
+        <v>93</v>
+      </c>
+      <c r="AF1" s="130"/>
+      <c r="AG1" s="130"/>
+      <c r="AH1" s="131" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI1" s="131"/>
+      <c r="AJ1" s="131"/>
+      <c r="AK1" s="132" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:37" s="2" customFormat="1" ht="60" customHeight="1">
+      <c r="A2" s="138"/>
+      <c r="B2" s="139"/>
+      <c r="C2" s="140"/>
+      <c r="D2" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="O2" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="R2" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="S2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="T2" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="U2" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="V2" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="W2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="X2" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y2" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z2" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA2" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB2" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC2" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD2" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE2" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="AF2" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="AG2" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="AH2" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="AI2" s="12"/>
+      <c r="AJ2" s="12"/>
+      <c r="AK2" s="133"/>
+    </row>
+    <row r="3" spans="1:37">
+      <c r="A3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" s="14">
+        <v>1</v>
+      </c>
+      <c r="F3" s="14">
+        <v>1</v>
+      </c>
+      <c r="G3" s="14">
+        <v>1</v>
+      </c>
+      <c r="H3" s="14">
+        <v>2</v>
+      </c>
+      <c r="I3" s="14">
+        <v>1</v>
+      </c>
+      <c r="J3" s="14">
+        <v>2</v>
+      </c>
+      <c r="K3" s="14">
+        <v>1</v>
+      </c>
+      <c r="L3" s="15">
+        <v>1</v>
+      </c>
+      <c r="M3" s="15">
+        <v>1</v>
+      </c>
+      <c r="N3" s="15">
+        <v>2</v>
+      </c>
+      <c r="O3" s="15">
+        <v>1</v>
+      </c>
+      <c r="P3" s="15">
+        <v>3</v>
+      </c>
+      <c r="Q3" s="15">
+        <v>3</v>
+      </c>
+      <c r="R3" s="16">
+        <v>3</v>
+      </c>
+      <c r="S3" s="16">
+        <v>3</v>
+      </c>
+      <c r="T3" s="16">
+        <v>3</v>
+      </c>
+      <c r="U3" s="17">
+        <v>2</v>
+      </c>
+      <c r="V3" s="17">
+        <v>2</v>
+      </c>
+      <c r="W3" s="17">
+        <v>2</v>
+      </c>
+      <c r="X3" s="17">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="17">
+        <v>2</v>
+      </c>
+      <c r="Z3" s="18">
+        <v>3</v>
+      </c>
+      <c r="AA3" s="18">
+        <v>2</v>
+      </c>
+      <c r="AB3" s="18">
+        <v>1</v>
+      </c>
+      <c r="AC3" s="18">
+        <v>2</v>
+      </c>
+      <c r="AD3" s="18">
+        <v>1</v>
+      </c>
+      <c r="AE3" s="19">
+        <v>3</v>
+      </c>
+      <c r="AF3" s="19">
+        <v>2</v>
+      </c>
+      <c r="AG3" s="19">
+        <v>3</v>
+      </c>
+      <c r="AH3" s="20">
+        <v>2</v>
+      </c>
+      <c r="AI3" s="20">
+        <v>2</v>
+      </c>
+      <c r="AJ3" s="20">
+        <v>1</v>
+      </c>
+      <c r="AK3" s="134"/>
+    </row>
+    <row r="4" spans="1:37">
+      <c r="A4" s="30">
+        <v>1</v>
+      </c>
+      <c r="B4" s="151" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="22">
+        <v>46314</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="62"/>
+      <c r="L4" s="63"/>
+      <c r="M4" s="63"/>
+      <c r="N4" s="63"/>
+      <c r="O4" s="63"/>
+      <c r="P4" s="63"/>
+      <c r="Q4" s="63"/>
+      <c r="R4" s="24"/>
+      <c r="S4" s="24"/>
+      <c r="T4" s="24"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="64"/>
+      <c r="W4" s="64"/>
+      <c r="X4" s="64"/>
+      <c r="Y4" s="64"/>
+      <c r="Z4" s="65"/>
+      <c r="AA4" s="65"/>
+      <c r="AB4" s="65"/>
+      <c r="AC4" s="65"/>
+      <c r="AD4" s="65"/>
+      <c r="AE4" s="66"/>
+      <c r="AF4" s="66"/>
+      <c r="AG4" s="66"/>
+      <c r="AH4" s="67"/>
+      <c r="AI4" s="67"/>
+      <c r="AJ4" s="67"/>
+      <c r="AK4" s="25">
+        <f t="shared" ref="AK4:AK16" si="0">SUMIF(E4:AJ4,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37">
+      <c r="A5" s="30">
+        <v>2</v>
+      </c>
+      <c r="B5" s="151" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="22">
+        <v>46315</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="62"/>
+      <c r="L5" s="63"/>
+      <c r="M5" s="63"/>
+      <c r="N5" s="63"/>
+      <c r="O5" s="63"/>
+      <c r="P5" s="63"/>
+      <c r="Q5" s="63"/>
+      <c r="R5" s="24"/>
+      <c r="S5" s="24"/>
+      <c r="T5" s="24"/>
+      <c r="U5" s="64"/>
+      <c r="V5" s="64"/>
+      <c r="W5" s="64"/>
+      <c r="X5" s="64"/>
+      <c r="Y5" s="64"/>
+      <c r="Z5" s="65"/>
+      <c r="AA5" s="65"/>
+      <c r="AB5" s="65"/>
+      <c r="AC5" s="65"/>
+      <c r="AD5" s="65"/>
+      <c r="AE5" s="66"/>
+      <c r="AF5" s="66"/>
+      <c r="AG5" s="66"/>
+      <c r="AH5" s="67"/>
+      <c r="AI5" s="67"/>
+      <c r="AJ5" s="67"/>
+      <c r="AK5" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:37">
+      <c r="A6" s="30">
+        <v>3</v>
+      </c>
+      <c r="B6" s="151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="22">
+        <v>46316</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="62"/>
+      <c r="L6" s="63"/>
+      <c r="M6" s="63"/>
+      <c r="N6" s="63"/>
+      <c r="O6" s="63"/>
+      <c r="P6" s="63"/>
+      <c r="Q6" s="63"/>
+      <c r="R6" s="24"/>
+      <c r="S6" s="24"/>
+      <c r="T6" s="24"/>
+      <c r="U6" s="64"/>
+      <c r="V6" s="64"/>
+      <c r="W6" s="64"/>
+      <c r="X6" s="64"/>
+      <c r="Y6" s="64"/>
+      <c r="Z6" s="65"/>
+      <c r="AA6" s="65"/>
+      <c r="AB6" s="65"/>
+      <c r="AC6" s="65"/>
+      <c r="AD6" s="65"/>
+      <c r="AE6" s="66"/>
+      <c r="AF6" s="66"/>
+      <c r="AG6" s="66"/>
+      <c r="AH6" s="67"/>
+      <c r="AI6" s="67"/>
+      <c r="AJ6" s="67"/>
+      <c r="AK6" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37">
+      <c r="A7" s="30">
+        <v>4</v>
+      </c>
+      <c r="B7" s="151" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="22">
+        <v>46317</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="62"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="62"/>
+      <c r="I7" s="62"/>
+      <c r="J7" s="62"/>
+      <c r="K7" s="62"/>
+      <c r="L7" s="63"/>
+      <c r="M7" s="63"/>
+      <c r="N7" s="63"/>
+      <c r="O7" s="63"/>
+      <c r="P7" s="63"/>
+      <c r="Q7" s="63"/>
+      <c r="R7" s="24"/>
+      <c r="S7" s="24"/>
+      <c r="T7" s="24"/>
+      <c r="U7" s="64"/>
+      <c r="V7" s="64"/>
+      <c r="W7" s="64"/>
+      <c r="X7" s="64"/>
+      <c r="Y7" s="64"/>
+      <c r="Z7" s="65"/>
+      <c r="AA7" s="65"/>
+      <c r="AB7" s="65"/>
+      <c r="AC7" s="65"/>
+      <c r="AD7" s="65"/>
+      <c r="AE7" s="66"/>
+      <c r="AF7" s="66"/>
+      <c r="AG7" s="66"/>
+      <c r="AH7" s="67"/>
+      <c r="AI7" s="67"/>
+      <c r="AJ7" s="67"/>
+      <c r="AK7" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37">
+      <c r="A8" s="30">
+        <v>5</v>
+      </c>
+      <c r="B8" s="151" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="22">
+        <v>46318</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="62"/>
+      <c r="F8" s="62"/>
+      <c r="G8" s="62"/>
+      <c r="H8" s="62"/>
+      <c r="I8" s="62"/>
+      <c r="J8" s="62"/>
+      <c r="K8" s="62"/>
+      <c r="L8" s="63"/>
+      <c r="M8" s="63"/>
+      <c r="N8" s="63"/>
+      <c r="O8" s="63"/>
+      <c r="P8" s="63"/>
+      <c r="Q8" s="63"/>
+      <c r="R8" s="24"/>
+      <c r="S8" s="24"/>
+      <c r="T8" s="24"/>
+      <c r="U8" s="64"/>
+      <c r="V8" s="64"/>
+      <c r="W8" s="64"/>
+      <c r="X8" s="64"/>
+      <c r="Y8" s="64"/>
+      <c r="Z8" s="65"/>
+      <c r="AA8" s="65"/>
+      <c r="AB8" s="65"/>
+      <c r="AC8" s="65"/>
+      <c r="AD8" s="65"/>
+      <c r="AE8" s="66"/>
+      <c r="AF8" s="66"/>
+      <c r="AG8" s="66"/>
+      <c r="AH8" s="67"/>
+      <c r="AI8" s="67"/>
+      <c r="AJ8" s="67"/>
+      <c r="AK8" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37">
+      <c r="A9" s="69">
+        <v>6</v>
+      </c>
+      <c r="B9" s="152" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="22">
+        <v>46319</v>
+      </c>
+      <c r="D9" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="70"/>
+      <c r="K9" s="70"/>
+      <c r="L9" s="71"/>
+      <c r="M9" s="71"/>
+      <c r="N9" s="71"/>
+      <c r="O9" s="71"/>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71"/>
+      <c r="R9" s="113"/>
+      <c r="S9" s="113"/>
+      <c r="T9" s="113"/>
+      <c r="U9" s="73"/>
+      <c r="V9" s="73"/>
+      <c r="W9" s="73"/>
+      <c r="X9" s="73"/>
+      <c r="Y9" s="73"/>
+      <c r="Z9" s="74"/>
+      <c r="AA9" s="74"/>
+      <c r="AB9" s="74"/>
+      <c r="AC9" s="74"/>
+      <c r="AD9" s="74"/>
+      <c r="AE9" s="75"/>
+      <c r="AF9" s="75"/>
+      <c r="AG9" s="75"/>
+      <c r="AH9" s="76"/>
+      <c r="AI9" s="76"/>
+      <c r="AJ9" s="76"/>
+      <c r="AK9" s="93">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:37">
+      <c r="A10" s="30">
+        <v>7</v>
+      </c>
+      <c r="B10" s="151" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="22">
+        <v>46320</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" s="62"/>
+      <c r="F10" s="62"/>
+      <c r="G10" s="62"/>
+      <c r="H10" s="62"/>
+      <c r="I10" s="62"/>
+      <c r="J10" s="62"/>
+      <c r="K10" s="62"/>
+      <c r="L10" s="63"/>
+      <c r="M10" s="63"/>
+      <c r="N10" s="63"/>
+      <c r="O10" s="63"/>
+      <c r="P10" s="63"/>
+      <c r="Q10" s="63"/>
+      <c r="R10" s="27"/>
+      <c r="S10" s="27"/>
+      <c r="T10" s="27"/>
+      <c r="U10" s="64"/>
+      <c r="V10" s="64"/>
+      <c r="W10" s="64"/>
+      <c r="X10" s="64"/>
+      <c r="Y10" s="64"/>
+      <c r="Z10" s="65"/>
+      <c r="AA10" s="65"/>
+      <c r="AB10" s="65"/>
+      <c r="AC10" s="65"/>
+      <c r="AD10" s="65"/>
+      <c r="AE10" s="66"/>
+      <c r="AF10" s="66"/>
+      <c r="AG10" s="66"/>
+      <c r="AH10" s="67"/>
+      <c r="AI10" s="67"/>
+      <c r="AJ10" s="67"/>
+      <c r="AK10" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37">
+      <c r="A11" s="84">
+        <v>8</v>
+      </c>
+      <c r="B11" s="153" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="22">
+        <v>46321</v>
+      </c>
+      <c r="D11" s="84" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="77"/>
+      <c r="J11" s="77"/>
+      <c r="K11" s="77"/>
+      <c r="L11" s="78"/>
+      <c r="M11" s="78"/>
+      <c r="N11" s="78"/>
+      <c r="O11" s="78"/>
+      <c r="P11" s="78"/>
+      <c r="Q11" s="78"/>
+      <c r="R11" s="79"/>
+      <c r="S11" s="79"/>
+      <c r="T11" s="79"/>
+      <c r="U11" s="80"/>
+      <c r="V11" s="80"/>
+      <c r="W11" s="80"/>
+      <c r="X11" s="80"/>
+      <c r="Y11" s="80"/>
+      <c r="Z11" s="81"/>
+      <c r="AA11" s="81"/>
+      <c r="AB11" s="81"/>
+      <c r="AC11" s="81"/>
+      <c r="AD11" s="81"/>
+      <c r="AE11" s="82"/>
+      <c r="AF11" s="82"/>
+      <c r="AG11" s="82"/>
+      <c r="AH11" s="83"/>
+      <c r="AI11" s="83"/>
+      <c r="AJ11" s="83"/>
+      <c r="AK11" s="94">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:37">
+      <c r="A12" s="30">
+        <v>9</v>
+      </c>
+      <c r="B12" s="151" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="22">
+        <v>46322</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" s="62"/>
+      <c r="F12" s="62"/>
+      <c r="G12" s="62"/>
+      <c r="H12" s="62"/>
+      <c r="I12" s="62"/>
+      <c r="J12" s="62"/>
+      <c r="K12" s="62"/>
+      <c r="L12" s="63"/>
+      <c r="M12" s="63"/>
+      <c r="N12" s="63"/>
+      <c r="O12" s="63"/>
+      <c r="P12" s="63"/>
+      <c r="Q12" s="63"/>
+      <c r="R12" s="28"/>
+      <c r="S12" s="28"/>
+      <c r="T12" s="28"/>
+      <c r="U12" s="64"/>
+      <c r="V12" s="64"/>
+      <c r="W12" s="64"/>
+      <c r="X12" s="64"/>
+      <c r="Y12" s="64"/>
+      <c r="Z12" s="65"/>
+      <c r="AA12" s="65"/>
+      <c r="AB12" s="65"/>
+      <c r="AC12" s="65"/>
+      <c r="AD12" s="65"/>
+      <c r="AE12" s="66"/>
+      <c r="AF12" s="66"/>
+      <c r="AG12" s="66"/>
+      <c r="AH12" s="67"/>
+      <c r="AI12" s="67"/>
+      <c r="AJ12" s="67"/>
+      <c r="AK12" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:37">
+      <c r="A13" s="30">
+        <v>10</v>
+      </c>
+      <c r="B13" s="151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="22">
+        <v>46323</v>
+      </c>
+      <c r="D13" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" s="62"/>
+      <c r="F13" s="62"/>
+      <c r="G13" s="62"/>
+      <c r="H13" s="62"/>
+      <c r="I13" s="62"/>
+      <c r="J13" s="62"/>
+      <c r="K13" s="62"/>
+      <c r="L13" s="63"/>
+      <c r="M13" s="63"/>
+      <c r="N13" s="63"/>
+      <c r="O13" s="63"/>
+      <c r="P13" s="63"/>
+      <c r="Q13" s="63"/>
+      <c r="R13" s="29"/>
+      <c r="S13" s="29"/>
+      <c r="T13" s="29"/>
+      <c r="U13" s="64"/>
+      <c r="V13" s="64"/>
+      <c r="W13" s="64"/>
+      <c r="X13" s="64"/>
+      <c r="Y13" s="64"/>
+      <c r="Z13" s="65"/>
+      <c r="AA13" s="65"/>
+      <c r="AB13" s="65"/>
+      <c r="AC13" s="65"/>
+      <c r="AD13" s="65"/>
+      <c r="AE13" s="66"/>
+      <c r="AF13" s="66"/>
+      <c r="AG13" s="66"/>
+      <c r="AH13" s="67"/>
+      <c r="AI13" s="67"/>
+      <c r="AJ13" s="67"/>
+      <c r="AK13" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37">
+      <c r="A14" s="30">
+        <v>11</v>
+      </c>
+      <c r="B14" s="151" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="22">
+        <v>46324</v>
+      </c>
+      <c r="D14" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" s="62"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="62"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="62"/>
+      <c r="J14" s="62"/>
+      <c r="K14" s="62"/>
+      <c r="L14" s="63"/>
+      <c r="M14" s="63"/>
+      <c r="N14" s="63"/>
+      <c r="O14" s="63"/>
+      <c r="P14" s="63"/>
+      <c r="Q14" s="63"/>
+      <c r="R14" s="29"/>
+      <c r="S14" s="29"/>
+      <c r="T14" s="29"/>
+      <c r="U14" s="64"/>
+      <c r="V14" s="64"/>
+      <c r="W14" s="64"/>
+      <c r="X14" s="64"/>
+      <c r="Y14" s="64"/>
+      <c r="Z14" s="65"/>
+      <c r="AA14" s="65"/>
+      <c r="AB14" s="65"/>
+      <c r="AC14" s="65"/>
+      <c r="AD14" s="65"/>
+      <c r="AE14" s="66"/>
+      <c r="AF14" s="66"/>
+      <c r="AG14" s="66"/>
+      <c r="AH14" s="67"/>
+      <c r="AI14" s="67"/>
+      <c r="AJ14" s="67"/>
+      <c r="AK14" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37">
+      <c r="A15" s="30">
+        <v>12</v>
+      </c>
+      <c r="B15" s="151" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="22">
+        <v>46325</v>
+      </c>
+      <c r="D15" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" s="62"/>
+      <c r="F15" s="62"/>
+      <c r="G15" s="62"/>
+      <c r="H15" s="62"/>
+      <c r="I15" s="62"/>
+      <c r="J15" s="62"/>
+      <c r="K15" s="62"/>
+      <c r="L15" s="63"/>
+      <c r="M15" s="63"/>
+      <c r="N15" s="63"/>
+      <c r="O15" s="63"/>
+      <c r="P15" s="63"/>
+      <c r="Q15" s="63"/>
+      <c r="R15" s="29"/>
+      <c r="S15" s="29"/>
+      <c r="T15" s="29"/>
+      <c r="U15" s="64"/>
+      <c r="V15" s="64"/>
+      <c r="W15" s="64"/>
+      <c r="X15" s="64"/>
+      <c r="Y15" s="64"/>
+      <c r="Z15" s="65"/>
+      <c r="AA15" s="65"/>
+      <c r="AB15" s="65"/>
+      <c r="AC15" s="65"/>
+      <c r="AD15" s="65"/>
+      <c r="AE15" s="66"/>
+      <c r="AF15" s="66"/>
+      <c r="AG15" s="66"/>
+      <c r="AH15" s="67"/>
+      <c r="AI15" s="67"/>
+      <c r="AJ15" s="67"/>
+      <c r="AK15" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:37">
+      <c r="A16" s="30">
+        <v>13</v>
+      </c>
+      <c r="B16" s="151" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="22">
+        <v>46326</v>
+      </c>
+      <c r="D16" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="70"/>
+      <c r="K16" s="70"/>
+      <c r="L16" s="71"/>
+      <c r="M16" s="71"/>
+      <c r="N16" s="71"/>
+      <c r="O16" s="71"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="72"/>
+      <c r="T16" s="72"/>
+      <c r="U16" s="73"/>
+      <c r="V16" s="73"/>
+      <c r="W16" s="73"/>
+      <c r="X16" s="73"/>
+      <c r="Y16" s="73"/>
+      <c r="Z16" s="74"/>
+      <c r="AA16" s="74"/>
+      <c r="AB16" s="74"/>
+      <c r="AC16" s="74"/>
+      <c r="AD16" s="74"/>
+      <c r="AE16" s="75"/>
+      <c r="AF16" s="75"/>
+      <c r="AG16" s="75"/>
+      <c r="AH16" s="76"/>
+      <c r="AI16" s="76"/>
+      <c r="AJ16" s="76"/>
+      <c r="AK16" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:37" ht="30" customHeight="1">
+      <c r="A17" s="127" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" s="128"/>
+      <c r="C17" s="128"/>
+      <c r="D17" s="129"/>
+      <c r="E17" s="106">
+        <f>COUNTA(E4:E16)</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="106">
+        <f>COUNTA(F4:F16)</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="106">
+        <f>COUNTA(G4:G16)</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="106">
+        <f>COUNTA(H4:H16)</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="106">
+        <f>COUNTA(I4:I16)</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="106">
+        <f>COUNTA(J4:J16)</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="106">
+        <f>COUNTA(K4:K16)</f>
+        <v>0</v>
+      </c>
+      <c r="L17" s="63">
+        <f>COUNTA(L4:L16)</f>
+        <v>0</v>
+      </c>
+      <c r="M17" s="63">
+        <f>COUNTA(M4:M16)</f>
+        <v>0</v>
+      </c>
+      <c r="N17" s="63">
+        <f>COUNTA(N4:N16)</f>
+        <v>0</v>
+      </c>
+      <c r="O17" s="63">
+        <f>COUNTA(O4:O16)</f>
+        <v>0</v>
+      </c>
+      <c r="P17" s="63">
+        <f>COUNTA(P4:P16)</f>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="63">
+        <f>COUNTA(Q4:Q16)</f>
+        <v>0</v>
+      </c>
+      <c r="R17" s="29">
+        <f>COUNTA(R4:R16)</f>
+        <v>0</v>
+      </c>
+      <c r="S17" s="29">
+        <f>COUNTA(S4:S16)</f>
+        <v>0</v>
+      </c>
+      <c r="T17" s="29">
+        <f>COUNTA(T4:T16)</f>
+        <v>0</v>
+      </c>
+      <c r="U17" s="64">
+        <f>COUNTA(U4:U16)</f>
+        <v>0</v>
+      </c>
+      <c r="V17" s="64">
+        <f>COUNTA(V4:V16)</f>
+        <v>0</v>
+      </c>
+      <c r="W17" s="64">
+        <f>COUNTA(W4:W16)</f>
+        <v>0</v>
+      </c>
+      <c r="X17" s="64">
+        <f>COUNTA(X4:X16)</f>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="64">
+        <f>COUNTA(Y4:Y16)</f>
+        <v>0</v>
+      </c>
+      <c r="Z17" s="65">
+        <f>COUNTA(Z4:Z16)</f>
+        <v>0</v>
+      </c>
+      <c r="AA17" s="65">
+        <f>COUNTA(AA4:AA16)</f>
+        <v>0</v>
+      </c>
+      <c r="AB17" s="65">
+        <f>COUNTA(AB4:AB16)</f>
+        <v>0</v>
+      </c>
+      <c r="AC17" s="65">
+        <f>COUNTA(AC4:AC16)</f>
+        <v>0</v>
+      </c>
+      <c r="AD17" s="65">
+        <f>COUNTA(AD4:AD16)</f>
+        <v>0</v>
+      </c>
+      <c r="AE17" s="66">
+        <f>COUNTA(AE4:AE16)</f>
+        <v>0</v>
+      </c>
+      <c r="AF17" s="66">
+        <f>COUNTA(AF4:AF16)</f>
+        <v>0</v>
+      </c>
+      <c r="AG17" s="66">
+        <f>COUNTA(AG4:AG16)</f>
+        <v>0</v>
+      </c>
+      <c r="AH17" s="67">
+        <f>COUNTA(AH4:AH16)</f>
+        <v>0</v>
+      </c>
+      <c r="AI17" s="67">
+        <f>COUNTA(AI4:AI16)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="67">
+        <f>COUNTA(AJ4:AJ16)</f>
+        <v>0</v>
+      </c>
+      <c r="AK17" s="25"/>
+    </row>
+    <row r="18" spans="1:37" ht="30" customHeight="1">
+      <c r="AG18" s="124" t="s">
+        <v>78</v>
+      </c>
+      <c r="AH18" s="125"/>
+      <c r="AI18" s="125"/>
+      <c r="AJ18" s="126"/>
+      <c r="AK18" s="107">
+        <f>ROUND(AVERAGE(AK4:AK16),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:37" ht="30" customHeight="1">
+      <c r="AG19" s="124" t="s">
+        <v>79</v>
+      </c>
+      <c r="AH19" s="125"/>
+      <c r="AI19" s="125"/>
+      <c r="AJ19" s="126"/>
+      <c r="AK19" s="107">
+        <f>MAX(AK4:AK16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:37" ht="30" customHeight="1">
+      <c r="AG20" s="124" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH20" s="125"/>
+      <c r="AI20" s="125"/>
+      <c r="AJ20" s="126"/>
+      <c r="AK20" s="107">
+        <f>MIN(AK4:AK16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:37" ht="30" customHeight="1">
+      <c r="AG21" s="124" t="s">
+        <v>81</v>
+      </c>
+      <c r="AH21" s="125"/>
+      <c r="AI21" s="125"/>
+      <c r="AJ21" s="126"/>
+      <c r="AK21" s="107">
+        <f>COUNTIF(AK4:AK16, "&gt;"&amp;AK18)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:37" ht="30" customHeight="1">
+      <c r="AG22" s="124" t="s">
+        <v>82</v>
+      </c>
+      <c r="AH22" s="125"/>
+      <c r="AI22" s="125"/>
+      <c r="AJ22" s="126"/>
+      <c r="AK22" s="107">
+        <f>COUNTIF(AK4:AK16, "&lt;"&amp;AK18)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:37" ht="30" customHeight="1">
+      <c r="AG23" s="124" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH23" s="125"/>
+      <c r="AI23" s="125"/>
+      <c r="AJ23" s="126"/>
+      <c r="AK23" s="107">
+        <f>COUNTIF(AK4:AK16, "&gt;"&amp;20)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:37" ht="30" customHeight="1">
+      <c r="AG24" s="124" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH24" s="125"/>
+      <c r="AI24" s="125"/>
+      <c r="AJ24" s="126"/>
+      <c r="AK24" s="107">
+        <f>COUNTIF(AK4:AK16, "&lt;"&amp;20)</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:37" ht="30" customHeight="1"/>
+    <row r="26" spans="1:37" ht="30" customHeight="1"/>
+    <row r="27" spans="1:37" ht="30" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="AG20:AJ20"/>
+    <mergeCell ref="AG21:AJ21"/>
+    <mergeCell ref="AG22:AJ22"/>
+    <mergeCell ref="AG23:AJ23"/>
+    <mergeCell ref="AG24:AJ24"/>
+    <mergeCell ref="AE1:AG1"/>
+    <mergeCell ref="AH1:AJ1"/>
+    <mergeCell ref="AK1:AK3"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="AG18:AJ18"/>
+    <mergeCell ref="AG19:AJ19"/>
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="E1:K1"/>
+    <mergeCell ref="L1:Q1"/>
+    <mergeCell ref="R1:T1"/>
+    <mergeCell ref="U1:Y1"/>
+    <mergeCell ref="Z1:AD1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="L17:Q17 E4:AJ16">
+    <cfRule type="expression" dxfId="5" priority="6">
+      <formula>E4="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R17:T17">
+    <cfRule type="expression" dxfId="4" priority="5">
+      <formula>R17="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U17:Y17">
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>U17="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z17:AD17">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>Z17="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE17:AG17">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>AE17="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH17:AJ17">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>AH17="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Другое/2026/study_chart.xlsx
+++ b/Другое/2026/study_chart.xlsx
@@ -953,7 +953,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="101">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -1236,6 +1236,53 @@
   <si>
     <t>Формирование других привычек</t>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Выполнить срочные/важные задачи
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tw Cen MT Condensed Extra Bold"/>
+        <family val="2"/>
+      </rPr>
+      <t>считается выполненным только когда важны задач нет, либо когда работал не поднимая головы весь день</t>
+    </r>
+  </si>
+  <si>
+    <t>Kpi</t>
+  </si>
+  <si>
+    <t>Заполнить таблицу с доходами/расходами</t>
+  </si>
+  <si>
+    <t>Таблица Шульте</t>
+  </si>
+  <si>
+    <t>Мантра</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Принятие себя
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tw Cen MT Condensed Extra Bold"/>
+        <family val="2"/>
+      </rPr>
+      <t>чтение материалов</t>
+    </r>
+  </si>
+  <si>
+    <t>Конспектирование прочитанных произведений</t>
+  </si>
 </sst>
 </file>
 
@@ -1244,7 +1291,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\.mmm"/>
   </numFmts>
-  <fonts count="37">
+  <fonts count="41">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1515,6 +1562,34 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Tw Cen MT Condensed Extra Bold"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFBD07B4"/>
+      <name val="Tw Cen MT Condensed Extra Bold"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFBD07B4"/>
+      <name val="Tw Cen MT Condensed Extra Bold"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Tw Cen MT Condensed Extra Bold"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="36">
@@ -2111,7 +2186,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="162">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2441,6 +2516,15 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="27" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2468,6 +2552,60 @@
     <xf numFmtId="0" fontId="19" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2486,60 +2624,6 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2549,20 +2633,42 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="23">
+  <dxfs count="24">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFB6EA86"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -3052,18 +3158,18 @@
   </cols>
   <sheetData>
     <row r="9" spans="8:17" ht="45" customHeight="1">
-      <c r="H9" s="115" t="s">
+      <c r="H9" s="118" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="116"/>
-      <c r="J9" s="116"/>
-      <c r="K9" s="116"/>
-      <c r="L9" s="116"/>
-      <c r="M9" s="116"/>
-      <c r="N9" s="116"/>
-      <c r="O9" s="116"/>
-      <c r="P9" s="116"/>
-      <c r="Q9" s="117"/>
+      <c r="I9" s="119"/>
+      <c r="J9" s="119"/>
+      <c r="K9" s="119"/>
+      <c r="L9" s="119"/>
+      <c r="M9" s="119"/>
+      <c r="N9" s="119"/>
+      <c r="O9" s="119"/>
+      <c r="P9" s="119"/>
+      <c r="Q9" s="120"/>
     </row>
     <row r="10" spans="8:17" ht="30" customHeight="1">
       <c r="H10" s="55" t="s">
@@ -3332,11 +3438,11 @@
       <c r="Q21" s="60"/>
     </row>
     <row r="22" spans="8:17" ht="15.75">
-      <c r="H22" s="118" t="s">
+      <c r="H22" s="121" t="s">
         <v>19</v>
       </c>
-      <c r="I22" s="119"/>
-      <c r="J22" s="120"/>
+      <c r="I22" s="122"/>
+      <c r="J22" s="123"/>
       <c r="K22" s="61">
         <f>COUNTA(K11:K21)</f>
         <v>6</v>
@@ -3372,12 +3478,12 @@
     <mergeCell ref="H22:J22"/>
   </mergeCells>
   <conditionalFormatting sqref="K22:Q22">
-    <cfRule type="expression" dxfId="22" priority="1">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>Q22="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11:Q21">
-    <cfRule type="expression" dxfId="21" priority="2">
+    <cfRule type="expression" dxfId="22" priority="2">
       <formula>Q11="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3413,39 +3519,39 @@
   </cols>
   <sheetData>
     <row r="9" spans="8:38" ht="45" customHeight="1">
-      <c r="H9" s="121" t="s">
+      <c r="H9" s="124" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="122"/>
-      <c r="J9" s="122"/>
-      <c r="K9" s="122"/>
-      <c r="L9" s="122"/>
-      <c r="M9" s="122"/>
-      <c r="N9" s="122"/>
-      <c r="O9" s="122"/>
-      <c r="P9" s="122"/>
-      <c r="Q9" s="122"/>
-      <c r="R9" s="122"/>
-      <c r="S9" s="122"/>
-      <c r="T9" s="122"/>
-      <c r="U9" s="122"/>
-      <c r="V9" s="122"/>
-      <c r="W9" s="122"/>
-      <c r="X9" s="122"/>
-      <c r="Y9" s="122"/>
-      <c r="Z9" s="122"/>
-      <c r="AA9" s="122"/>
-      <c r="AB9" s="122"/>
-      <c r="AC9" s="122"/>
-      <c r="AD9" s="122"/>
-      <c r="AE9" s="122"/>
-      <c r="AF9" s="122"/>
-      <c r="AG9" s="122"/>
-      <c r="AH9" s="122"/>
-      <c r="AI9" s="122"/>
-      <c r="AJ9" s="122"/>
-      <c r="AK9" s="122"/>
-      <c r="AL9" s="122"/>
+      <c r="I9" s="125"/>
+      <c r="J9" s="125"/>
+      <c r="K9" s="125"/>
+      <c r="L9" s="125"/>
+      <c r="M9" s="125"/>
+      <c r="N9" s="125"/>
+      <c r="O9" s="125"/>
+      <c r="P9" s="125"/>
+      <c r="Q9" s="125"/>
+      <c r="R9" s="125"/>
+      <c r="S9" s="125"/>
+      <c r="T9" s="125"/>
+      <c r="U9" s="125"/>
+      <c r="V9" s="125"/>
+      <c r="W9" s="125"/>
+      <c r="X9" s="125"/>
+      <c r="Y9" s="125"/>
+      <c r="Z9" s="125"/>
+      <c r="AA9" s="125"/>
+      <c r="AB9" s="125"/>
+      <c r="AC9" s="125"/>
+      <c r="AD9" s="125"/>
+      <c r="AE9" s="125"/>
+      <c r="AF9" s="125"/>
+      <c r="AG9" s="125"/>
+      <c r="AH9" s="125"/>
+      <c r="AI9" s="125"/>
+      <c r="AJ9" s="125"/>
+      <c r="AK9" s="125"/>
+      <c r="AL9" s="125"/>
     </row>
     <row r="10" spans="8:38" ht="30" customHeight="1">
       <c r="H10" s="32" t="s">
@@ -5125,11 +5231,11 @@
       </c>
     </row>
     <row r="42" spans="8:38" ht="15.75">
-      <c r="H42" s="123" t="s">
+      <c r="H42" s="126" t="s">
         <v>19</v>
       </c>
-      <c r="I42" s="123"/>
-      <c r="J42" s="123"/>
+      <c r="I42" s="126"/>
+      <c r="J42" s="126"/>
       <c r="K42" s="32">
         <f>COUNTA(K11:K41)</f>
         <v>6</v>
@@ -5243,12 +5349,12 @@
     <mergeCell ref="H42:J42"/>
   </mergeCells>
   <conditionalFormatting sqref="AL42">
-    <cfRule type="expression" dxfId="20" priority="10">
+    <cfRule type="expression" dxfId="21" priority="10">
       <formula>AU42="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11:AK41">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>K11&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5294,66 +5400,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="135"/>
-      <c r="B1" s="136"/>
-      <c r="C1" s="137"/>
+      <c r="A1" s="132"/>
+      <c r="B1" s="133"/>
+      <c r="C1" s="134"/>
       <c r="D1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="141" t="s">
+      <c r="E1" s="138" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="141"/>
-      <c r="G1" s="141"/>
-      <c r="H1" s="141"/>
-      <c r="I1" s="141"/>
-      <c r="J1" s="141"/>
-      <c r="K1" s="141"/>
-      <c r="L1" s="142" t="s">
+      <c r="F1" s="138"/>
+      <c r="G1" s="138"/>
+      <c r="H1" s="138"/>
+      <c r="I1" s="138"/>
+      <c r="J1" s="138"/>
+      <c r="K1" s="138"/>
+      <c r="L1" s="139" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="142"/>
-      <c r="N1" s="142"/>
-      <c r="O1" s="142"/>
-      <c r="P1" s="142"/>
-      <c r="Q1" s="142"/>
-      <c r="R1" s="142"/>
-      <c r="S1" s="143" t="s">
+      <c r="M1" s="139"/>
+      <c r="N1" s="139"/>
+      <c r="O1" s="139"/>
+      <c r="P1" s="139"/>
+      <c r="Q1" s="139"/>
+      <c r="R1" s="139"/>
+      <c r="S1" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="T1" s="143"/>
-      <c r="U1" s="144" t="s">
+      <c r="T1" s="140"/>
+      <c r="U1" s="141" t="s">
         <v>40</v>
       </c>
-      <c r="V1" s="145"/>
-      <c r="W1" s="145"/>
-      <c r="X1" s="145"/>
-      <c r="Y1" s="146"/>
-      <c r="Z1" s="147" t="s">
+      <c r="V1" s="142"/>
+      <c r="W1" s="142"/>
+      <c r="X1" s="142"/>
+      <c r="Y1" s="143"/>
+      <c r="Z1" s="144" t="s">
         <v>41</v>
       </c>
-      <c r="AA1" s="147"/>
-      <c r="AB1" s="147"/>
-      <c r="AC1" s="147"/>
-      <c r="AD1" s="147"/>
-      <c r="AE1" s="130" t="s">
+      <c r="AA1" s="144"/>
+      <c r="AB1" s="144"/>
+      <c r="AC1" s="144"/>
+      <c r="AD1" s="144"/>
+      <c r="AE1" s="127" t="s">
         <v>42</v>
       </c>
-      <c r="AF1" s="130"/>
-      <c r="AG1" s="130"/>
-      <c r="AH1" s="131" t="s">
+      <c r="AF1" s="127"/>
+      <c r="AG1" s="127"/>
+      <c r="AH1" s="128" t="s">
         <v>43</v>
       </c>
-      <c r="AI1" s="131"/>
-      <c r="AJ1" s="131"/>
-      <c r="AK1" s="132" t="s">
+      <c r="AI1" s="128"/>
+      <c r="AJ1" s="128"/>
+      <c r="AK1" s="129" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:37" s="2" customFormat="1" ht="30" customHeight="1">
-      <c r="A2" s="138"/>
-      <c r="B2" s="139"/>
-      <c r="C2" s="140"/>
+      <c r="A2" s="135"/>
+      <c r="B2" s="136"/>
+      <c r="C2" s="137"/>
       <c r="D2" s="5" t="s">
         <v>44</v>
       </c>
@@ -5447,7 +5553,7 @@
       <c r="AH2" s="12"/>
       <c r="AI2" s="12"/>
       <c r="AJ2" s="12"/>
-      <c r="AK2" s="133"/>
+      <c r="AK2" s="130"/>
     </row>
     <row r="3" spans="1:37">
       <c r="A3" s="13" t="s">
@@ -5558,7 +5664,7 @@
       <c r="AJ3" s="20">
         <v>2</v>
       </c>
-      <c r="AK3" s="134"/>
+      <c r="AK3" s="131"/>
     </row>
     <row r="4" spans="1:37">
       <c r="A4" s="21">
@@ -7609,12 +7715,12 @@
       </c>
     </row>
     <row r="35" spans="1:37" ht="30" customHeight="1">
-      <c r="A35" s="127" t="s">
+      <c r="A35" s="148" t="s">
         <v>77</v>
       </c>
-      <c r="B35" s="128"/>
-      <c r="C35" s="128"/>
-      <c r="D35" s="129"/>
+      <c r="B35" s="149"/>
+      <c r="C35" s="149"/>
+      <c r="D35" s="150"/>
       <c r="E35" s="106">
         <f>COUNTA(E4:E34)</f>
         <v>14</v>
@@ -7746,84 +7852,84 @@
       <c r="AK35" s="25"/>
     </row>
     <row r="36" spans="1:37" ht="30" customHeight="1">
-      <c r="AG36" s="124" t="s">
+      <c r="AG36" s="145" t="s">
         <v>78</v>
       </c>
-      <c r="AH36" s="125"/>
-      <c r="AI36" s="125"/>
-      <c r="AJ36" s="126"/>
+      <c r="AH36" s="146"/>
+      <c r="AI36" s="146"/>
+      <c r="AJ36" s="147"/>
       <c r="AK36" s="107">
         <f>ROUND(AVERAGE(AK4:AK34),0)</f>
         <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:37" ht="30" customHeight="1">
-      <c r="AG37" s="124" t="s">
+      <c r="AG37" s="145" t="s">
         <v>79</v>
       </c>
-      <c r="AH37" s="125"/>
-      <c r="AI37" s="125"/>
-      <c r="AJ37" s="126"/>
+      <c r="AH37" s="146"/>
+      <c r="AI37" s="146"/>
+      <c r="AJ37" s="147"/>
       <c r="AK37" s="107">
         <f>MAX(AK4:AK34)</f>
         <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:37" ht="30" customHeight="1">
-      <c r="AG38" s="124" t="s">
+      <c r="AG38" s="145" t="s">
         <v>80</v>
       </c>
-      <c r="AH38" s="125"/>
-      <c r="AI38" s="125"/>
-      <c r="AJ38" s="126"/>
+      <c r="AH38" s="146"/>
+      <c r="AI38" s="146"/>
+      <c r="AJ38" s="147"/>
       <c r="AK38" s="107">
         <f>MIN(AK4:AK34)</f>
         <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:37" ht="30" customHeight="1">
-      <c r="AG39" s="124" t="s">
+      <c r="AG39" s="145" t="s">
         <v>81</v>
       </c>
-      <c r="AH39" s="125"/>
-      <c r="AI39" s="125"/>
-      <c r="AJ39" s="126"/>
+      <c r="AH39" s="146"/>
+      <c r="AI39" s="146"/>
+      <c r="AJ39" s="147"/>
       <c r="AK39" s="107">
         <f>COUNTIF(AK4:AK34, "&gt;"&amp;AK36)</f>
         <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:37" ht="30" customHeight="1">
-      <c r="AG40" s="124" t="s">
+      <c r="AG40" s="145" t="s">
         <v>82</v>
       </c>
-      <c r="AH40" s="125"/>
-      <c r="AI40" s="125"/>
-      <c r="AJ40" s="126"/>
+      <c r="AH40" s="146"/>
+      <c r="AI40" s="146"/>
+      <c r="AJ40" s="147"/>
       <c r="AK40" s="107">
         <f>COUNTIF(AK4:AK34, "&lt;"&amp;AK36)</f>
         <v>18</v>
       </c>
     </row>
     <row r="41" spans="1:37" ht="30" customHeight="1">
-      <c r="AG41" s="124" t="s">
+      <c r="AG41" s="145" t="s">
         <v>83</v>
       </c>
-      <c r="AH41" s="125"/>
-      <c r="AI41" s="125"/>
-      <c r="AJ41" s="126"/>
+      <c r="AH41" s="146"/>
+      <c r="AI41" s="146"/>
+      <c r="AJ41" s="147"/>
       <c r="AK41" s="107">
         <f>COUNTIF(AK4:AK34, "&gt;"&amp;20)</f>
         <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:37" ht="30" customHeight="1">
-      <c r="AG42" s="124" t="s">
+      <c r="AG42" s="145" t="s">
         <v>84</v>
       </c>
-      <c r="AH42" s="125"/>
-      <c r="AI42" s="125"/>
-      <c r="AJ42" s="126"/>
+      <c r="AH42" s="146"/>
+      <c r="AI42" s="146"/>
+      <c r="AJ42" s="147"/>
       <c r="AK42" s="107">
         <f>COUNTIF(AK4:AK34, "&lt;"&amp;20)</f>
         <v>21</v>
@@ -7834,6 +7940,14 @@
     <row r="45" spans="1:37" ht="30" customHeight="1"/>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="AG40:AJ40"/>
+    <mergeCell ref="AG41:AJ41"/>
+    <mergeCell ref="AG42:AJ42"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="AG36:AJ36"/>
+    <mergeCell ref="AG37:AJ37"/>
+    <mergeCell ref="AG38:AJ38"/>
+    <mergeCell ref="AG39:AJ39"/>
     <mergeCell ref="AE1:AG1"/>
     <mergeCell ref="AH1:AJ1"/>
     <mergeCell ref="AK1:AK3"/>
@@ -7843,47 +7957,39 @@
     <mergeCell ref="S1:T1"/>
     <mergeCell ref="U1:Y1"/>
     <mergeCell ref="Z1:AD1"/>
-    <mergeCell ref="AG40:AJ40"/>
-    <mergeCell ref="AG41:AJ41"/>
-    <mergeCell ref="AG42:AJ42"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="AG36:AJ36"/>
-    <mergeCell ref="AG37:AJ37"/>
-    <mergeCell ref="AG38:AJ38"/>
-    <mergeCell ref="AG39:AJ39"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:AJ34">
-    <cfRule type="expression" dxfId="18" priority="7">
+    <cfRule type="expression" dxfId="19" priority="7">
       <formula>E4="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L35:R35">
-    <cfRule type="expression" dxfId="17" priority="6">
+    <cfRule type="expression" dxfId="18" priority="6">
       <formula>L35="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S35:T35">
-    <cfRule type="expression" dxfId="16" priority="5">
+    <cfRule type="expression" dxfId="17" priority="5">
       <formula>S35="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U35:Y35">
-    <cfRule type="expression" dxfId="15" priority="4">
+    <cfRule type="expression" dxfId="16" priority="4">
       <formula>U35="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z35:AD35">
-    <cfRule type="expression" dxfId="14" priority="3">
+    <cfRule type="expression" dxfId="15" priority="3">
       <formula>Z35="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE35:AG35">
-    <cfRule type="expression" dxfId="13" priority="2">
+    <cfRule type="expression" dxfId="14" priority="2">
       <formula>AE35="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH35:AJ35">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>AH35="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7928,66 +8034,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="135"/>
-      <c r="B1" s="136"/>
-      <c r="C1" s="137"/>
+      <c r="A1" s="132"/>
+      <c r="B1" s="133"/>
+      <c r="C1" s="134"/>
       <c r="D1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="141" t="s">
+      <c r="E1" s="138" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="141"/>
-      <c r="G1" s="141"/>
-      <c r="H1" s="141"/>
-      <c r="I1" s="141"/>
-      <c r="J1" s="141"/>
-      <c r="K1" s="141"/>
-      <c r="L1" s="142" t="s">
+      <c r="F1" s="138"/>
+      <c r="G1" s="138"/>
+      <c r="H1" s="138"/>
+      <c r="I1" s="138"/>
+      <c r="J1" s="138"/>
+      <c r="K1" s="138"/>
+      <c r="L1" s="139" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="142"/>
-      <c r="N1" s="142"/>
-      <c r="O1" s="142"/>
-      <c r="P1" s="142"/>
-      <c r="Q1" s="142"/>
-      <c r="R1" s="148" t="s">
+      <c r="M1" s="139"/>
+      <c r="N1" s="139"/>
+      <c r="O1" s="139"/>
+      <c r="P1" s="139"/>
+      <c r="Q1" s="139"/>
+      <c r="R1" s="151" t="s">
         <v>39</v>
       </c>
-      <c r="S1" s="149"/>
-      <c r="T1" s="150"/>
-      <c r="U1" s="144" t="s">
+      <c r="S1" s="152"/>
+      <c r="T1" s="153"/>
+      <c r="U1" s="141" t="s">
         <v>40</v>
       </c>
-      <c r="V1" s="145"/>
-      <c r="W1" s="145"/>
-      <c r="X1" s="145"/>
-      <c r="Y1" s="146"/>
-      <c r="Z1" s="147" t="s">
+      <c r="V1" s="142"/>
+      <c r="W1" s="142"/>
+      <c r="X1" s="142"/>
+      <c r="Y1" s="143"/>
+      <c r="Z1" s="144" t="s">
         <v>41</v>
       </c>
-      <c r="AA1" s="147"/>
-      <c r="AB1" s="147"/>
-      <c r="AC1" s="147"/>
-      <c r="AD1" s="147"/>
-      <c r="AE1" s="130" t="s">
+      <c r="AA1" s="144"/>
+      <c r="AB1" s="144"/>
+      <c r="AC1" s="144"/>
+      <c r="AD1" s="144"/>
+      <c r="AE1" s="127" t="s">
         <v>42</v>
       </c>
-      <c r="AF1" s="130"/>
-      <c r="AG1" s="130"/>
-      <c r="AH1" s="131" t="s">
+      <c r="AF1" s="127"/>
+      <c r="AG1" s="127"/>
+      <c r="AH1" s="128" t="s">
         <v>43</v>
       </c>
-      <c r="AI1" s="131"/>
-      <c r="AJ1" s="131"/>
-      <c r="AK1" s="132" t="s">
+      <c r="AI1" s="128"/>
+      <c r="AJ1" s="128"/>
+      <c r="AK1" s="129" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:37" s="2" customFormat="1" ht="45" customHeight="1">
-      <c r="A2" s="138"/>
-      <c r="B2" s="139"/>
-      <c r="C2" s="140"/>
+      <c r="A2" s="135"/>
+      <c r="B2" s="136"/>
+      <c r="C2" s="137"/>
       <c r="D2" s="5" t="s">
         <v>44</v>
       </c>
@@ -8083,7 +8189,7 @@
       </c>
       <c r="AI2" s="12"/>
       <c r="AJ2" s="12"/>
-      <c r="AK2" s="133"/>
+      <c r="AK2" s="130"/>
     </row>
     <row r="3" spans="1:37">
       <c r="A3" s="13" t="s">
@@ -8194,7 +8300,7 @@
       <c r="AJ3" s="20">
         <v>1</v>
       </c>
-      <c r="AK3" s="134"/>
+      <c r="AK3" s="131"/>
     </row>
     <row r="4" spans="1:37">
       <c r="A4" s="30">
@@ -9951,12 +10057,12 @@
       </c>
     </row>
     <row r="34" spans="1:37" ht="30" customHeight="1">
-      <c r="A34" s="127" t="s">
+      <c r="A34" s="148" t="s">
         <v>77</v>
       </c>
-      <c r="B34" s="128"/>
-      <c r="C34" s="128"/>
-      <c r="D34" s="129"/>
+      <c r="B34" s="149"/>
+      <c r="C34" s="149"/>
+      <c r="D34" s="150"/>
       <c r="E34" s="106">
         <f t="shared" ref="E34:AJ34" si="1">COUNTA(E4:E33)</f>
         <v>2</v>
@@ -10088,84 +10194,84 @@
       <c r="AK34" s="25"/>
     </row>
     <row r="35" spans="1:37" ht="30" customHeight="1">
-      <c r="AG35" s="124" t="s">
+      <c r="AG35" s="145" t="s">
         <v>78</v>
       </c>
-      <c r="AH35" s="125"/>
-      <c r="AI35" s="125"/>
-      <c r="AJ35" s="126"/>
+      <c r="AH35" s="146"/>
+      <c r="AI35" s="146"/>
+      <c r="AJ35" s="147"/>
       <c r="AK35" s="107">
         <f>ROUND(AVERAGE(AK4:AK33),0)</f>
         <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:37" ht="30" customHeight="1">
-      <c r="AG36" s="124" t="s">
+      <c r="AG36" s="145" t="s">
         <v>79</v>
       </c>
-      <c r="AH36" s="125"/>
-      <c r="AI36" s="125"/>
-      <c r="AJ36" s="126"/>
+      <c r="AH36" s="146"/>
+      <c r="AI36" s="146"/>
+      <c r="AJ36" s="147"/>
       <c r="AK36" s="107">
         <f>MAX(AK4:AK33)</f>
         <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:37" ht="30" customHeight="1">
-      <c r="AG37" s="124" t="s">
+      <c r="AG37" s="145" t="s">
         <v>80</v>
       </c>
-      <c r="AH37" s="125"/>
-      <c r="AI37" s="125"/>
-      <c r="AJ37" s="126"/>
+      <c r="AH37" s="146"/>
+      <c r="AI37" s="146"/>
+      <c r="AJ37" s="147"/>
       <c r="AK37" s="107">
         <f>MIN(AK4:AK33)</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:37" ht="30" customHeight="1">
-      <c r="AG38" s="124" t="s">
+      <c r="AG38" s="145" t="s">
         <v>81</v>
       </c>
-      <c r="AH38" s="125"/>
-      <c r="AI38" s="125"/>
-      <c r="AJ38" s="126"/>
+      <c r="AH38" s="146"/>
+      <c r="AI38" s="146"/>
+      <c r="AJ38" s="147"/>
       <c r="AK38" s="107">
         <f>COUNTIF(AK4:AK33, "&gt;"&amp;AK35)</f>
         <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:37" ht="30" customHeight="1">
-      <c r="AG39" s="124" t="s">
+      <c r="AG39" s="145" t="s">
         <v>82</v>
       </c>
-      <c r="AH39" s="125"/>
-      <c r="AI39" s="125"/>
-      <c r="AJ39" s="126"/>
+      <c r="AH39" s="146"/>
+      <c r="AI39" s="146"/>
+      <c r="AJ39" s="147"/>
       <c r="AK39" s="107">
         <f>COUNTIF(AK4:AK33, "&lt;"&amp;AK35)</f>
         <v>14</v>
       </c>
     </row>
     <row r="40" spans="1:37" ht="30" customHeight="1">
-      <c r="AG40" s="124" t="s">
+      <c r="AG40" s="145" t="s">
         <v>83</v>
       </c>
-      <c r="AH40" s="125"/>
-      <c r="AI40" s="125"/>
-      <c r="AJ40" s="126"/>
+      <c r="AH40" s="146"/>
+      <c r="AI40" s="146"/>
+      <c r="AJ40" s="147"/>
       <c r="AK40" s="107">
         <f>COUNTIF(AK4:AK33, "&gt;"&amp;20)</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:37" ht="30" customHeight="1">
-      <c r="AG41" s="124" t="s">
+      <c r="AG41" s="145" t="s">
         <v>84</v>
       </c>
-      <c r="AH41" s="125"/>
-      <c r="AI41" s="125"/>
-      <c r="AJ41" s="126"/>
+      <c r="AH41" s="146"/>
+      <c r="AI41" s="146"/>
+      <c r="AJ41" s="147"/>
       <c r="AK41" s="107">
         <f>COUNTIF(AK4:AK33, "&lt;"&amp;20)</f>
         <v>30</v>
@@ -10176,51 +10282,51 @@
     <row r="44" spans="1:37" ht="30" customHeight="1"/>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="AE1:AG1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="AG40:AJ40"/>
-    <mergeCell ref="AG41:AJ41"/>
-    <mergeCell ref="AK1:AK3"/>
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="E1:K1"/>
+    <mergeCell ref="L1:Q1"/>
+    <mergeCell ref="U1:Y1"/>
+    <mergeCell ref="Z1:AD1"/>
+    <mergeCell ref="R1:T1"/>
     <mergeCell ref="A34:D34"/>
     <mergeCell ref="AG37:AJ37"/>
     <mergeCell ref="AG38:AJ38"/>
     <mergeCell ref="AG39:AJ39"/>
     <mergeCell ref="AG35:AJ35"/>
     <mergeCell ref="AG36:AJ36"/>
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="E1:K1"/>
-    <mergeCell ref="L1:Q1"/>
-    <mergeCell ref="U1:Y1"/>
-    <mergeCell ref="Z1:AD1"/>
-    <mergeCell ref="R1:T1"/>
+    <mergeCell ref="AE1:AG1"/>
+    <mergeCell ref="AH1:AJ1"/>
+    <mergeCell ref="AG40:AJ40"/>
+    <mergeCell ref="AG41:AJ41"/>
+    <mergeCell ref="AK1:AK3"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:AJ33 L34:Q34">
-    <cfRule type="expression" dxfId="11" priority="7">
+    <cfRule type="expression" dxfId="12" priority="7">
       <formula>E4="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R34:T34">
-    <cfRule type="expression" dxfId="10" priority="5">
+    <cfRule type="expression" dxfId="11" priority="5">
       <formula>R34="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U34:Y34">
-    <cfRule type="expression" dxfId="9" priority="4">
+    <cfRule type="expression" dxfId="10" priority="4">
       <formula>U34="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z34:AD34">
-    <cfRule type="expression" dxfId="8" priority="3">
+    <cfRule type="expression" dxfId="9" priority="3">
       <formula>Z34="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE34:AG34">
-    <cfRule type="expression" dxfId="7" priority="2">
+    <cfRule type="expression" dxfId="8" priority="2">
       <formula>AE34="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH34:AJ34">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>AH34="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10242,89 +10348,87 @@
     <col min="8" max="11" width="15.7109375" style="3" customWidth="1"/>
     <col min="12" max="12" width="20.28515625" style="3" customWidth="1"/>
     <col min="13" max="13" width="20.42578125" style="3" customWidth="1"/>
-    <col min="14" max="14" width="33.42578125" style="3" customWidth="1"/>
-    <col min="15" max="15" width="26.7109375" style="3" customWidth="1"/>
+    <col min="14" max="14" width="38.7109375" style="3" customWidth="1"/>
+    <col min="15" max="15" width="17.28515625" style="3" customWidth="1"/>
     <col min="16" max="16" width="32.28515625" style="3" customWidth="1"/>
     <col min="17" max="17" width="21.140625" style="3" customWidth="1"/>
     <col min="18" max="20" width="15.7109375" style="3" customWidth="1"/>
     <col min="21" max="21" width="23.7109375" style="3" customWidth="1"/>
     <col min="22" max="22" width="21.5703125" style="3" customWidth="1"/>
     <col min="23" max="25" width="15.7109375" style="3" customWidth="1"/>
-    <col min="26" max="26" width="21.42578125" style="3" customWidth="1"/>
-    <col min="27" max="27" width="15.7109375" style="3" customWidth="1"/>
-    <col min="28" max="28" width="27.140625" style="3" customWidth="1"/>
-    <col min="29" max="29" width="15.7109375" style="3" customWidth="1"/>
-    <col min="30" max="30" width="29.28515625" style="3" customWidth="1"/>
-    <col min="31" max="31" width="24.42578125" style="3" customWidth="1"/>
-    <col min="32" max="32" width="33.7109375" style="3" customWidth="1"/>
-    <col min="33" max="33" width="34.28515625" style="3" customWidth="1"/>
-    <col min="34" max="36" width="15.7109375" style="3" customWidth="1"/>
+    <col min="26" max="26" width="16.7109375" style="3" customWidth="1"/>
+    <col min="27" max="28" width="15.7109375" style="3" customWidth="1"/>
+    <col min="29" max="29" width="17.140625" style="3" customWidth="1"/>
+    <col min="30" max="30" width="24.42578125" style="3" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="3" customWidth="1"/>
+    <col min="32" max="32" width="20" style="3" customWidth="1"/>
+    <col min="33" max="33" width="17" style="3" customWidth="1"/>
+    <col min="34" max="35" width="15.7109375" style="3" customWidth="1"/>
+    <col min="36" max="36" width="26.28515625" style="3" customWidth="1"/>
     <col min="37" max="37" width="24.5703125" style="3" customWidth="1"/>
     <col min="38" max="38" width="20.7109375" style="3" customWidth="1"/>
     <col min="39" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="135"/>
-      <c r="B1" s="136"/>
-      <c r="C1" s="137"/>
+      <c r="A1" s="132"/>
+      <c r="B1" s="133"/>
+      <c r="C1" s="134"/>
       <c r="D1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="141" t="s">
+      <c r="E1" s="138" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="141"/>
-      <c r="G1" s="141"/>
-      <c r="H1" s="141"/>
-      <c r="I1" s="141"/>
-      <c r="J1" s="141"/>
-      <c r="K1" s="141"/>
-      <c r="L1" s="142" t="s">
+      <c r="F1" s="138"/>
+      <c r="G1" s="138"/>
+      <c r="H1" s="138"/>
+      <c r="I1" s="138"/>
+      <c r="J1" s="138"/>
+      <c r="K1" s="138"/>
+      <c r="L1" s="139" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="142"/>
-      <c r="N1" s="142"/>
-      <c r="O1" s="142"/>
-      <c r="P1" s="142"/>
-      <c r="Q1" s="142"/>
-      <c r="R1" s="148" t="s">
+      <c r="M1" s="139"/>
+      <c r="N1" s="139"/>
+      <c r="O1" s="139"/>
+      <c r="P1" s="139"/>
+      <c r="Q1" s="139"/>
+      <c r="R1" s="156" t="s">
         <v>39</v>
       </c>
-      <c r="S1" s="149"/>
-      <c r="T1" s="150"/>
-      <c r="U1" s="144" t="s">
+      <c r="S1" s="157"/>
+      <c r="T1" s="158"/>
+      <c r="U1" s="141" t="s">
         <v>40</v>
       </c>
-      <c r="V1" s="145"/>
-      <c r="W1" s="145"/>
-      <c r="X1" s="145"/>
-      <c r="Y1" s="146"/>
-      <c r="Z1" s="147" t="s">
+      <c r="V1" s="142"/>
+      <c r="W1" s="142"/>
+      <c r="X1" s="142"/>
+      <c r="Y1" s="143"/>
+      <c r="Z1" s="144" t="s">
         <v>41</v>
       </c>
-      <c r="AA1" s="147"/>
-      <c r="AB1" s="147"/>
-      <c r="AC1" s="147"/>
-      <c r="AD1" s="147"/>
-      <c r="AE1" s="130" t="s">
+      <c r="AA1" s="144"/>
+      <c r="AB1" s="144"/>
+      <c r="AC1" s="144"/>
+      <c r="AD1" s="159" t="s">
         <v>93</v>
       </c>
-      <c r="AF1" s="130"/>
-      <c r="AG1" s="130"/>
-      <c r="AH1" s="131" t="s">
-        <v>43</v>
-      </c>
-      <c r="AI1" s="131"/>
-      <c r="AJ1" s="131"/>
-      <c r="AK1" s="132" t="s">
+      <c r="AE1" s="160"/>
+      <c r="AF1" s="160"/>
+      <c r="AG1" s="160"/>
+      <c r="AH1" s="160"/>
+      <c r="AI1" s="160"/>
+      <c r="AJ1" s="161"/>
+      <c r="AK1" s="129" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:37" s="2" customFormat="1" ht="60" customHeight="1">
-      <c r="A2" s="138"/>
-      <c r="B2" s="139"/>
-      <c r="C2" s="140"/>
+    <row r="2" spans="1:37" s="2" customFormat="1" ht="70.5" customHeight="1">
+      <c r="A2" s="135"/>
+      <c r="B2" s="136"/>
+      <c r="C2" s="137"/>
       <c r="D2" s="5" t="s">
         <v>44</v>
       </c>
@@ -10356,7 +10460,7 @@
         <v>47</v>
       </c>
       <c r="N2" s="7" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="O2" s="7" t="s">
         <v>29</v>
@@ -10367,14 +10471,14 @@
       <c r="Q2" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="R2" s="8" t="s">
+      <c r="R2" s="155" t="s">
         <v>52</v>
       </c>
-      <c r="S2" s="8" t="s">
+      <c r="S2" s="154" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="8" t="s">
-        <v>86</v>
+      <c r="T2" s="154" t="s">
+        <v>95</v>
       </c>
       <c r="U2" s="9" t="s">
         <v>53</v>
@@ -10398,16 +10502,16 @@
         <v>58</v>
       </c>
       <c r="AB2" s="10" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="AC2" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD2" s="10" t="s">
         <v>60</v>
       </c>
+      <c r="AD2" s="11" t="s">
+        <v>96</v>
+      </c>
       <c r="AE2" s="11" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="AF2" s="11" t="s">
         <v>88</v>
@@ -10415,12 +10519,16 @@
       <c r="AG2" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="AH2" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AI2" s="12"/>
-      <c r="AJ2" s="12"/>
-      <c r="AK2" s="133"/>
+      <c r="AH2" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI2" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="AJ2" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="AK2" s="130"/>
     </row>
     <row r="3" spans="1:37">
       <c r="A3" s="13" t="s">
@@ -10445,13 +10553,13 @@
         <v>1</v>
       </c>
       <c r="H3" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" s="14">
         <v>1</v>
       </c>
       <c r="J3" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" s="14">
         <v>1</v>
@@ -10463,81 +10571,81 @@
         <v>1</v>
       </c>
       <c r="N3" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O3" s="15">
         <v>1</v>
       </c>
       <c r="P3" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R3" s="16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S3" s="16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T3" s="16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U3" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V3" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W3" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X3" s="17">
         <v>1</v>
       </c>
       <c r="Y3" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z3" s="18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA3" s="18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB3" s="18">
         <v>1</v>
       </c>
       <c r="AC3" s="18">
-        <v>2</v>
-      </c>
-      <c r="AD3" s="18">
         <v>1</v>
       </c>
+      <c r="AD3" s="19">
+        <v>1</v>
+      </c>
       <c r="AE3" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF3" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG3" s="19">
-        <v>3</v>
-      </c>
-      <c r="AH3" s="20">
-        <v>2</v>
-      </c>
-      <c r="AI3" s="20">
-        <v>2</v>
-      </c>
-      <c r="AJ3" s="20">
         <v>1</v>
       </c>
-      <c r="AK3" s="134"/>
+      <c r="AH3" s="19">
+        <v>1</v>
+      </c>
+      <c r="AI3" s="19">
+        <v>1</v>
+      </c>
+      <c r="AJ3" s="19">
+        <v>1</v>
+      </c>
+      <c r="AK3" s="131"/>
     </row>
     <row r="4" spans="1:37">
       <c r="A4" s="30">
         <v>1</v>
       </c>
-      <c r="B4" s="151" t="s">
+      <c r="B4" s="115" t="s">
         <v>14</v>
       </c>
       <c r="C4" s="22">
@@ -10546,15 +10654,23 @@
       <c r="D4" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="E4" s="62"/>
+      <c r="E4" s="62" t="s">
+        <v>12</v>
+      </c>
       <c r="F4" s="62"/>
       <c r="G4" s="62"/>
       <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62"/>
+      <c r="I4" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" s="62" t="s">
+        <v>12</v>
+      </c>
       <c r="K4" s="62"/>
       <c r="L4" s="63"/>
-      <c r="M4" s="63"/>
+      <c r="M4" s="63" t="s">
+        <v>12</v>
+      </c>
       <c r="N4" s="63"/>
       <c r="O4" s="63"/>
       <c r="P4" s="63"/>
@@ -10567,27 +10683,31 @@
       <c r="W4" s="64"/>
       <c r="X4" s="64"/>
       <c r="Y4" s="64"/>
-      <c r="Z4" s="65"/>
+      <c r="Z4" s="65" t="s">
+        <v>12</v>
+      </c>
       <c r="AA4" s="65"/>
       <c r="AB4" s="65"/>
       <c r="AC4" s="65"/>
-      <c r="AD4" s="65"/>
+      <c r="AD4" s="66" t="s">
+        <v>12</v>
+      </c>
       <c r="AE4" s="66"/>
       <c r="AF4" s="66"/>
       <c r="AG4" s="66"/>
-      <c r="AH4" s="67"/>
-      <c r="AI4" s="67"/>
-      <c r="AJ4" s="67"/>
+      <c r="AH4" s="66"/>
+      <c r="AI4" s="66"/>
+      <c r="AJ4" s="66"/>
       <c r="AK4" s="25">
-        <f t="shared" ref="AK4:AK16" si="0">SUMIF(E4:AJ4,"&lt;&gt;",$E$3:$AJ$3)</f>
-        <v>0</v>
+        <f>SUMIF(E4:AJ4,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:37">
       <c r="A5" s="30">
         <v>2</v>
       </c>
-      <c r="B5" s="151" t="s">
+      <c r="B5" s="115" t="s">
         <v>15</v>
       </c>
       <c r="C5" s="22">
@@ -10598,13 +10718,23 @@
       </c>
       <c r="E5" s="62"/>
       <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
+      <c r="G5" s="62" t="s">
+        <v>12</v>
+      </c>
       <c r="H5" s="62"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="62"/>
+      <c r="I5" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="62" t="s">
+        <v>12</v>
+      </c>
       <c r="K5" s="62"/>
-      <c r="L5" s="63"/>
-      <c r="M5" s="63"/>
+      <c r="L5" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="M5" s="63" t="s">
+        <v>12</v>
+      </c>
       <c r="N5" s="63"/>
       <c r="O5" s="63"/>
       <c r="P5" s="63"/>
@@ -10621,23 +10751,25 @@
       <c r="AA5" s="65"/>
       <c r="AB5" s="65"/>
       <c r="AC5" s="65"/>
-      <c r="AD5" s="65"/>
-      <c r="AE5" s="66"/>
+      <c r="AD5" s="66"/>
+      <c r="AE5" s="66" t="s">
+        <v>12</v>
+      </c>
       <c r="AF5" s="66"/>
       <c r="AG5" s="66"/>
-      <c r="AH5" s="67"/>
-      <c r="AI5" s="67"/>
-      <c r="AJ5" s="67"/>
+      <c r="AH5" s="66"/>
+      <c r="AI5" s="66"/>
+      <c r="AJ5" s="66"/>
       <c r="AK5" s="25">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>SUMIF(E5:AJ5,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:37">
       <c r="A6" s="30">
         <v>3</v>
       </c>
-      <c r="B6" s="151" t="s">
+      <c r="B6" s="115" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="22">
@@ -10671,15 +10803,15 @@
       <c r="AA6" s="65"/>
       <c r="AB6" s="65"/>
       <c r="AC6" s="65"/>
-      <c r="AD6" s="65"/>
+      <c r="AD6" s="66"/>
       <c r="AE6" s="66"/>
       <c r="AF6" s="66"/>
       <c r="AG6" s="66"/>
-      <c r="AH6" s="67"/>
-      <c r="AI6" s="67"/>
-      <c r="AJ6" s="67"/>
+      <c r="AH6" s="66"/>
+      <c r="AI6" s="66"/>
+      <c r="AJ6" s="66"/>
       <c r="AK6" s="25">
-        <f t="shared" si="0"/>
+        <f>SUMIF(E6:AJ6,"&lt;&gt;",$E$3:$AJ$3)</f>
         <v>0</v>
       </c>
     </row>
@@ -10687,7 +10819,7 @@
       <c r="A7" s="30">
         <v>4</v>
       </c>
-      <c r="B7" s="151" t="s">
+      <c r="B7" s="115" t="s">
         <v>17</v>
       </c>
       <c r="C7" s="22">
@@ -10721,15 +10853,15 @@
       <c r="AA7" s="65"/>
       <c r="AB7" s="65"/>
       <c r="AC7" s="65"/>
-      <c r="AD7" s="65"/>
+      <c r="AD7" s="66"/>
       <c r="AE7" s="66"/>
       <c r="AF7" s="66"/>
       <c r="AG7" s="66"/>
-      <c r="AH7" s="67"/>
-      <c r="AI7" s="67"/>
-      <c r="AJ7" s="67"/>
+      <c r="AH7" s="66"/>
+      <c r="AI7" s="66"/>
+      <c r="AJ7" s="66"/>
       <c r="AK7" s="25">
-        <f t="shared" si="0"/>
+        <f>SUMIF(E7:AJ7,"&lt;&gt;",$E$3:$AJ$3)</f>
         <v>0</v>
       </c>
     </row>
@@ -10737,7 +10869,7 @@
       <c r="A8" s="30">
         <v>5</v>
       </c>
-      <c r="B8" s="151" t="s">
+      <c r="B8" s="115" t="s">
         <v>18</v>
       </c>
       <c r="C8" s="22">
@@ -10771,15 +10903,15 @@
       <c r="AA8" s="65"/>
       <c r="AB8" s="65"/>
       <c r="AC8" s="65"/>
-      <c r="AD8" s="65"/>
+      <c r="AD8" s="66"/>
       <c r="AE8" s="66"/>
       <c r="AF8" s="66"/>
       <c r="AG8" s="66"/>
-      <c r="AH8" s="67"/>
-      <c r="AI8" s="67"/>
-      <c r="AJ8" s="67"/>
+      <c r="AH8" s="66"/>
+      <c r="AI8" s="66"/>
+      <c r="AJ8" s="66"/>
       <c r="AK8" s="25">
-        <f t="shared" si="0"/>
+        <f>SUMIF(E8:AJ8,"&lt;&gt;",$E$3:$AJ$3)</f>
         <v>0</v>
       </c>
     </row>
@@ -10787,7 +10919,7 @@
       <c r="A9" s="69">
         <v>6</v>
       </c>
-      <c r="B9" s="152" t="s">
+      <c r="B9" s="116" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="22">
@@ -10821,15 +10953,15 @@
       <c r="AA9" s="74"/>
       <c r="AB9" s="74"/>
       <c r="AC9" s="74"/>
-      <c r="AD9" s="74"/>
+      <c r="AD9" s="75"/>
       <c r="AE9" s="75"/>
       <c r="AF9" s="75"/>
       <c r="AG9" s="75"/>
-      <c r="AH9" s="76"/>
-      <c r="AI9" s="76"/>
-      <c r="AJ9" s="76"/>
+      <c r="AH9" s="75"/>
+      <c r="AI9" s="75"/>
+      <c r="AJ9" s="75"/>
       <c r="AK9" s="93">
-        <f t="shared" si="0"/>
+        <f>SUMIF(E9:AJ9,"&lt;&gt;",$E$3:$AJ$3)</f>
         <v>0</v>
       </c>
     </row>
@@ -10837,7 +10969,7 @@
       <c r="A10" s="30">
         <v>7</v>
       </c>
-      <c r="B10" s="151" t="s">
+      <c r="B10" s="115" t="s">
         <v>13</v>
       </c>
       <c r="C10" s="22">
@@ -10871,15 +11003,15 @@
       <c r="AA10" s="65"/>
       <c r="AB10" s="65"/>
       <c r="AC10" s="65"/>
-      <c r="AD10" s="65"/>
+      <c r="AD10" s="66"/>
       <c r="AE10" s="66"/>
       <c r="AF10" s="66"/>
       <c r="AG10" s="66"/>
-      <c r="AH10" s="67"/>
-      <c r="AI10" s="67"/>
-      <c r="AJ10" s="67"/>
+      <c r="AH10" s="66"/>
+      <c r="AI10" s="66"/>
+      <c r="AJ10" s="66"/>
       <c r="AK10" s="25">
-        <f t="shared" si="0"/>
+        <f>SUMIF(E10:AJ10,"&lt;&gt;",$E$3:$AJ$3)</f>
         <v>0</v>
       </c>
     </row>
@@ -10887,7 +11019,7 @@
       <c r="A11" s="84">
         <v>8</v>
       </c>
-      <c r="B11" s="153" t="s">
+      <c r="B11" s="117" t="s">
         <v>14</v>
       </c>
       <c r="C11" s="22">
@@ -10921,15 +11053,15 @@
       <c r="AA11" s="81"/>
       <c r="AB11" s="81"/>
       <c r="AC11" s="81"/>
-      <c r="AD11" s="81"/>
+      <c r="AD11" s="82"/>
       <c r="AE11" s="82"/>
       <c r="AF11" s="82"/>
       <c r="AG11" s="82"/>
-      <c r="AH11" s="83"/>
-      <c r="AI11" s="83"/>
-      <c r="AJ11" s="83"/>
+      <c r="AH11" s="82"/>
+      <c r="AI11" s="82"/>
+      <c r="AJ11" s="82"/>
       <c r="AK11" s="94">
-        <f t="shared" si="0"/>
+        <f>SUMIF(E11:AJ11,"&lt;&gt;",$E$3:$AJ$3)</f>
         <v>0</v>
       </c>
     </row>
@@ -10937,7 +11069,7 @@
       <c r="A12" s="30">
         <v>9</v>
       </c>
-      <c r="B12" s="151" t="s">
+      <c r="B12" s="115" t="s">
         <v>15</v>
       </c>
       <c r="C12" s="22">
@@ -10971,15 +11103,15 @@
       <c r="AA12" s="65"/>
       <c r="AB12" s="65"/>
       <c r="AC12" s="65"/>
-      <c r="AD12" s="65"/>
+      <c r="AD12" s="66"/>
       <c r="AE12" s="66"/>
       <c r="AF12" s="66"/>
       <c r="AG12" s="66"/>
-      <c r="AH12" s="67"/>
-      <c r="AI12" s="67"/>
-      <c r="AJ12" s="67"/>
+      <c r="AH12" s="66"/>
+      <c r="AI12" s="66"/>
+      <c r="AJ12" s="66"/>
       <c r="AK12" s="25">
-        <f t="shared" si="0"/>
+        <f>SUMIF(E12:AJ12,"&lt;&gt;",$E$3:$AJ$3)</f>
         <v>0</v>
       </c>
     </row>
@@ -10987,7 +11119,7 @@
       <c r="A13" s="30">
         <v>10</v>
       </c>
-      <c r="B13" s="151" t="s">
+      <c r="B13" s="115" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="22">
@@ -11021,15 +11153,15 @@
       <c r="AA13" s="65"/>
       <c r="AB13" s="65"/>
       <c r="AC13" s="65"/>
-      <c r="AD13" s="65"/>
+      <c r="AD13" s="66"/>
       <c r="AE13" s="66"/>
       <c r="AF13" s="66"/>
       <c r="AG13" s="66"/>
-      <c r="AH13" s="67"/>
-      <c r="AI13" s="67"/>
-      <c r="AJ13" s="67"/>
+      <c r="AH13" s="66"/>
+      <c r="AI13" s="66"/>
+      <c r="AJ13" s="66"/>
       <c r="AK13" s="25">
-        <f t="shared" si="0"/>
+        <f>SUMIF(E13:AJ13,"&lt;&gt;",$E$3:$AJ$3)</f>
         <v>0</v>
       </c>
     </row>
@@ -11037,7 +11169,7 @@
       <c r="A14" s="30">
         <v>11</v>
       </c>
-      <c r="B14" s="151" t="s">
+      <c r="B14" s="115" t="s">
         <v>17</v>
       </c>
       <c r="C14" s="22">
@@ -11071,15 +11203,15 @@
       <c r="AA14" s="65"/>
       <c r="AB14" s="65"/>
       <c r="AC14" s="65"/>
-      <c r="AD14" s="65"/>
+      <c r="AD14" s="66"/>
       <c r="AE14" s="66"/>
       <c r="AF14" s="66"/>
       <c r="AG14" s="66"/>
-      <c r="AH14" s="67"/>
-      <c r="AI14" s="67"/>
-      <c r="AJ14" s="67"/>
+      <c r="AH14" s="66"/>
+      <c r="AI14" s="66"/>
+      <c r="AJ14" s="66"/>
       <c r="AK14" s="25">
-        <f t="shared" si="0"/>
+        <f>SUMIF(E14:AJ14,"&lt;&gt;",$E$3:$AJ$3)</f>
         <v>0</v>
       </c>
     </row>
@@ -11087,7 +11219,7 @@
       <c r="A15" s="30">
         <v>12</v>
       </c>
-      <c r="B15" s="151" t="s">
+      <c r="B15" s="115" t="s">
         <v>18</v>
       </c>
       <c r="C15" s="22">
@@ -11121,15 +11253,15 @@
       <c r="AA15" s="65"/>
       <c r="AB15" s="65"/>
       <c r="AC15" s="65"/>
-      <c r="AD15" s="65"/>
+      <c r="AD15" s="66"/>
       <c r="AE15" s="66"/>
       <c r="AF15" s="66"/>
       <c r="AG15" s="66"/>
-      <c r="AH15" s="67"/>
-      <c r="AI15" s="67"/>
-      <c r="AJ15" s="67"/>
+      <c r="AH15" s="66"/>
+      <c r="AI15" s="66"/>
+      <c r="AJ15" s="66"/>
       <c r="AK15" s="25">
-        <f t="shared" si="0"/>
+        <f>SUMIF(E15:AJ15,"&lt;&gt;",$E$3:$AJ$3)</f>
         <v>0</v>
       </c>
     </row>
@@ -11137,7 +11269,7 @@
       <c r="A16" s="30">
         <v>13</v>
       </c>
-      <c r="B16" s="151" t="s">
+      <c r="B16" s="115" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="22">
@@ -11171,234 +11303,234 @@
       <c r="AA16" s="74"/>
       <c r="AB16" s="74"/>
       <c r="AC16" s="74"/>
-      <c r="AD16" s="74"/>
+      <c r="AD16" s="75"/>
       <c r="AE16" s="75"/>
       <c r="AF16" s="75"/>
       <c r="AG16" s="75"/>
-      <c r="AH16" s="76"/>
-      <c r="AI16" s="76"/>
-      <c r="AJ16" s="76"/>
+      <c r="AH16" s="75"/>
+      <c r="AI16" s="75"/>
+      <c r="AJ16" s="75"/>
       <c r="AK16" s="25">
-        <f t="shared" si="0"/>
+        <f>SUMIF(E16:AJ16,"&lt;&gt;",$E$3:$AJ$3)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:37" ht="30" customHeight="1">
-      <c r="A17" s="127" t="s">
+      <c r="A17" s="148" t="s">
         <v>77</v>
       </c>
-      <c r="B17" s="128"/>
-      <c r="C17" s="128"/>
-      <c r="D17" s="129"/>
+      <c r="B17" s="149"/>
+      <c r="C17" s="149"/>
+      <c r="D17" s="150"/>
       <c r="E17" s="106">
-        <f>COUNTA(E4:E16)</f>
+        <f t="shared" ref="E17:AJ17" si="0">COUNTA(E4:E16)</f>
+        <v>1</v>
+      </c>
+      <c r="F17" s="106">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F17" s="106">
-        <f>COUNTA(F4:F16)</f>
+      <c r="G17" s="106">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H17" s="106">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G17" s="106">
-        <f>COUNTA(G4:G16)</f>
+      <c r="I17" s="106">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="J17" s="106">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K17" s="106">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H17" s="106">
-        <f>COUNTA(H4:H16)</f>
+      <c r="L17" s="63">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M17" s="63">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="N17" s="63">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I17" s="106">
-        <f>COUNTA(I4:I16)</f>
+      <c r="O17" s="63">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J17" s="106">
-        <f>COUNTA(J4:J16)</f>
+      <c r="P17" s="63">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K17" s="106">
-        <f>COUNTA(K4:K16)</f>
+      <c r="Q17" s="63">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L17" s="63">
-        <f>COUNTA(L4:L16)</f>
+      <c r="R17" s="29">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M17" s="63">
-        <f>COUNTA(M4:M16)</f>
+      <c r="S17" s="29">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N17" s="63">
-        <f>COUNTA(N4:N16)</f>
+      <c r="T17" s="29">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O17" s="63">
-        <f>COUNTA(O4:O16)</f>
+      <c r="U17" s="64">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P17" s="63">
-        <f>COUNTA(P4:P16)</f>
+      <c r="V17" s="64">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q17" s="63">
-        <f>COUNTA(Q4:Q16)</f>
+      <c r="W17" s="64">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R17" s="29">
-        <f>COUNTA(R4:R16)</f>
+      <c r="X17" s="64">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S17" s="29">
-        <f>COUNTA(S4:S16)</f>
+      <c r="Y17" s="64">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="T17" s="29">
-        <f>COUNTA(T4:T16)</f>
+      <c r="Z17" s="65">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AA17" s="65">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U17" s="64">
-        <f>COUNTA(U4:U16)</f>
+      <c r="AB17" s="65">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V17" s="64">
-        <f>COUNTA(V4:V16)</f>
+      <c r="AC17" s="65">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W17" s="64">
-        <f>COUNTA(W4:W16)</f>
+      <c r="AD17" s="66">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AE17" s="66">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AF17" s="66">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X17" s="64">
-        <f>COUNTA(X4:X16)</f>
+      <c r="AG17" s="66">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Y17" s="64">
-        <f>COUNTA(Y4:Y16)</f>
+      <c r="AH17" s="66">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Z17" s="65">
-        <f>COUNTA(Z4:Z16)</f>
+      <c r="AI17" s="66">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AA17" s="65">
-        <f>COUNTA(AA4:AA16)</f>
+      <c r="AJ17" s="66">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AB17" s="65">
-        <f>COUNTA(AB4:AB16)</f>
-        <v>0</v>
-      </c>
-      <c r="AC17" s="65">
-        <f>COUNTA(AC4:AC16)</f>
-        <v>0</v>
-      </c>
-      <c r="AD17" s="65">
-        <f>COUNTA(AD4:AD16)</f>
-        <v>0</v>
-      </c>
-      <c r="AE17" s="66">
-        <f>COUNTA(AE4:AE16)</f>
-        <v>0</v>
-      </c>
-      <c r="AF17" s="66">
-        <f>COUNTA(AF4:AF16)</f>
-        <v>0</v>
-      </c>
-      <c r="AG17" s="66">
-        <f>COUNTA(AG4:AG16)</f>
-        <v>0</v>
-      </c>
-      <c r="AH17" s="67">
-        <f>COUNTA(AH4:AH16)</f>
-        <v>0</v>
-      </c>
-      <c r="AI17" s="67">
-        <f>COUNTA(AI4:AI16)</f>
-        <v>0</v>
-      </c>
-      <c r="AJ17" s="67">
-        <f>COUNTA(AJ4:AJ16)</f>
-        <v>0</v>
-      </c>
       <c r="AK17" s="25"/>
     </row>
     <row r="18" spans="1:37" ht="30" customHeight="1">
-      <c r="AG18" s="124" t="s">
+      <c r="AG18" s="145" t="s">
         <v>78</v>
       </c>
-      <c r="AH18" s="125"/>
-      <c r="AI18" s="125"/>
-      <c r="AJ18" s="126"/>
+      <c r="AH18" s="146"/>
+      <c r="AI18" s="146"/>
+      <c r="AJ18" s="147"/>
       <c r="AK18" s="107">
         <f>ROUND(AVERAGE(AK4:AK16),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:37" ht="30" customHeight="1">
-      <c r="AG19" s="124" t="s">
+      <c r="AG19" s="145" t="s">
         <v>79</v>
       </c>
-      <c r="AH19" s="125"/>
-      <c r="AI19" s="125"/>
-      <c r="AJ19" s="126"/>
+      <c r="AH19" s="146"/>
+      <c r="AI19" s="146"/>
+      <c r="AJ19" s="147"/>
       <c r="AK19" s="107">
         <f>MAX(AK4:AK16)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:37" ht="30" customHeight="1">
-      <c r="AG20" s="124" t="s">
+      <c r="AG20" s="145" t="s">
         <v>80</v>
       </c>
-      <c r="AH20" s="125"/>
-      <c r="AI20" s="125"/>
-      <c r="AJ20" s="126"/>
+      <c r="AH20" s="146"/>
+      <c r="AI20" s="146"/>
+      <c r="AJ20" s="147"/>
       <c r="AK20" s="107">
         <f>MIN(AK4:AK16)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:37" ht="30" customHeight="1">
-      <c r="AG21" s="124" t="s">
+      <c r="AG21" s="145" t="s">
         <v>81</v>
       </c>
-      <c r="AH21" s="125"/>
-      <c r="AI21" s="125"/>
-      <c r="AJ21" s="126"/>
+      <c r="AH21" s="146"/>
+      <c r="AI21" s="146"/>
+      <c r="AJ21" s="147"/>
       <c r="AK21" s="107">
         <f>COUNTIF(AK4:AK16, "&gt;"&amp;AK18)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:37" ht="30" customHeight="1">
-      <c r="AG22" s="124" t="s">
+      <c r="AG22" s="145" t="s">
         <v>82</v>
       </c>
-      <c r="AH22" s="125"/>
-      <c r="AI22" s="125"/>
-      <c r="AJ22" s="126"/>
+      <c r="AH22" s="146"/>
+      <c r="AI22" s="146"/>
+      <c r="AJ22" s="147"/>
       <c r="AK22" s="107">
         <f>COUNTIF(AK4:AK16, "&lt;"&amp;AK18)</f>
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:37" ht="30" customHeight="1">
-      <c r="AG23" s="124" t="s">
+      <c r="AG23" s="145" t="s">
         <v>83</v>
       </c>
-      <c r="AH23" s="125"/>
-      <c r="AI23" s="125"/>
-      <c r="AJ23" s="126"/>
+      <c r="AH23" s="146"/>
+      <c r="AI23" s="146"/>
+      <c r="AJ23" s="147"/>
       <c r="AK23" s="107">
         <f>COUNTIF(AK4:AK16, "&gt;"&amp;20)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:37" ht="30" customHeight="1">
-      <c r="AG24" s="124" t="s">
+      <c r="AG24" s="145" t="s">
         <v>84</v>
       </c>
-      <c r="AH24" s="125"/>
-      <c r="AI24" s="125"/>
-      <c r="AJ24" s="126"/>
+      <c r="AH24" s="146"/>
+      <c r="AI24" s="146"/>
+      <c r="AJ24" s="147"/>
       <c r="AK24" s="107">
         <f>COUNTIF(AK4:AK16, "&lt;"&amp;20)</f>
         <v>13</v>
@@ -11408,53 +11540,27 @@
     <row r="26" spans="1:37" ht="30" customHeight="1"/>
     <row r="27" spans="1:37" ht="30" customHeight="1"/>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="AG20:AJ20"/>
-    <mergeCell ref="AG21:AJ21"/>
-    <mergeCell ref="AG22:AJ22"/>
-    <mergeCell ref="AG23:AJ23"/>
-    <mergeCell ref="AG24:AJ24"/>
-    <mergeCell ref="AE1:AG1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="AK1:AK3"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="AG18:AJ18"/>
+  <mergeCells count="16">
     <mergeCell ref="AG19:AJ19"/>
     <mergeCell ref="A1:C2"/>
     <mergeCell ref="E1:K1"/>
     <mergeCell ref="L1:Q1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:Y1"/>
-    <mergeCell ref="Z1:AD1"/>
+    <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="AD1:AJ1"/>
+    <mergeCell ref="AK1:AK3"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="AG18:AJ18"/>
+    <mergeCell ref="AG20:AJ20"/>
+    <mergeCell ref="AG21:AJ21"/>
+    <mergeCell ref="AG22:AJ22"/>
+    <mergeCell ref="AG23:AJ23"/>
+    <mergeCell ref="AG24:AJ24"/>
   </mergeCells>
-  <conditionalFormatting sqref="L17:Q17 E4:AJ16">
-    <cfRule type="expression" dxfId="5" priority="6">
+  <conditionalFormatting sqref="E4:AJ16 L17:AJ17 AH4:AJ17">
+    <cfRule type="expression" dxfId="4" priority="7">
       <formula>E4="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R17:T17">
-    <cfRule type="expression" dxfId="4" priority="5">
-      <formula>R17="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U17:Y17">
-    <cfRule type="expression" dxfId="3" priority="4">
-      <formula>U17="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z17:AD17">
-    <cfRule type="expression" dxfId="2" priority="3">
-      <formula>Z17="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE17:AG17">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>AE17="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AH17:AJ17">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>AH17="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Другое/2026/study_chart.xlsx
+++ b/Другое/2026/study_chart.xlsx
@@ -953,7 +953,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="101">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -2525,6 +2525,12 @@
     <xf numFmtId="0" fontId="1" fillId="26" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="27" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2552,6 +2558,24 @@
     <xf numFmtId="0" fontId="19" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2606,24 +2630,6 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2632,12 +2638,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2661,49 +2661,7 @@
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFB6EA86"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFB6EA86"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFB6EA86"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFB6EA86"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFB6EA86"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFB6EA86"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="18">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -3158,18 +3116,18 @@
   </cols>
   <sheetData>
     <row r="9" spans="8:17" ht="45" customHeight="1">
-      <c r="H9" s="118" t="s">
+      <c r="H9" s="120" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="119"/>
-      <c r="J9" s="119"/>
-      <c r="K9" s="119"/>
-      <c r="L9" s="119"/>
-      <c r="M9" s="119"/>
-      <c r="N9" s="119"/>
-      <c r="O9" s="119"/>
-      <c r="P9" s="119"/>
-      <c r="Q9" s="120"/>
+      <c r="I9" s="121"/>
+      <c r="J9" s="121"/>
+      <c r="K9" s="121"/>
+      <c r="L9" s="121"/>
+      <c r="M9" s="121"/>
+      <c r="N9" s="121"/>
+      <c r="O9" s="121"/>
+      <c r="P9" s="121"/>
+      <c r="Q9" s="122"/>
     </row>
     <row r="10" spans="8:17" ht="30" customHeight="1">
       <c r="H10" s="55" t="s">
@@ -3438,11 +3396,11 @@
       <c r="Q21" s="60"/>
     </row>
     <row r="22" spans="8:17" ht="15.75">
-      <c r="H22" s="121" t="s">
+      <c r="H22" s="123" t="s">
         <v>19</v>
       </c>
-      <c r="I22" s="122"/>
-      <c r="J22" s="123"/>
+      <c r="I22" s="124"/>
+      <c r="J22" s="125"/>
       <c r="K22" s="61">
         <f>COUNTA(K11:K21)</f>
         <v>6</v>
@@ -3478,12 +3436,12 @@
     <mergeCell ref="H22:J22"/>
   </mergeCells>
   <conditionalFormatting sqref="K22:Q22">
-    <cfRule type="expression" dxfId="23" priority="1">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>Q22="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11:Q21">
-    <cfRule type="expression" dxfId="22" priority="2">
+    <cfRule type="expression" dxfId="16" priority="2">
       <formula>Q11="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3519,39 +3477,39 @@
   </cols>
   <sheetData>
     <row r="9" spans="8:38" ht="45" customHeight="1">
-      <c r="H9" s="124" t="s">
+      <c r="H9" s="126" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="125"/>
-      <c r="J9" s="125"/>
-      <c r="K9" s="125"/>
-      <c r="L9" s="125"/>
-      <c r="M9" s="125"/>
-      <c r="N9" s="125"/>
-      <c r="O9" s="125"/>
-      <c r="P9" s="125"/>
-      <c r="Q9" s="125"/>
-      <c r="R9" s="125"/>
-      <c r="S9" s="125"/>
-      <c r="T9" s="125"/>
-      <c r="U9" s="125"/>
-      <c r="V9" s="125"/>
-      <c r="W9" s="125"/>
-      <c r="X9" s="125"/>
-      <c r="Y9" s="125"/>
-      <c r="Z9" s="125"/>
-      <c r="AA9" s="125"/>
-      <c r="AB9" s="125"/>
-      <c r="AC9" s="125"/>
-      <c r="AD9" s="125"/>
-      <c r="AE9" s="125"/>
-      <c r="AF9" s="125"/>
-      <c r="AG9" s="125"/>
-      <c r="AH9" s="125"/>
-      <c r="AI9" s="125"/>
-      <c r="AJ9" s="125"/>
-      <c r="AK9" s="125"/>
-      <c r="AL9" s="125"/>
+      <c r="I9" s="127"/>
+      <c r="J9" s="127"/>
+      <c r="K9" s="127"/>
+      <c r="L9" s="127"/>
+      <c r="M9" s="127"/>
+      <c r="N9" s="127"/>
+      <c r="O9" s="127"/>
+      <c r="P9" s="127"/>
+      <c r="Q9" s="127"/>
+      <c r="R9" s="127"/>
+      <c r="S9" s="127"/>
+      <c r="T9" s="127"/>
+      <c r="U9" s="127"/>
+      <c r="V9" s="127"/>
+      <c r="W9" s="127"/>
+      <c r="X9" s="127"/>
+      <c r="Y9" s="127"/>
+      <c r="Z9" s="127"/>
+      <c r="AA9" s="127"/>
+      <c r="AB9" s="127"/>
+      <c r="AC9" s="127"/>
+      <c r="AD9" s="127"/>
+      <c r="AE9" s="127"/>
+      <c r="AF9" s="127"/>
+      <c r="AG9" s="127"/>
+      <c r="AH9" s="127"/>
+      <c r="AI9" s="127"/>
+      <c r="AJ9" s="127"/>
+      <c r="AK9" s="127"/>
+      <c r="AL9" s="127"/>
     </row>
     <row r="10" spans="8:38" ht="30" customHeight="1">
       <c r="H10" s="32" t="s">
@@ -5231,11 +5189,11 @@
       </c>
     </row>
     <row r="42" spans="8:38" ht="15.75">
-      <c r="H42" s="126" t="s">
+      <c r="H42" s="128" t="s">
         <v>19</v>
       </c>
-      <c r="I42" s="126"/>
-      <c r="J42" s="126"/>
+      <c r="I42" s="128"/>
+      <c r="J42" s="128"/>
       <c r="K42" s="32">
         <f>COUNTA(K11:K41)</f>
         <v>6</v>
@@ -5349,12 +5307,12 @@
     <mergeCell ref="H42:J42"/>
   </mergeCells>
   <conditionalFormatting sqref="AL42">
-    <cfRule type="expression" dxfId="21" priority="10">
+    <cfRule type="expression" dxfId="15" priority="10">
       <formula>AU42="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11:AK41">
-    <cfRule type="expression" dxfId="20" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>K11&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5400,66 +5358,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="132"/>
-      <c r="B1" s="133"/>
-      <c r="C1" s="134"/>
+      <c r="A1" s="140"/>
+      <c r="B1" s="141"/>
+      <c r="C1" s="142"/>
       <c r="D1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="138" t="s">
+      <c r="E1" s="146" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
-      <c r="H1" s="138"/>
-      <c r="I1" s="138"/>
-      <c r="J1" s="138"/>
-      <c r="K1" s="138"/>
-      <c r="L1" s="139" t="s">
+      <c r="F1" s="146"/>
+      <c r="G1" s="146"/>
+      <c r="H1" s="146"/>
+      <c r="I1" s="146"/>
+      <c r="J1" s="146"/>
+      <c r="K1" s="146"/>
+      <c r="L1" s="147" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="139"/>
-      <c r="N1" s="139"/>
-      <c r="O1" s="139"/>
-      <c r="P1" s="139"/>
-      <c r="Q1" s="139"/>
-      <c r="R1" s="139"/>
-      <c r="S1" s="140" t="s">
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="147"/>
+      <c r="R1" s="147"/>
+      <c r="S1" s="148" t="s">
         <v>39</v>
       </c>
-      <c r="T1" s="140"/>
-      <c r="U1" s="141" t="s">
+      <c r="T1" s="148"/>
+      <c r="U1" s="149" t="s">
         <v>40</v>
       </c>
-      <c r="V1" s="142"/>
-      <c r="W1" s="142"/>
-      <c r="X1" s="142"/>
-      <c r="Y1" s="143"/>
-      <c r="Z1" s="144" t="s">
+      <c r="V1" s="150"/>
+      <c r="W1" s="150"/>
+      <c r="X1" s="150"/>
+      <c r="Y1" s="151"/>
+      <c r="Z1" s="152" t="s">
         <v>41</v>
       </c>
-      <c r="AA1" s="144"/>
-      <c r="AB1" s="144"/>
-      <c r="AC1" s="144"/>
-      <c r="AD1" s="144"/>
-      <c r="AE1" s="127" t="s">
+      <c r="AA1" s="152"/>
+      <c r="AB1" s="152"/>
+      <c r="AC1" s="152"/>
+      <c r="AD1" s="152"/>
+      <c r="AE1" s="135" t="s">
         <v>42</v>
       </c>
-      <c r="AF1" s="127"/>
-      <c r="AG1" s="127"/>
-      <c r="AH1" s="128" t="s">
+      <c r="AF1" s="135"/>
+      <c r="AG1" s="135"/>
+      <c r="AH1" s="136" t="s">
         <v>43</v>
       </c>
-      <c r="AI1" s="128"/>
-      <c r="AJ1" s="128"/>
-      <c r="AK1" s="129" t="s">
+      <c r="AI1" s="136"/>
+      <c r="AJ1" s="136"/>
+      <c r="AK1" s="137" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:37" s="2" customFormat="1" ht="30" customHeight="1">
-      <c r="A2" s="135"/>
-      <c r="B2" s="136"/>
-      <c r="C2" s="137"/>
+      <c r="A2" s="143"/>
+      <c r="B2" s="144"/>
+      <c r="C2" s="145"/>
       <c r="D2" s="5" t="s">
         <v>44</v>
       </c>
@@ -5553,7 +5511,7 @@
       <c r="AH2" s="12"/>
       <c r="AI2" s="12"/>
       <c r="AJ2" s="12"/>
-      <c r="AK2" s="130"/>
+      <c r="AK2" s="138"/>
     </row>
     <row r="3" spans="1:37">
       <c r="A3" s="13" t="s">
@@ -5664,7 +5622,7 @@
       <c r="AJ3" s="20">
         <v>2</v>
       </c>
-      <c r="AK3" s="131"/>
+      <c r="AK3" s="139"/>
     </row>
     <row r="4" spans="1:37">
       <c r="A4" s="21">
@@ -7715,12 +7673,12 @@
       </c>
     </row>
     <row r="35" spans="1:37" ht="30" customHeight="1">
-      <c r="A35" s="148" t="s">
+      <c r="A35" s="132" t="s">
         <v>77</v>
       </c>
-      <c r="B35" s="149"/>
-      <c r="C35" s="149"/>
-      <c r="D35" s="150"/>
+      <c r="B35" s="133"/>
+      <c r="C35" s="133"/>
+      <c r="D35" s="134"/>
       <c r="E35" s="106">
         <f>COUNTA(E4:E34)</f>
         <v>14</v>
@@ -7852,84 +7810,84 @@
       <c r="AK35" s="25"/>
     </row>
     <row r="36" spans="1:37" ht="30" customHeight="1">
-      <c r="AG36" s="145" t="s">
+      <c r="AG36" s="129" t="s">
         <v>78</v>
       </c>
-      <c r="AH36" s="146"/>
-      <c r="AI36" s="146"/>
-      <c r="AJ36" s="147"/>
+      <c r="AH36" s="130"/>
+      <c r="AI36" s="130"/>
+      <c r="AJ36" s="131"/>
       <c r="AK36" s="107">
         <f>ROUND(AVERAGE(AK4:AK34),0)</f>
         <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:37" ht="30" customHeight="1">
-      <c r="AG37" s="145" t="s">
+      <c r="AG37" s="129" t="s">
         <v>79</v>
       </c>
-      <c r="AH37" s="146"/>
-      <c r="AI37" s="146"/>
-      <c r="AJ37" s="147"/>
+      <c r="AH37" s="130"/>
+      <c r="AI37" s="130"/>
+      <c r="AJ37" s="131"/>
       <c r="AK37" s="107">
         <f>MAX(AK4:AK34)</f>
         <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:37" ht="30" customHeight="1">
-      <c r="AG38" s="145" t="s">
+      <c r="AG38" s="129" t="s">
         <v>80</v>
       </c>
-      <c r="AH38" s="146"/>
-      <c r="AI38" s="146"/>
-      <c r="AJ38" s="147"/>
+      <c r="AH38" s="130"/>
+      <c r="AI38" s="130"/>
+      <c r="AJ38" s="131"/>
       <c r="AK38" s="107">
         <f>MIN(AK4:AK34)</f>
         <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:37" ht="30" customHeight="1">
-      <c r="AG39" s="145" t="s">
+      <c r="AG39" s="129" t="s">
         <v>81</v>
       </c>
-      <c r="AH39" s="146"/>
-      <c r="AI39" s="146"/>
-      <c r="AJ39" s="147"/>
+      <c r="AH39" s="130"/>
+      <c r="AI39" s="130"/>
+      <c r="AJ39" s="131"/>
       <c r="AK39" s="107">
         <f>COUNTIF(AK4:AK34, "&gt;"&amp;AK36)</f>
         <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:37" ht="30" customHeight="1">
-      <c r="AG40" s="145" t="s">
+      <c r="AG40" s="129" t="s">
         <v>82</v>
       </c>
-      <c r="AH40" s="146"/>
-      <c r="AI40" s="146"/>
-      <c r="AJ40" s="147"/>
+      <c r="AH40" s="130"/>
+      <c r="AI40" s="130"/>
+      <c r="AJ40" s="131"/>
       <c r="AK40" s="107">
         <f>COUNTIF(AK4:AK34, "&lt;"&amp;AK36)</f>
         <v>18</v>
       </c>
     </row>
     <row r="41" spans="1:37" ht="30" customHeight="1">
-      <c r="AG41" s="145" t="s">
+      <c r="AG41" s="129" t="s">
         <v>83</v>
       </c>
-      <c r="AH41" s="146"/>
-      <c r="AI41" s="146"/>
-      <c r="AJ41" s="147"/>
+      <c r="AH41" s="130"/>
+      <c r="AI41" s="130"/>
+      <c r="AJ41" s="131"/>
       <c r="AK41" s="107">
         <f>COUNTIF(AK4:AK34, "&gt;"&amp;20)</f>
         <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:37" ht="30" customHeight="1">
-      <c r="AG42" s="145" t="s">
+      <c r="AG42" s="129" t="s">
         <v>84</v>
       </c>
-      <c r="AH42" s="146"/>
-      <c r="AI42" s="146"/>
-      <c r="AJ42" s="147"/>
+      <c r="AH42" s="130"/>
+      <c r="AI42" s="130"/>
+      <c r="AJ42" s="131"/>
       <c r="AK42" s="107">
         <f>COUNTIF(AK4:AK34, "&lt;"&amp;20)</f>
         <v>21</v>
@@ -7940,14 +7898,6 @@
     <row r="45" spans="1:37" ht="30" customHeight="1"/>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="AG40:AJ40"/>
-    <mergeCell ref="AG41:AJ41"/>
-    <mergeCell ref="AG42:AJ42"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="AG36:AJ36"/>
-    <mergeCell ref="AG37:AJ37"/>
-    <mergeCell ref="AG38:AJ38"/>
-    <mergeCell ref="AG39:AJ39"/>
     <mergeCell ref="AE1:AG1"/>
     <mergeCell ref="AH1:AJ1"/>
     <mergeCell ref="AK1:AK3"/>
@@ -7957,39 +7907,47 @@
     <mergeCell ref="S1:T1"/>
     <mergeCell ref="U1:Y1"/>
     <mergeCell ref="Z1:AD1"/>
+    <mergeCell ref="AG40:AJ40"/>
+    <mergeCell ref="AG41:AJ41"/>
+    <mergeCell ref="AG42:AJ42"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="AG36:AJ36"/>
+    <mergeCell ref="AG37:AJ37"/>
+    <mergeCell ref="AG38:AJ38"/>
+    <mergeCell ref="AG39:AJ39"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:AJ34">
-    <cfRule type="expression" dxfId="19" priority="7">
+    <cfRule type="expression" dxfId="13" priority="7">
       <formula>E4="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L35:R35">
-    <cfRule type="expression" dxfId="18" priority="6">
+    <cfRule type="expression" dxfId="12" priority="6">
       <formula>L35="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S35:T35">
-    <cfRule type="expression" dxfId="17" priority="5">
+    <cfRule type="expression" dxfId="11" priority="5">
       <formula>S35="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U35:Y35">
-    <cfRule type="expression" dxfId="16" priority="4">
+    <cfRule type="expression" dxfId="10" priority="4">
       <formula>U35="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z35:AD35">
-    <cfRule type="expression" dxfId="15" priority="3">
+    <cfRule type="expression" dxfId="9" priority="3">
       <formula>Z35="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE35:AG35">
-    <cfRule type="expression" dxfId="14" priority="2">
+    <cfRule type="expression" dxfId="8" priority="2">
       <formula>AE35="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH35:AJ35">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>AH35="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8034,66 +7992,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="132"/>
-      <c r="B1" s="133"/>
-      <c r="C1" s="134"/>
+      <c r="A1" s="140"/>
+      <c r="B1" s="141"/>
+      <c r="C1" s="142"/>
       <c r="D1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="138" t="s">
+      <c r="E1" s="146" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
-      <c r="H1" s="138"/>
-      <c r="I1" s="138"/>
-      <c r="J1" s="138"/>
-      <c r="K1" s="138"/>
-      <c r="L1" s="139" t="s">
+      <c r="F1" s="146"/>
+      <c r="G1" s="146"/>
+      <c r="H1" s="146"/>
+      <c r="I1" s="146"/>
+      <c r="J1" s="146"/>
+      <c r="K1" s="146"/>
+      <c r="L1" s="147" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="139"/>
-      <c r="N1" s="139"/>
-      <c r="O1" s="139"/>
-      <c r="P1" s="139"/>
-      <c r="Q1" s="139"/>
-      <c r="R1" s="151" t="s">
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="147"/>
+      <c r="R1" s="153" t="s">
         <v>39</v>
       </c>
-      <c r="S1" s="152"/>
-      <c r="T1" s="153"/>
-      <c r="U1" s="141" t="s">
+      <c r="S1" s="154"/>
+      <c r="T1" s="155"/>
+      <c r="U1" s="149" t="s">
         <v>40</v>
       </c>
-      <c r="V1" s="142"/>
-      <c r="W1" s="142"/>
-      <c r="X1" s="142"/>
-      <c r="Y1" s="143"/>
-      <c r="Z1" s="144" t="s">
+      <c r="V1" s="150"/>
+      <c r="W1" s="150"/>
+      <c r="X1" s="150"/>
+      <c r="Y1" s="151"/>
+      <c r="Z1" s="152" t="s">
         <v>41</v>
       </c>
-      <c r="AA1" s="144"/>
-      <c r="AB1" s="144"/>
-      <c r="AC1" s="144"/>
-      <c r="AD1" s="144"/>
-      <c r="AE1" s="127" t="s">
+      <c r="AA1" s="152"/>
+      <c r="AB1" s="152"/>
+      <c r="AC1" s="152"/>
+      <c r="AD1" s="152"/>
+      <c r="AE1" s="135" t="s">
         <v>42</v>
       </c>
-      <c r="AF1" s="127"/>
-      <c r="AG1" s="127"/>
-      <c r="AH1" s="128" t="s">
+      <c r="AF1" s="135"/>
+      <c r="AG1" s="135"/>
+      <c r="AH1" s="136" t="s">
         <v>43</v>
       </c>
-      <c r="AI1" s="128"/>
-      <c r="AJ1" s="128"/>
-      <c r="AK1" s="129" t="s">
+      <c r="AI1" s="136"/>
+      <c r="AJ1" s="136"/>
+      <c r="AK1" s="137" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:37" s="2" customFormat="1" ht="45" customHeight="1">
-      <c r="A2" s="135"/>
-      <c r="B2" s="136"/>
-      <c r="C2" s="137"/>
+      <c r="A2" s="143"/>
+      <c r="B2" s="144"/>
+      <c r="C2" s="145"/>
       <c r="D2" s="5" t="s">
         <v>44</v>
       </c>
@@ -8189,7 +8147,7 @@
       </c>
       <c r="AI2" s="12"/>
       <c r="AJ2" s="12"/>
-      <c r="AK2" s="130"/>
+      <c r="AK2" s="138"/>
     </row>
     <row r="3" spans="1:37">
       <c r="A3" s="13" t="s">
@@ -8300,7 +8258,7 @@
       <c r="AJ3" s="20">
         <v>1</v>
       </c>
-      <c r="AK3" s="131"/>
+      <c r="AK3" s="139"/>
     </row>
     <row r="4" spans="1:37">
       <c r="A4" s="30">
@@ -10057,12 +10015,12 @@
       </c>
     </row>
     <row r="34" spans="1:37" ht="30" customHeight="1">
-      <c r="A34" s="148" t="s">
+      <c r="A34" s="132" t="s">
         <v>77</v>
       </c>
-      <c r="B34" s="149"/>
-      <c r="C34" s="149"/>
-      <c r="D34" s="150"/>
+      <c r="B34" s="133"/>
+      <c r="C34" s="133"/>
+      <c r="D34" s="134"/>
       <c r="E34" s="106">
         <f t="shared" ref="E34:AJ34" si="1">COUNTA(E4:E33)</f>
         <v>2</v>
@@ -10194,84 +10152,84 @@
       <c r="AK34" s="25"/>
     </row>
     <row r="35" spans="1:37" ht="30" customHeight="1">
-      <c r="AG35" s="145" t="s">
+      <c r="AG35" s="129" t="s">
         <v>78</v>
       </c>
-      <c r="AH35" s="146"/>
-      <c r="AI35" s="146"/>
-      <c r="AJ35" s="147"/>
+      <c r="AH35" s="130"/>
+      <c r="AI35" s="130"/>
+      <c r="AJ35" s="131"/>
       <c r="AK35" s="107">
         <f>ROUND(AVERAGE(AK4:AK33),0)</f>
         <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:37" ht="30" customHeight="1">
-      <c r="AG36" s="145" t="s">
+      <c r="AG36" s="129" t="s">
         <v>79</v>
       </c>
-      <c r="AH36" s="146"/>
-      <c r="AI36" s="146"/>
-      <c r="AJ36" s="147"/>
+      <c r="AH36" s="130"/>
+      <c r="AI36" s="130"/>
+      <c r="AJ36" s="131"/>
       <c r="AK36" s="107">
         <f>MAX(AK4:AK33)</f>
         <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:37" ht="30" customHeight="1">
-      <c r="AG37" s="145" t="s">
+      <c r="AG37" s="129" t="s">
         <v>80</v>
       </c>
-      <c r="AH37" s="146"/>
-      <c r="AI37" s="146"/>
-      <c r="AJ37" s="147"/>
+      <c r="AH37" s="130"/>
+      <c r="AI37" s="130"/>
+      <c r="AJ37" s="131"/>
       <c r="AK37" s="107">
         <f>MIN(AK4:AK33)</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:37" ht="30" customHeight="1">
-      <c r="AG38" s="145" t="s">
+      <c r="AG38" s="129" t="s">
         <v>81</v>
       </c>
-      <c r="AH38" s="146"/>
-      <c r="AI38" s="146"/>
-      <c r="AJ38" s="147"/>
+      <c r="AH38" s="130"/>
+      <c r="AI38" s="130"/>
+      <c r="AJ38" s="131"/>
       <c r="AK38" s="107">
         <f>COUNTIF(AK4:AK33, "&gt;"&amp;AK35)</f>
         <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:37" ht="30" customHeight="1">
-      <c r="AG39" s="145" t="s">
+      <c r="AG39" s="129" t="s">
         <v>82</v>
       </c>
-      <c r="AH39" s="146"/>
-      <c r="AI39" s="146"/>
-      <c r="AJ39" s="147"/>
+      <c r="AH39" s="130"/>
+      <c r="AI39" s="130"/>
+      <c r="AJ39" s="131"/>
       <c r="AK39" s="107">
         <f>COUNTIF(AK4:AK33, "&lt;"&amp;AK35)</f>
         <v>14</v>
       </c>
     </row>
     <row r="40" spans="1:37" ht="30" customHeight="1">
-      <c r="AG40" s="145" t="s">
+      <c r="AG40" s="129" t="s">
         <v>83</v>
       </c>
-      <c r="AH40" s="146"/>
-      <c r="AI40" s="146"/>
-      <c r="AJ40" s="147"/>
+      <c r="AH40" s="130"/>
+      <c r="AI40" s="130"/>
+      <c r="AJ40" s="131"/>
       <c r="AK40" s="107">
         <f>COUNTIF(AK4:AK33, "&gt;"&amp;20)</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:37" ht="30" customHeight="1">
-      <c r="AG41" s="145" t="s">
+      <c r="AG41" s="129" t="s">
         <v>84</v>
       </c>
-      <c r="AH41" s="146"/>
-      <c r="AI41" s="146"/>
-      <c r="AJ41" s="147"/>
+      <c r="AH41" s="130"/>
+      <c r="AI41" s="130"/>
+      <c r="AJ41" s="131"/>
       <c r="AK41" s="107">
         <f>COUNTIF(AK4:AK33, "&lt;"&amp;20)</f>
         <v>30</v>
@@ -10282,51 +10240,51 @@
     <row r="44" spans="1:37" ht="30" customHeight="1"/>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="AE1:AG1"/>
+    <mergeCell ref="AH1:AJ1"/>
+    <mergeCell ref="AG40:AJ40"/>
+    <mergeCell ref="AG41:AJ41"/>
+    <mergeCell ref="AK1:AK3"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="AG37:AJ37"/>
+    <mergeCell ref="AG38:AJ38"/>
+    <mergeCell ref="AG39:AJ39"/>
+    <mergeCell ref="AG35:AJ35"/>
+    <mergeCell ref="AG36:AJ36"/>
     <mergeCell ref="A1:C2"/>
     <mergeCell ref="E1:K1"/>
     <mergeCell ref="L1:Q1"/>
     <mergeCell ref="U1:Y1"/>
     <mergeCell ref="Z1:AD1"/>
     <mergeCell ref="R1:T1"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="AG37:AJ37"/>
-    <mergeCell ref="AG38:AJ38"/>
-    <mergeCell ref="AG39:AJ39"/>
-    <mergeCell ref="AG35:AJ35"/>
-    <mergeCell ref="AG36:AJ36"/>
-    <mergeCell ref="AE1:AG1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="AG40:AJ40"/>
-    <mergeCell ref="AG41:AJ41"/>
-    <mergeCell ref="AK1:AK3"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:AJ33 L34:Q34">
-    <cfRule type="expression" dxfId="12" priority="7">
+    <cfRule type="expression" dxfId="6" priority="7">
       <formula>E4="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R34:T34">
-    <cfRule type="expression" dxfId="11" priority="5">
+    <cfRule type="expression" dxfId="5" priority="5">
       <formula>R34="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U34:Y34">
-    <cfRule type="expression" dxfId="10" priority="4">
+    <cfRule type="expression" dxfId="4" priority="4">
       <formula>U34="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z34:AD34">
-    <cfRule type="expression" dxfId="9" priority="3">
+    <cfRule type="expression" dxfId="3" priority="3">
       <formula>Z34="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE34:AG34">
-    <cfRule type="expression" dxfId="8" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>AE34="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH34:AJ34">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>AH34="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10371,47 +10329,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="132"/>
-      <c r="B1" s="133"/>
-      <c r="C1" s="134"/>
+      <c r="A1" s="140"/>
+      <c r="B1" s="141"/>
+      <c r="C1" s="142"/>
       <c r="D1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="138" t="s">
+      <c r="E1" s="146" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
-      <c r="H1" s="138"/>
-      <c r="I1" s="138"/>
-      <c r="J1" s="138"/>
-      <c r="K1" s="138"/>
-      <c r="L1" s="139" t="s">
+      <c r="F1" s="146"/>
+      <c r="G1" s="146"/>
+      <c r="H1" s="146"/>
+      <c r="I1" s="146"/>
+      <c r="J1" s="146"/>
+      <c r="K1" s="146"/>
+      <c r="L1" s="147" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="139"/>
-      <c r="N1" s="139"/>
-      <c r="O1" s="139"/>
-      <c r="P1" s="139"/>
-      <c r="Q1" s="139"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="147"/>
       <c r="R1" s="156" t="s">
         <v>39</v>
       </c>
       <c r="S1" s="157"/>
       <c r="T1" s="158"/>
-      <c r="U1" s="141" t="s">
+      <c r="U1" s="149" t="s">
         <v>40</v>
       </c>
-      <c r="V1" s="142"/>
-      <c r="W1" s="142"/>
-      <c r="X1" s="142"/>
-      <c r="Y1" s="143"/>
-      <c r="Z1" s="144" t="s">
+      <c r="V1" s="150"/>
+      <c r="W1" s="150"/>
+      <c r="X1" s="150"/>
+      <c r="Y1" s="151"/>
+      <c r="Z1" s="152" t="s">
         <v>41</v>
       </c>
-      <c r="AA1" s="144"/>
-      <c r="AB1" s="144"/>
-      <c r="AC1" s="144"/>
+      <c r="AA1" s="152"/>
+      <c r="AB1" s="152"/>
+      <c r="AC1" s="152"/>
       <c r="AD1" s="159" t="s">
         <v>93</v>
       </c>
@@ -10421,14 +10379,14 @@
       <c r="AH1" s="160"/>
       <c r="AI1" s="160"/>
       <c r="AJ1" s="161"/>
-      <c r="AK1" s="129" t="s">
+      <c r="AK1" s="137" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:37" s="2" customFormat="1" ht="70.5" customHeight="1">
-      <c r="A2" s="135"/>
-      <c r="B2" s="136"/>
-      <c r="C2" s="137"/>
+      <c r="A2" s="143"/>
+      <c r="B2" s="144"/>
+      <c r="C2" s="145"/>
       <c r="D2" s="5" t="s">
         <v>44</v>
       </c>
@@ -10471,13 +10429,13 @@
       <c r="Q2" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="R2" s="155" t="s">
+      <c r="R2" s="119" t="s">
         <v>52</v>
       </c>
-      <c r="S2" s="154" t="s">
+      <c r="S2" s="118" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="154" t="s">
+      <c r="T2" s="118" t="s">
         <v>95</v>
       </c>
       <c r="U2" s="9" t="s">
@@ -10528,7 +10486,7 @@
       <c r="AJ2" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="AK2" s="130"/>
+      <c r="AK2" s="138"/>
     </row>
     <row r="3" spans="1:37">
       <c r="A3" s="13" t="s">
@@ -10639,7 +10597,7 @@
       <c r="AJ3" s="19">
         <v>1</v>
       </c>
-      <c r="AK3" s="131"/>
+      <c r="AK3" s="139"/>
     </row>
     <row r="4" spans="1:37">
       <c r="A4" s="30">
@@ -10699,7 +10657,7 @@
       <c r="AI4" s="66"/>
       <c r="AJ4" s="66"/>
       <c r="AK4" s="25">
-        <f>SUMIF(E4:AJ4,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <f t="shared" ref="AK4:AK16" si="0">SUMIF(E4:AJ4,"&lt;&gt;",$E$3:$AJ$3)</f>
         <v>6</v>
       </c>
     </row>
@@ -10744,14 +10702,22 @@
       <c r="T5" s="24"/>
       <c r="U5" s="64"/>
       <c r="V5" s="64"/>
-      <c r="W5" s="64"/>
-      <c r="X5" s="64"/>
+      <c r="W5" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="X5" s="64" t="s">
+        <v>12</v>
+      </c>
       <c r="Y5" s="64"/>
       <c r="Z5" s="65"/>
       <c r="AA5" s="65"/>
       <c r="AB5" s="65"/>
-      <c r="AC5" s="65"/>
-      <c r="AD5" s="66"/>
+      <c r="AC5" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD5" s="66" t="s">
+        <v>12</v>
+      </c>
       <c r="AE5" s="66" t="s">
         <v>12</v>
       </c>
@@ -10761,8 +10727,8 @@
       <c r="AI5" s="66"/>
       <c r="AJ5" s="66"/>
       <c r="AK5" s="25">
-        <f>SUMIF(E5:AJ5,"&lt;&gt;",$E$3:$AJ$3)</f>
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -10779,14 +10745,24 @@
         <v>62</v>
       </c>
       <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="62"/>
+      <c r="F6" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="62" t="s">
+        <v>12</v>
+      </c>
       <c r="H6" s="62"/>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
+      <c r="I6" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="J6" s="62" t="s">
+        <v>12</v>
+      </c>
       <c r="K6" s="62"/>
       <c r="L6" s="63"/>
-      <c r="M6" s="63"/>
+      <c r="M6" s="63" t="s">
+        <v>12</v>
+      </c>
       <c r="N6" s="63"/>
       <c r="O6" s="63"/>
       <c r="P6" s="63"/>
@@ -10803,16 +10779,20 @@
       <c r="AA6" s="65"/>
       <c r="AB6" s="65"/>
       <c r="AC6" s="65"/>
-      <c r="AD6" s="66"/>
-      <c r="AE6" s="66"/>
+      <c r="AD6" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE6" s="66" t="s">
+        <v>12</v>
+      </c>
       <c r="AF6" s="66"/>
       <c r="AG6" s="66"/>
       <c r="AH6" s="66"/>
       <c r="AI6" s="66"/>
       <c r="AJ6" s="66"/>
       <c r="AK6" s="25">
-        <f>SUMIF(E6:AJ6,"&lt;&gt;",$E$3:$AJ$3)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -10861,7 +10841,7 @@
       <c r="AI7" s="66"/>
       <c r="AJ7" s="66"/>
       <c r="AK7" s="25">
-        <f>SUMIF(E7:AJ7,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -10911,7 +10891,7 @@
       <c r="AI8" s="66"/>
       <c r="AJ8" s="66"/>
       <c r="AK8" s="25">
-        <f>SUMIF(E8:AJ8,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -10961,7 +10941,7 @@
       <c r="AI9" s="75"/>
       <c r="AJ9" s="75"/>
       <c r="AK9" s="93">
-        <f>SUMIF(E9:AJ9,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -11011,7 +10991,7 @@
       <c r="AI10" s="66"/>
       <c r="AJ10" s="66"/>
       <c r="AK10" s="25">
-        <f>SUMIF(E10:AJ10,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -11061,7 +11041,7 @@
       <c r="AI11" s="82"/>
       <c r="AJ11" s="82"/>
       <c r="AK11" s="94">
-        <f>SUMIF(E11:AJ11,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -11111,7 +11091,7 @@
       <c r="AI12" s="66"/>
       <c r="AJ12" s="66"/>
       <c r="AK12" s="25">
-        <f>SUMIF(E12:AJ12,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -11161,7 +11141,7 @@
       <c r="AI13" s="66"/>
       <c r="AJ13" s="66"/>
       <c r="AK13" s="25">
-        <f>SUMIF(E13:AJ13,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -11211,7 +11191,7 @@
       <c r="AI14" s="66"/>
       <c r="AJ14" s="66"/>
       <c r="AK14" s="25">
-        <f>SUMIF(E14:AJ14,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -11261,7 +11241,7 @@
       <c r="AI15" s="66"/>
       <c r="AJ15" s="66"/>
       <c r="AK15" s="25">
-        <f>SUMIF(E15:AJ15,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -11311,226 +11291,226 @@
       <c r="AI16" s="75"/>
       <c r="AJ16" s="75"/>
       <c r="AK16" s="25">
-        <f>SUMIF(E16:AJ16,"&lt;&gt;",$E$3:$AJ$3)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:37" ht="30" customHeight="1">
-      <c r="A17" s="148" t="s">
-        <v>77</v>
-      </c>
-      <c r="B17" s="149"/>
-      <c r="C17" s="149"/>
-      <c r="D17" s="150"/>
-      <c r="E17" s="106">
-        <f t="shared" ref="E17:AJ17" si="0">COUNTA(E4:E16)</f>
-        <v>1</v>
-      </c>
-      <c r="F17" s="106">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+    </row>
+    <row r="17" spans="1:37" ht="30" customHeight="1">
+      <c r="A17" s="132" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" s="133"/>
+      <c r="C17" s="133"/>
+      <c r="D17" s="134"/>
+      <c r="E17" s="106">
+        <f t="shared" ref="E17:AJ17" si="1">COUNTA(E4:E16)</f>
+        <v>1</v>
+      </c>
+      <c r="F17" s="106">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
       <c r="G17" s="106">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="H17" s="106">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I17" s="106">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="J17" s="106">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="K17" s="106">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L17" s="63">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="H17" s="106">
-        <f t="shared" si="0"/>
+      <c r="M17" s="63">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="N17" s="63">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I17" s="106">
-        <f t="shared" si="0"/>
+      <c r="O17" s="63">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P17" s="63">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="63">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="R17" s="29">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="29">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="29">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="64">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="64">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="64">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="X17" s="64">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Y17" s="64">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z17" s="65">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AA17" s="65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AB17" s="65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AC17" s="65">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AD17" s="66">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AE17" s="66">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J17" s="106">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="K17" s="106">
-        <f t="shared" si="0"/>
+      <c r="AF17" s="66">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L17" s="63">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M17" s="63">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="N17" s="63">
-        <f t="shared" si="0"/>
+      <c r="AG17" s="66">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O17" s="63">
-        <f t="shared" si="0"/>
+      <c r="AH17" s="66">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P17" s="63">
-        <f t="shared" si="0"/>
+      <c r="AI17" s="66">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q17" s="63">
-        <f t="shared" si="0"/>
+      <c r="AJ17" s="66">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R17" s="29">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S17" s="29">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="T17" s="29">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U17" s="64">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V17" s="64">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W17" s="64">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X17" s="64">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y17" s="64">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Z17" s="65">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AA17" s="65">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AB17" s="65">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AC17" s="65">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD17" s="66">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AE17" s="66">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AF17" s="66">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AG17" s="66">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AH17" s="66">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AI17" s="66">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AJ17" s="66">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
       <c r="AK17" s="25"/>
     </row>
     <row r="18" spans="1:37" ht="30" customHeight="1">
-      <c r="AG18" s="145" t="s">
+      <c r="AG18" s="129" t="s">
         <v>78</v>
       </c>
-      <c r="AH18" s="146"/>
-      <c r="AI18" s="146"/>
-      <c r="AJ18" s="147"/>
+      <c r="AH18" s="130"/>
+      <c r="AI18" s="130"/>
+      <c r="AJ18" s="131"/>
       <c r="AK18" s="107">
         <f>ROUND(AVERAGE(AK4:AK16),0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:37" ht="30" customHeight="1">
-      <c r="AG19" s="145" t="s">
+      <c r="AG19" s="129" t="s">
         <v>79</v>
       </c>
-      <c r="AH19" s="146"/>
-      <c r="AI19" s="146"/>
-      <c r="AJ19" s="147"/>
+      <c r="AH19" s="130"/>
+      <c r="AI19" s="130"/>
+      <c r="AJ19" s="131"/>
       <c r="AK19" s="107">
         <f>MAX(AK4:AK16)</f>
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:37" ht="30" customHeight="1">
-      <c r="AG20" s="145" t="s">
+      <c r="AG20" s="129" t="s">
         <v>80</v>
       </c>
-      <c r="AH20" s="146"/>
-      <c r="AI20" s="146"/>
-      <c r="AJ20" s="147"/>
+      <c r="AH20" s="130"/>
+      <c r="AI20" s="130"/>
+      <c r="AJ20" s="131"/>
       <c r="AK20" s="107">
         <f>MIN(AK4:AK16)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:37" ht="30" customHeight="1">
-      <c r="AG21" s="145" t="s">
+      <c r="AG21" s="129" t="s">
         <v>81</v>
       </c>
-      <c r="AH21" s="146"/>
-      <c r="AI21" s="146"/>
-      <c r="AJ21" s="147"/>
+      <c r="AH21" s="130"/>
+      <c r="AI21" s="130"/>
+      <c r="AJ21" s="131"/>
       <c r="AK21" s="107">
         <f>COUNTIF(AK4:AK16, "&gt;"&amp;AK18)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:37" ht="30" customHeight="1">
-      <c r="AG22" s="145" t="s">
+      <c r="AG22" s="129" t="s">
         <v>82</v>
       </c>
-      <c r="AH22" s="146"/>
-      <c r="AI22" s="146"/>
-      <c r="AJ22" s="147"/>
+      <c r="AH22" s="130"/>
+      <c r="AI22" s="130"/>
+      <c r="AJ22" s="131"/>
       <c r="AK22" s="107">
         <f>COUNTIF(AK4:AK16, "&lt;"&amp;AK18)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:37" ht="30" customHeight="1">
-      <c r="AG23" s="145" t="s">
+      <c r="AG23" s="129" t="s">
         <v>83</v>
       </c>
-      <c r="AH23" s="146"/>
-      <c r="AI23" s="146"/>
-      <c r="AJ23" s="147"/>
+      <c r="AH23" s="130"/>
+      <c r="AI23" s="130"/>
+      <c r="AJ23" s="131"/>
       <c r="AK23" s="107">
         <f>COUNTIF(AK4:AK16, "&gt;"&amp;20)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:37" ht="30" customHeight="1">
-      <c r="AG24" s="145" t="s">
+      <c r="AG24" s="129" t="s">
         <v>84</v>
       </c>
-      <c r="AH24" s="146"/>
-      <c r="AI24" s="146"/>
-      <c r="AJ24" s="147"/>
+      <c r="AH24" s="130"/>
+      <c r="AI24" s="130"/>
+      <c r="AJ24" s="131"/>
       <c r="AK24" s="107">
         <f>COUNTIF(AK4:AK16, "&lt;"&amp;20)</f>
         <v>13</v>
@@ -11541,6 +11521,14 @@
     <row r="27" spans="1:37" ht="30" customHeight="1"/>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="AG22:AJ22"/>
+    <mergeCell ref="AG23:AJ23"/>
+    <mergeCell ref="AG24:AJ24"/>
+    <mergeCell ref="AK1:AK3"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="AG18:AJ18"/>
+    <mergeCell ref="AG20:AJ20"/>
+    <mergeCell ref="AG21:AJ21"/>
     <mergeCell ref="AG19:AJ19"/>
     <mergeCell ref="A1:C2"/>
     <mergeCell ref="E1:K1"/>
@@ -11549,17 +11537,9 @@
     <mergeCell ref="U1:Y1"/>
     <mergeCell ref="Z1:AC1"/>
     <mergeCell ref="AD1:AJ1"/>
-    <mergeCell ref="AK1:AK3"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="AG18:AJ18"/>
-    <mergeCell ref="AG20:AJ20"/>
-    <mergeCell ref="AG21:AJ21"/>
-    <mergeCell ref="AG22:AJ22"/>
-    <mergeCell ref="AG23:AJ23"/>
-    <mergeCell ref="AG24:AJ24"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:AJ16 L17:AJ17 AH4:AJ17">
-    <cfRule type="expression" dxfId="4" priority="7">
+    <cfRule type="expression" dxfId="0" priority="7">
       <formula>E4="+"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Другое/2026/study_chart.xlsx
+++ b/Другое/2026/study_chart.xlsx
@@ -953,7 +953,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="101">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -10777,8 +10777,12 @@
       <c r="Y6" s="64"/>
       <c r="Z6" s="65"/>
       <c r="AA6" s="65"/>
-      <c r="AB6" s="65"/>
-      <c r="AC6" s="65"/>
+      <c r="AB6" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC6" s="65" t="s">
+        <v>12</v>
+      </c>
       <c r="AD6" s="66" t="s">
         <v>12</v>
       </c>
@@ -10792,7 +10796,7 @@
       <c r="AJ6" s="66"/>
       <c r="AK6" s="25">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -10808,15 +10812,29 @@
       <c r="D7" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="E7" s="62"/>
-      <c r="F7" s="62"/>
-      <c r="G7" s="62"/>
+      <c r="E7" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="62" t="s">
+        <v>12</v>
+      </c>
       <c r="H7" s="62"/>
-      <c r="I7" s="62"/>
-      <c r="J7" s="62"/>
+      <c r="I7" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="J7" s="62" t="s">
+        <v>12</v>
+      </c>
       <c r="K7" s="62"/>
-      <c r="L7" s="63"/>
-      <c r="M7" s="63"/>
+      <c r="L7" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="M7" s="63" t="s">
+        <v>12</v>
+      </c>
       <c r="N7" s="63"/>
       <c r="O7" s="63"/>
       <c r="P7" s="63"/>
@@ -10831,18 +10849,28 @@
       <c r="Y7" s="64"/>
       <c r="Z7" s="65"/>
       <c r="AA7" s="65"/>
-      <c r="AB7" s="65"/>
+      <c r="AB7" s="65" t="s">
+        <v>12</v>
+      </c>
       <c r="AC7" s="65"/>
-      <c r="AD7" s="66"/>
-      <c r="AE7" s="66"/>
+      <c r="AD7" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE7" s="66" t="s">
+        <v>12</v>
+      </c>
       <c r="AF7" s="66"/>
       <c r="AG7" s="66"/>
-      <c r="AH7" s="66"/>
-      <c r="AI7" s="66"/>
+      <c r="AH7" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AI7" s="66" t="s">
+        <v>12</v>
+      </c>
       <c r="AJ7" s="66"/>
       <c r="AK7" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -11304,15 +11332,15 @@
       <c r="D17" s="134"/>
       <c r="E17" s="106">
         <f t="shared" ref="E17:AJ17" si="1">COUNTA(E4:E16)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="106">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17" s="106">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H17" s="106">
         <f t="shared" si="1"/>
@@ -11320,11 +11348,11 @@
       </c>
       <c r="I17" s="106">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J17" s="106">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K17" s="106">
         <f t="shared" si="1"/>
@@ -11332,11 +11360,11 @@
       </c>
       <c r="L17" s="63">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M17" s="63">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N17" s="63">
         <f t="shared" si="1"/>
@@ -11396,19 +11424,19 @@
       </c>
       <c r="AB17" s="65">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC17" s="65">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD17" s="66">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE17" s="66">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF17" s="66">
         <f t="shared" si="1"/>
@@ -11420,11 +11448,11 @@
       </c>
       <c r="AH17" s="66">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI17" s="66">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ17" s="66">
         <f t="shared" si="1"/>
@@ -11441,7 +11469,7 @@
       <c r="AJ18" s="131"/>
       <c r="AK18" s="107">
         <f>ROUND(AVERAGE(AK4:AK16),0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:37" ht="30" customHeight="1">
@@ -11453,7 +11481,7 @@
       <c r="AJ19" s="131"/>
       <c r="AK19" s="107">
         <f>MAX(AK4:AK16)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:37" ht="30" customHeight="1">
@@ -11477,7 +11505,7 @@
       <c r="AJ21" s="131"/>
       <c r="AK21" s="107">
         <f>COUNTIF(AK4:AK16, "&gt;"&amp;AK18)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:37" ht="30" customHeight="1">
@@ -11489,7 +11517,7 @@
       <c r="AJ22" s="131"/>
       <c r="AK22" s="107">
         <f>COUNTIF(AK4:AK16, "&lt;"&amp;AK18)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:37" ht="30" customHeight="1">

--- a/Другое/2026/study_chart.xlsx
+++ b/Другое/2026/study_chart.xlsx
@@ -953,7 +953,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="969" uniqueCount="101">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -2558,6 +2558,60 @@
     <xf numFmtId="0" fontId="19" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2574,60 +2628,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5358,66 +5358,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="140"/>
-      <c r="B1" s="141"/>
-      <c r="C1" s="142"/>
+      <c r="A1" s="134"/>
+      <c r="B1" s="135"/>
+      <c r="C1" s="136"/>
       <c r="D1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="146" t="s">
+      <c r="E1" s="140" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="146"/>
-      <c r="G1" s="146"/>
-      <c r="H1" s="146"/>
-      <c r="I1" s="146"/>
-      <c r="J1" s="146"/>
-      <c r="K1" s="146"/>
-      <c r="L1" s="147" t="s">
+      <c r="F1" s="140"/>
+      <c r="G1" s="140"/>
+      <c r="H1" s="140"/>
+      <c r="I1" s="140"/>
+      <c r="J1" s="140"/>
+      <c r="K1" s="140"/>
+      <c r="L1" s="141" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
-      <c r="O1" s="147"/>
-      <c r="P1" s="147"/>
-      <c r="Q1" s="147"/>
-      <c r="R1" s="147"/>
-      <c r="S1" s="148" t="s">
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
+      <c r="S1" s="142" t="s">
         <v>39</v>
       </c>
-      <c r="T1" s="148"/>
-      <c r="U1" s="149" t="s">
+      <c r="T1" s="142"/>
+      <c r="U1" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="V1" s="150"/>
-      <c r="W1" s="150"/>
-      <c r="X1" s="150"/>
-      <c r="Y1" s="151"/>
-      <c r="Z1" s="152" t="s">
+      <c r="V1" s="144"/>
+      <c r="W1" s="144"/>
+      <c r="X1" s="144"/>
+      <c r="Y1" s="145"/>
+      <c r="Z1" s="146" t="s">
         <v>41</v>
       </c>
-      <c r="AA1" s="152"/>
-      <c r="AB1" s="152"/>
-      <c r="AC1" s="152"/>
-      <c r="AD1" s="152"/>
-      <c r="AE1" s="135" t="s">
+      <c r="AA1" s="146"/>
+      <c r="AB1" s="146"/>
+      <c r="AC1" s="146"/>
+      <c r="AD1" s="146"/>
+      <c r="AE1" s="129" t="s">
         <v>42</v>
       </c>
-      <c r="AF1" s="135"/>
-      <c r="AG1" s="135"/>
-      <c r="AH1" s="136" t="s">
+      <c r="AF1" s="129"/>
+      <c r="AG1" s="129"/>
+      <c r="AH1" s="130" t="s">
         <v>43</v>
       </c>
-      <c r="AI1" s="136"/>
-      <c r="AJ1" s="136"/>
-      <c r="AK1" s="137" t="s">
+      <c r="AI1" s="130"/>
+      <c r="AJ1" s="130"/>
+      <c r="AK1" s="131" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:37" s="2" customFormat="1" ht="30" customHeight="1">
-      <c r="A2" s="143"/>
-      <c r="B2" s="144"/>
-      <c r="C2" s="145"/>
+      <c r="A2" s="137"/>
+      <c r="B2" s="138"/>
+      <c r="C2" s="139"/>
       <c r="D2" s="5" t="s">
         <v>44</v>
       </c>
@@ -5511,7 +5511,7 @@
       <c r="AH2" s="12"/>
       <c r="AI2" s="12"/>
       <c r="AJ2" s="12"/>
-      <c r="AK2" s="138"/>
+      <c r="AK2" s="132"/>
     </row>
     <row r="3" spans="1:37">
       <c r="A3" s="13" t="s">
@@ -5622,7 +5622,7 @@
       <c r="AJ3" s="20">
         <v>2</v>
       </c>
-      <c r="AK3" s="139"/>
+      <c r="AK3" s="133"/>
     </row>
     <row r="4" spans="1:37">
       <c r="A4" s="21">
@@ -7673,12 +7673,12 @@
       </c>
     </row>
     <row r="35" spans="1:37" ht="30" customHeight="1">
-      <c r="A35" s="132" t="s">
+      <c r="A35" s="150" t="s">
         <v>77</v>
       </c>
-      <c r="B35" s="133"/>
-      <c r="C35" s="133"/>
-      <c r="D35" s="134"/>
+      <c r="B35" s="151"/>
+      <c r="C35" s="151"/>
+      <c r="D35" s="152"/>
       <c r="E35" s="106">
         <f>COUNTA(E4:E34)</f>
         <v>14</v>
@@ -7810,84 +7810,84 @@
       <c r="AK35" s="25"/>
     </row>
     <row r="36" spans="1:37" ht="30" customHeight="1">
-      <c r="AG36" s="129" t="s">
+      <c r="AG36" s="147" t="s">
         <v>78</v>
       </c>
-      <c r="AH36" s="130"/>
-      <c r="AI36" s="130"/>
-      <c r="AJ36" s="131"/>
+      <c r="AH36" s="148"/>
+      <c r="AI36" s="148"/>
+      <c r="AJ36" s="149"/>
       <c r="AK36" s="107">
         <f>ROUND(AVERAGE(AK4:AK34),0)</f>
         <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:37" ht="30" customHeight="1">
-      <c r="AG37" s="129" t="s">
+      <c r="AG37" s="147" t="s">
         <v>79</v>
       </c>
-      <c r="AH37" s="130"/>
-      <c r="AI37" s="130"/>
-      <c r="AJ37" s="131"/>
+      <c r="AH37" s="148"/>
+      <c r="AI37" s="148"/>
+      <c r="AJ37" s="149"/>
       <c r="AK37" s="107">
         <f>MAX(AK4:AK34)</f>
         <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:37" ht="30" customHeight="1">
-      <c r="AG38" s="129" t="s">
+      <c r="AG38" s="147" t="s">
         <v>80</v>
       </c>
-      <c r="AH38" s="130"/>
-      <c r="AI38" s="130"/>
-      <c r="AJ38" s="131"/>
+      <c r="AH38" s="148"/>
+      <c r="AI38" s="148"/>
+      <c r="AJ38" s="149"/>
       <c r="AK38" s="107">
         <f>MIN(AK4:AK34)</f>
         <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:37" ht="30" customHeight="1">
-      <c r="AG39" s="129" t="s">
+      <c r="AG39" s="147" t="s">
         <v>81</v>
       </c>
-      <c r="AH39" s="130"/>
-      <c r="AI39" s="130"/>
-      <c r="AJ39" s="131"/>
+      <c r="AH39" s="148"/>
+      <c r="AI39" s="148"/>
+      <c r="AJ39" s="149"/>
       <c r="AK39" s="107">
         <f>COUNTIF(AK4:AK34, "&gt;"&amp;AK36)</f>
         <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:37" ht="30" customHeight="1">
-      <c r="AG40" s="129" t="s">
+      <c r="AG40" s="147" t="s">
         <v>82</v>
       </c>
-      <c r="AH40" s="130"/>
-      <c r="AI40" s="130"/>
-      <c r="AJ40" s="131"/>
+      <c r="AH40" s="148"/>
+      <c r="AI40" s="148"/>
+      <c r="AJ40" s="149"/>
       <c r="AK40" s="107">
         <f>COUNTIF(AK4:AK34, "&lt;"&amp;AK36)</f>
         <v>18</v>
       </c>
     </row>
     <row r="41" spans="1:37" ht="30" customHeight="1">
-      <c r="AG41" s="129" t="s">
+      <c r="AG41" s="147" t="s">
         <v>83</v>
       </c>
-      <c r="AH41" s="130"/>
-      <c r="AI41" s="130"/>
-      <c r="AJ41" s="131"/>
+      <c r="AH41" s="148"/>
+      <c r="AI41" s="148"/>
+      <c r="AJ41" s="149"/>
       <c r="AK41" s="107">
         <f>COUNTIF(AK4:AK34, "&gt;"&amp;20)</f>
         <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:37" ht="30" customHeight="1">
-      <c r="AG42" s="129" t="s">
+      <c r="AG42" s="147" t="s">
         <v>84</v>
       </c>
-      <c r="AH42" s="130"/>
-      <c r="AI42" s="130"/>
-      <c r="AJ42" s="131"/>
+      <c r="AH42" s="148"/>
+      <c r="AI42" s="148"/>
+      <c r="AJ42" s="149"/>
       <c r="AK42" s="107">
         <f>COUNTIF(AK4:AK34, "&lt;"&amp;20)</f>
         <v>21</v>
@@ -7898,6 +7898,14 @@
     <row r="45" spans="1:37" ht="30" customHeight="1"/>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="AG40:AJ40"/>
+    <mergeCell ref="AG41:AJ41"/>
+    <mergeCell ref="AG42:AJ42"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="AG36:AJ36"/>
+    <mergeCell ref="AG37:AJ37"/>
+    <mergeCell ref="AG38:AJ38"/>
+    <mergeCell ref="AG39:AJ39"/>
     <mergeCell ref="AE1:AG1"/>
     <mergeCell ref="AH1:AJ1"/>
     <mergeCell ref="AK1:AK3"/>
@@ -7907,14 +7915,6 @@
     <mergeCell ref="S1:T1"/>
     <mergeCell ref="U1:Y1"/>
     <mergeCell ref="Z1:AD1"/>
-    <mergeCell ref="AG40:AJ40"/>
-    <mergeCell ref="AG41:AJ41"/>
-    <mergeCell ref="AG42:AJ42"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="AG36:AJ36"/>
-    <mergeCell ref="AG37:AJ37"/>
-    <mergeCell ref="AG38:AJ38"/>
-    <mergeCell ref="AG39:AJ39"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:AJ34">
     <cfRule type="expression" dxfId="13" priority="7">
@@ -7992,66 +7992,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="140"/>
-      <c r="B1" s="141"/>
-      <c r="C1" s="142"/>
+      <c r="A1" s="134"/>
+      <c r="B1" s="135"/>
+      <c r="C1" s="136"/>
       <c r="D1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="146" t="s">
+      <c r="E1" s="140" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="146"/>
-      <c r="G1" s="146"/>
-      <c r="H1" s="146"/>
-      <c r="I1" s="146"/>
-      <c r="J1" s="146"/>
-      <c r="K1" s="146"/>
-      <c r="L1" s="147" t="s">
+      <c r="F1" s="140"/>
+      <c r="G1" s="140"/>
+      <c r="H1" s="140"/>
+      <c r="I1" s="140"/>
+      <c r="J1" s="140"/>
+      <c r="K1" s="140"/>
+      <c r="L1" s="141" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
-      <c r="O1" s="147"/>
-      <c r="P1" s="147"/>
-      <c r="Q1" s="147"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
       <c r="R1" s="153" t="s">
         <v>39</v>
       </c>
       <c r="S1" s="154"/>
       <c r="T1" s="155"/>
-      <c r="U1" s="149" t="s">
+      <c r="U1" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="V1" s="150"/>
-      <c r="W1" s="150"/>
-      <c r="X1" s="150"/>
-      <c r="Y1" s="151"/>
-      <c r="Z1" s="152" t="s">
+      <c r="V1" s="144"/>
+      <c r="W1" s="144"/>
+      <c r="X1" s="144"/>
+      <c r="Y1" s="145"/>
+      <c r="Z1" s="146" t="s">
         <v>41</v>
       </c>
-      <c r="AA1" s="152"/>
-      <c r="AB1" s="152"/>
-      <c r="AC1" s="152"/>
-      <c r="AD1" s="152"/>
-      <c r="AE1" s="135" t="s">
+      <c r="AA1" s="146"/>
+      <c r="AB1" s="146"/>
+      <c r="AC1" s="146"/>
+      <c r="AD1" s="146"/>
+      <c r="AE1" s="129" t="s">
         <v>42</v>
       </c>
-      <c r="AF1" s="135"/>
-      <c r="AG1" s="135"/>
-      <c r="AH1" s="136" t="s">
+      <c r="AF1" s="129"/>
+      <c r="AG1" s="129"/>
+      <c r="AH1" s="130" t="s">
         <v>43</v>
       </c>
-      <c r="AI1" s="136"/>
-      <c r="AJ1" s="136"/>
-      <c r="AK1" s="137" t="s">
+      <c r="AI1" s="130"/>
+      <c r="AJ1" s="130"/>
+      <c r="AK1" s="131" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:37" s="2" customFormat="1" ht="45" customHeight="1">
-      <c r="A2" s="143"/>
-      <c r="B2" s="144"/>
-      <c r="C2" s="145"/>
+      <c r="A2" s="137"/>
+      <c r="B2" s="138"/>
+      <c r="C2" s="139"/>
       <c r="D2" s="5" t="s">
         <v>44</v>
       </c>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="AI2" s="12"/>
       <c r="AJ2" s="12"/>
-      <c r="AK2" s="138"/>
+      <c r="AK2" s="132"/>
     </row>
     <row r="3" spans="1:37">
       <c r="A3" s="13" t="s">
@@ -8258,7 +8258,7 @@
       <c r="AJ3" s="20">
         <v>1</v>
       </c>
-      <c r="AK3" s="139"/>
+      <c r="AK3" s="133"/>
     </row>
     <row r="4" spans="1:37">
       <c r="A4" s="30">
@@ -10015,12 +10015,12 @@
       </c>
     </row>
     <row r="34" spans="1:37" ht="30" customHeight="1">
-      <c r="A34" s="132" t="s">
+      <c r="A34" s="150" t="s">
         <v>77</v>
       </c>
-      <c r="B34" s="133"/>
-      <c r="C34" s="133"/>
-      <c r="D34" s="134"/>
+      <c r="B34" s="151"/>
+      <c r="C34" s="151"/>
+      <c r="D34" s="152"/>
       <c r="E34" s="106">
         <f t="shared" ref="E34:AJ34" si="1">COUNTA(E4:E33)</f>
         <v>2</v>
@@ -10152,84 +10152,84 @@
       <c r="AK34" s="25"/>
     </row>
     <row r="35" spans="1:37" ht="30" customHeight="1">
-      <c r="AG35" s="129" t="s">
+      <c r="AG35" s="147" t="s">
         <v>78</v>
       </c>
-      <c r="AH35" s="130"/>
-      <c r="AI35" s="130"/>
-      <c r="AJ35" s="131"/>
+      <c r="AH35" s="148"/>
+      <c r="AI35" s="148"/>
+      <c r="AJ35" s="149"/>
       <c r="AK35" s="107">
         <f>ROUND(AVERAGE(AK4:AK33),0)</f>
         <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:37" ht="30" customHeight="1">
-      <c r="AG36" s="129" t="s">
+      <c r="AG36" s="147" t="s">
         <v>79</v>
       </c>
-      <c r="AH36" s="130"/>
-      <c r="AI36" s="130"/>
-      <c r="AJ36" s="131"/>
+      <c r="AH36" s="148"/>
+      <c r="AI36" s="148"/>
+      <c r="AJ36" s="149"/>
       <c r="AK36" s="107">
         <f>MAX(AK4:AK33)</f>
         <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:37" ht="30" customHeight="1">
-      <c r="AG37" s="129" t="s">
+      <c r="AG37" s="147" t="s">
         <v>80</v>
       </c>
-      <c r="AH37" s="130"/>
-      <c r="AI37" s="130"/>
-      <c r="AJ37" s="131"/>
+      <c r="AH37" s="148"/>
+      <c r="AI37" s="148"/>
+      <c r="AJ37" s="149"/>
       <c r="AK37" s="107">
         <f>MIN(AK4:AK33)</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:37" ht="30" customHeight="1">
-      <c r="AG38" s="129" t="s">
+      <c r="AG38" s="147" t="s">
         <v>81</v>
       </c>
-      <c r="AH38" s="130"/>
-      <c r="AI38" s="130"/>
-      <c r="AJ38" s="131"/>
+      <c r="AH38" s="148"/>
+      <c r="AI38" s="148"/>
+      <c r="AJ38" s="149"/>
       <c r="AK38" s="107">
         <f>COUNTIF(AK4:AK33, "&gt;"&amp;AK35)</f>
         <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:37" ht="30" customHeight="1">
-      <c r="AG39" s="129" t="s">
+      <c r="AG39" s="147" t="s">
         <v>82</v>
       </c>
-      <c r="AH39" s="130"/>
-      <c r="AI39" s="130"/>
-      <c r="AJ39" s="131"/>
+      <c r="AH39" s="148"/>
+      <c r="AI39" s="148"/>
+      <c r="AJ39" s="149"/>
       <c r="AK39" s="107">
         <f>COUNTIF(AK4:AK33, "&lt;"&amp;AK35)</f>
         <v>14</v>
       </c>
     </row>
     <row r="40" spans="1:37" ht="30" customHeight="1">
-      <c r="AG40" s="129" t="s">
+      <c r="AG40" s="147" t="s">
         <v>83</v>
       </c>
-      <c r="AH40" s="130"/>
-      <c r="AI40" s="130"/>
-      <c r="AJ40" s="131"/>
+      <c r="AH40" s="148"/>
+      <c r="AI40" s="148"/>
+      <c r="AJ40" s="149"/>
       <c r="AK40" s="107">
         <f>COUNTIF(AK4:AK33, "&gt;"&amp;20)</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:37" ht="30" customHeight="1">
-      <c r="AG41" s="129" t="s">
+      <c r="AG41" s="147" t="s">
         <v>84</v>
       </c>
-      <c r="AH41" s="130"/>
-      <c r="AI41" s="130"/>
-      <c r="AJ41" s="131"/>
+      <c r="AH41" s="148"/>
+      <c r="AI41" s="148"/>
+      <c r="AJ41" s="149"/>
       <c r="AK41" s="107">
         <f>COUNTIF(AK4:AK33, "&lt;"&amp;20)</f>
         <v>30</v>
@@ -10240,23 +10240,23 @@
     <row r="44" spans="1:37" ht="30" customHeight="1"/>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="AE1:AG1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="AG40:AJ40"/>
-    <mergeCell ref="AG41:AJ41"/>
-    <mergeCell ref="AK1:AK3"/>
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="E1:K1"/>
+    <mergeCell ref="L1:Q1"/>
+    <mergeCell ref="U1:Y1"/>
+    <mergeCell ref="Z1:AD1"/>
+    <mergeCell ref="R1:T1"/>
     <mergeCell ref="A34:D34"/>
     <mergeCell ref="AG37:AJ37"/>
     <mergeCell ref="AG38:AJ38"/>
     <mergeCell ref="AG39:AJ39"/>
     <mergeCell ref="AG35:AJ35"/>
     <mergeCell ref="AG36:AJ36"/>
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="E1:K1"/>
-    <mergeCell ref="L1:Q1"/>
-    <mergeCell ref="U1:Y1"/>
-    <mergeCell ref="Z1:AD1"/>
-    <mergeCell ref="R1:T1"/>
+    <mergeCell ref="AE1:AG1"/>
+    <mergeCell ref="AH1:AJ1"/>
+    <mergeCell ref="AG40:AJ40"/>
+    <mergeCell ref="AG41:AJ41"/>
+    <mergeCell ref="AK1:AK3"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:AJ33 L34:Q34">
     <cfRule type="expression" dxfId="6" priority="7">
@@ -10329,47 +10329,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="140"/>
-      <c r="B1" s="141"/>
-      <c r="C1" s="142"/>
+      <c r="A1" s="134"/>
+      <c r="B1" s="135"/>
+      <c r="C1" s="136"/>
       <c r="D1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="146" t="s">
+      <c r="E1" s="140" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="146"/>
-      <c r="G1" s="146"/>
-      <c r="H1" s="146"/>
-      <c r="I1" s="146"/>
-      <c r="J1" s="146"/>
-      <c r="K1" s="146"/>
-      <c r="L1" s="147" t="s">
+      <c r="F1" s="140"/>
+      <c r="G1" s="140"/>
+      <c r="H1" s="140"/>
+      <c r="I1" s="140"/>
+      <c r="J1" s="140"/>
+      <c r="K1" s="140"/>
+      <c r="L1" s="141" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
-      <c r="O1" s="147"/>
-      <c r="P1" s="147"/>
-      <c r="Q1" s="147"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
       <c r="R1" s="156" t="s">
         <v>39</v>
       </c>
       <c r="S1" s="157"/>
       <c r="T1" s="158"/>
-      <c r="U1" s="149" t="s">
+      <c r="U1" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="V1" s="150"/>
-      <c r="W1" s="150"/>
-      <c r="X1" s="150"/>
-      <c r="Y1" s="151"/>
-      <c r="Z1" s="152" t="s">
+      <c r="V1" s="144"/>
+      <c r="W1" s="144"/>
+      <c r="X1" s="144"/>
+      <c r="Y1" s="145"/>
+      <c r="Z1" s="146" t="s">
         <v>41</v>
       </c>
-      <c r="AA1" s="152"/>
-      <c r="AB1" s="152"/>
-      <c r="AC1" s="152"/>
+      <c r="AA1" s="146"/>
+      <c r="AB1" s="146"/>
+      <c r="AC1" s="146"/>
       <c r="AD1" s="159" t="s">
         <v>93</v>
       </c>
@@ -10379,14 +10379,14 @@
       <c r="AH1" s="160"/>
       <c r="AI1" s="160"/>
       <c r="AJ1" s="161"/>
-      <c r="AK1" s="137" t="s">
+      <c r="AK1" s="131" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:37" s="2" customFormat="1" ht="70.5" customHeight="1">
-      <c r="A2" s="143"/>
-      <c r="B2" s="144"/>
-      <c r="C2" s="145"/>
+      <c r="A2" s="137"/>
+      <c r="B2" s="138"/>
+      <c r="C2" s="139"/>
       <c r="D2" s="5" t="s">
         <v>44</v>
       </c>
@@ -10486,7 +10486,7 @@
       <c r="AJ2" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="AK2" s="138"/>
+      <c r="AK2" s="132"/>
     </row>
     <row r="3" spans="1:37">
       <c r="A3" s="13" t="s">
@@ -10597,7 +10597,7 @@
       <c r="AJ3" s="19">
         <v>1</v>
       </c>
-      <c r="AK3" s="139"/>
+      <c r="AK3" s="133"/>
     </row>
     <row r="4" spans="1:37">
       <c r="A4" s="30">
@@ -10852,7 +10852,9 @@
       <c r="AB7" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="AC7" s="65"/>
+      <c r="AC7" s="65" t="s">
+        <v>12</v>
+      </c>
       <c r="AD7" s="66" t="s">
         <v>12</v>
       </c>
@@ -10870,7 +10872,7 @@
       <c r="AJ7" s="66"/>
       <c r="AK7" s="25">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -10888,13 +10890,19 @@
       </c>
       <c r="E8" s="62"/>
       <c r="F8" s="62"/>
-      <c r="G8" s="62"/>
+      <c r="G8" s="62" t="s">
+        <v>12</v>
+      </c>
       <c r="H8" s="62"/>
       <c r="I8" s="62"/>
-      <c r="J8" s="62"/>
+      <c r="J8" s="62" t="s">
+        <v>12</v>
+      </c>
       <c r="K8" s="62"/>
       <c r="L8" s="63"/>
-      <c r="M8" s="63"/>
+      <c r="M8" s="63" t="s">
+        <v>12</v>
+      </c>
       <c r="N8" s="63"/>
       <c r="O8" s="63"/>
       <c r="P8" s="63"/>
@@ -10911,16 +10919,22 @@
       <c r="AA8" s="65"/>
       <c r="AB8" s="65"/>
       <c r="AC8" s="65"/>
-      <c r="AD8" s="66"/>
-      <c r="AE8" s="66"/>
+      <c r="AD8" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE8" s="66" t="s">
+        <v>12</v>
+      </c>
       <c r="AF8" s="66"/>
       <c r="AG8" s="66"/>
-      <c r="AH8" s="66"/>
+      <c r="AH8" s="66" t="s">
+        <v>12</v>
+      </c>
       <c r="AI8" s="66"/>
       <c r="AJ8" s="66"/>
       <c r="AK8" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -11324,12 +11338,12 @@
       </c>
     </row>
     <row r="17" spans="1:37" ht="30" customHeight="1">
-      <c r="A17" s="132" t="s">
+      <c r="A17" s="150" t="s">
         <v>77</v>
       </c>
-      <c r="B17" s="133"/>
-      <c r="C17" s="133"/>
-      <c r="D17" s="134"/>
+      <c r="B17" s="151"/>
+      <c r="C17" s="151"/>
+      <c r="D17" s="152"/>
       <c r="E17" s="106">
         <f t="shared" ref="E17:AJ17" si="1">COUNTA(E4:E16)</f>
         <v>2</v>
@@ -11340,7 +11354,7 @@
       </c>
       <c r="G17" s="106">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H17" s="106">
         <f t="shared" si="1"/>
@@ -11352,7 +11366,7 @@
       </c>
       <c r="J17" s="106">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K17" s="106">
         <f t="shared" si="1"/>
@@ -11364,7 +11378,7 @@
       </c>
       <c r="M17" s="63">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N17" s="63">
         <f t="shared" si="1"/>
@@ -11428,15 +11442,15 @@
       </c>
       <c r="AC17" s="65">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD17" s="66">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE17" s="66">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF17" s="66">
         <f t="shared" si="1"/>
@@ -11448,7 +11462,7 @@
       </c>
       <c r="AH17" s="66">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI17" s="66">
         <f t="shared" si="1"/>
@@ -11461,84 +11475,84 @@
       <c r="AK17" s="25"/>
     </row>
     <row r="18" spans="1:37" ht="30" customHeight="1">
-      <c r="AG18" s="129" t="s">
+      <c r="AG18" s="147" t="s">
         <v>78</v>
       </c>
-      <c r="AH18" s="130"/>
-      <c r="AI18" s="130"/>
-      <c r="AJ18" s="131"/>
+      <c r="AH18" s="148"/>
+      <c r="AI18" s="148"/>
+      <c r="AJ18" s="149"/>
       <c r="AK18" s="107">
         <f>ROUND(AVERAGE(AK4:AK16),0)</f>
         <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:37" ht="30" customHeight="1">
-      <c r="AG19" s="129" t="s">
+      <c r="AG19" s="147" t="s">
         <v>79</v>
       </c>
-      <c r="AH19" s="130"/>
-      <c r="AI19" s="130"/>
-      <c r="AJ19" s="131"/>
+      <c r="AH19" s="148"/>
+      <c r="AI19" s="148"/>
+      <c r="AJ19" s="149"/>
       <c r="AK19" s="107">
         <f>MAX(AK4:AK16)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:37" ht="30" customHeight="1">
-      <c r="AG20" s="129" t="s">
+      <c r="AG20" s="147" t="s">
         <v>80</v>
       </c>
-      <c r="AH20" s="130"/>
-      <c r="AI20" s="130"/>
-      <c r="AJ20" s="131"/>
+      <c r="AH20" s="148"/>
+      <c r="AI20" s="148"/>
+      <c r="AJ20" s="149"/>
       <c r="AK20" s="107">
         <f>MIN(AK4:AK16)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:37" ht="30" customHeight="1">
-      <c r="AG21" s="129" t="s">
+      <c r="AG21" s="147" t="s">
         <v>81</v>
       </c>
-      <c r="AH21" s="130"/>
-      <c r="AI21" s="130"/>
-      <c r="AJ21" s="131"/>
+      <c r="AH21" s="148"/>
+      <c r="AI21" s="148"/>
+      <c r="AJ21" s="149"/>
       <c r="AK21" s="107">
         <f>COUNTIF(AK4:AK16, "&gt;"&amp;AK18)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:37" ht="30" customHeight="1">
-      <c r="AG22" s="129" t="s">
+      <c r="AG22" s="147" t="s">
         <v>82</v>
       </c>
-      <c r="AH22" s="130"/>
-      <c r="AI22" s="130"/>
-      <c r="AJ22" s="131"/>
+      <c r="AH22" s="148"/>
+      <c r="AI22" s="148"/>
+      <c r="AJ22" s="149"/>
       <c r="AK22" s="107">
         <f>COUNTIF(AK4:AK16, "&lt;"&amp;AK18)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:37" ht="30" customHeight="1">
-      <c r="AG23" s="129" t="s">
+      <c r="AG23" s="147" t="s">
         <v>83</v>
       </c>
-      <c r="AH23" s="130"/>
-      <c r="AI23" s="130"/>
-      <c r="AJ23" s="131"/>
+      <c r="AH23" s="148"/>
+      <c r="AI23" s="148"/>
+      <c r="AJ23" s="149"/>
       <c r="AK23" s="107">
         <f>COUNTIF(AK4:AK16, "&gt;"&amp;20)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:37" ht="30" customHeight="1">
-      <c r="AG24" s="129" t="s">
+      <c r="AG24" s="147" t="s">
         <v>84</v>
       </c>
-      <c r="AH24" s="130"/>
-      <c r="AI24" s="130"/>
-      <c r="AJ24" s="131"/>
+      <c r="AH24" s="148"/>
+      <c r="AI24" s="148"/>
+      <c r="AJ24" s="149"/>
       <c r="AK24" s="107">
         <f>COUNTIF(AK4:AK16, "&lt;"&amp;20)</f>
         <v>13</v>

--- a/Другое/2026/study_chart.xlsx
+++ b/Другое/2026/study_chart.xlsx
@@ -1,13 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROG\Git\Repository_1\Другое\2026\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4507"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="10980" activeTab="4"/>
   </bookViews>
@@ -18,7 +13,7 @@
     <sheet name="Сентябрь" sheetId="6" r:id="rId4"/>
     <sheet name="Октябрь" sheetId="7" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="125725"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -41,7 +36,7 @@
     <author>Собянин Евгений Андреевич (new)</author>
   </authors>
   <commentList>
-    <comment ref="AF21" authorId="0" shapeId="0">
+    <comment ref="AF21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -64,7 +59,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF22" authorId="0" shapeId="0">
+    <comment ref="AF22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -88,7 +83,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF23" authorId="0" shapeId="0">
+    <comment ref="AF23" authorId="0">
       <text>
         <r>
           <rPr>
@@ -114,7 +109,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF24" authorId="0" shapeId="0">
+    <comment ref="AF24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -138,7 +133,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG24" authorId="0" shapeId="0">
+    <comment ref="AG24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -160,7 +155,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH24" authorId="0" shapeId="0">
+    <comment ref="AH24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -182,7 +177,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF25" authorId="0" shapeId="0">
+    <comment ref="AF25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -208,7 +203,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG25" authorId="0" shapeId="0">
+    <comment ref="AG25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -230,7 +225,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH25" authorId="0" shapeId="0">
+    <comment ref="AH25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -252,7 +247,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AI25" authorId="0" shapeId="0">
+    <comment ref="AI25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -274,7 +269,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AJ25" authorId="0" shapeId="0">
+    <comment ref="AJ25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -296,7 +291,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AK25" authorId="0" shapeId="0">
+    <comment ref="AK25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -318,7 +313,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF26" authorId="0" shapeId="0">
+    <comment ref="AF26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -340,7 +335,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG26" authorId="0" shapeId="0">
+    <comment ref="AG26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -362,7 +357,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH26" authorId="0" shapeId="0">
+    <comment ref="AH26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -384,7 +379,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AI26" authorId="0" shapeId="0">
+    <comment ref="AI26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -406,7 +401,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AJ26" authorId="0" shapeId="0">
+    <comment ref="AJ26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -428,7 +423,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AK26" authorId="0" shapeId="0">
+    <comment ref="AK26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -450,7 +445,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF27" authorId="0" shapeId="0">
+    <comment ref="AF27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -472,7 +467,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG27" authorId="0" shapeId="0">
+    <comment ref="AG27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -494,7 +489,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH27" authorId="0" shapeId="0">
+    <comment ref="AH27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -516,7 +511,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF28" authorId="0" shapeId="0">
+    <comment ref="AF28" authorId="0">
       <text>
         <r>
           <rPr>
@@ -538,7 +533,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF29" authorId="0" shapeId="0">
+    <comment ref="AF29" authorId="0">
       <text>
         <r>
           <rPr>
@@ -561,7 +556,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF30" authorId="0" shapeId="0">
+    <comment ref="AF30" authorId="0">
       <text>
         <r>
           <rPr>
@@ -585,7 +580,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF31" authorId="0" shapeId="0">
+    <comment ref="AF31" authorId="0">
       <text>
         <r>
           <rPr>
@@ -608,7 +603,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF32" authorId="0" shapeId="0">
+    <comment ref="AF32" authorId="0">
       <text>
         <r>
           <rPr>
@@ -632,7 +627,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF33" authorId="0" shapeId="0">
+    <comment ref="AF33" authorId="0">
       <text>
         <r>
           <rPr>
@@ -655,7 +650,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF35" authorId="0" shapeId="0">
+    <comment ref="AF35" authorId="0">
       <text>
         <r>
           <rPr>
@@ -677,7 +672,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF36" authorId="0" shapeId="0">
+    <comment ref="AF36" authorId="0">
       <text>
         <r>
           <rPr>
@@ -699,7 +694,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF37" authorId="0" shapeId="0">
+    <comment ref="AF37" authorId="0">
       <text>
         <r>
           <rPr>
@@ -721,7 +716,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF38" authorId="0" shapeId="0">
+    <comment ref="AF38" authorId="0">
       <text>
         <r>
           <rPr>
@@ -753,7 +748,7 @@
     <author>Собянин Евгений Андреевич (new)</author>
   </authors>
   <commentList>
-    <comment ref="AH14" authorId="0" shapeId="0">
+    <comment ref="AH14" authorId="0">
       <text>
         <r>
           <rPr>
@@ -777,7 +772,7 @@
     <author>Собянин Евгений Андреевич (new)</author>
   </authors>
   <commentList>
-    <comment ref="AH5" authorId="0" shapeId="0">
+    <comment ref="AH5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -790,7 +785,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH6" authorId="0" shapeId="0">
+    <comment ref="AH6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -803,7 +798,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH8" authorId="0" shapeId="0">
+    <comment ref="AH8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -816,7 +811,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH9" authorId="0" shapeId="0">
+    <comment ref="AH9" authorId="0">
       <text>
         <r>
           <rPr>
@@ -829,7 +824,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AI9" authorId="0" shapeId="0">
+    <comment ref="AI9" authorId="0">
       <text>
         <r>
           <rPr>
@@ -842,7 +837,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AI16" authorId="0" shapeId="0">
+    <comment ref="AI16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -855,7 +850,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AI22" authorId="0" shapeId="0">
+    <comment ref="AI22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -868,7 +863,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AI23" authorId="0" shapeId="0">
+    <comment ref="AI23" authorId="0">
       <text>
         <r>
           <rPr>
@@ -886,7 +881,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="103">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -1232,13 +1227,19 @@
   <si>
     <t>Конспектирование прочитанных произведений</t>
   </si>
+  <si>
+    <t>Количество дней больше 10</t>
+  </si>
+  <si>
+    <t>Количество дней меньше 10</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="dd\.mmm"/>
+    <numFmt numFmtId="164" formatCode="dd\.mmm"/>
   </numFmts>
   <fonts count="41">
     <font>
@@ -2175,7 +2176,7 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2202,7 +2203,7 @@
     <xf numFmtId="0" fontId="1" fillId="18" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="1" fillId="18" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="18" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2289,13 +2290,13 @@
     <xf numFmtId="0" fontId="1" fillId="23" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="22" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="22" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2368,7 +2369,7 @@
     <xf numFmtId="0" fontId="17" fillId="25" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="0" xfId="0" applyFill="1"/>
@@ -2418,7 +2419,7 @@
     <xf numFmtId="0" fontId="31" fillId="30" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="31" fillId="30" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="31" fillId="30" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="31" fillId="30" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2428,7 +2429,7 @@
     <xf numFmtId="0" fontId="32" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="31" fillId="30" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="31" fillId="30" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2447,11 +2448,17 @@
     <xf numFmtId="0" fontId="31" fillId="30" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="31" fillId="30" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="31" fillId="30" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="31" fillId="30" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="28" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="16" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="34" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2481,6 +2488,57 @@
     <xf numFmtId="0" fontId="24" fillId="28" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2502,57 +2560,6 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2562,6 +2569,15 @@
     <xf numFmtId="0" fontId="21" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2569,53 +2585,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="16" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="17">
     <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFC0E16D"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC0E16D"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFB6EA86"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFB6EA86"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3042,7 +3022,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="H9:Q22"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -3059,18 +3039,18 @@
   </cols>
   <sheetData>
     <row r="9" spans="8:17" ht="45" customHeight="1">
-      <c r="H9" s="119" t="s">
+      <c r="H9" s="121" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="120"/>
-      <c r="J9" s="120"/>
-      <c r="K9" s="120"/>
-      <c r="L9" s="120"/>
-      <c r="M9" s="120"/>
-      <c r="N9" s="120"/>
-      <c r="O9" s="120"/>
-      <c r="P9" s="120"/>
-      <c r="Q9" s="121"/>
+      <c r="I9" s="122"/>
+      <c r="J9" s="122"/>
+      <c r="K9" s="122"/>
+      <c r="L9" s="122"/>
+      <c r="M9" s="122"/>
+      <c r="N9" s="122"/>
+      <c r="O9" s="122"/>
+      <c r="P9" s="122"/>
+      <c r="Q9" s="123"/>
     </row>
     <row r="10" spans="8:17" ht="30" customHeight="1">
       <c r="H10" s="112" t="s">
@@ -3339,11 +3319,11 @@
       <c r="Q21" s="117"/>
     </row>
     <row r="22" spans="8:17" ht="15.75">
-      <c r="H22" s="122" t="s">
+      <c r="H22" s="124" t="s">
         <v>19</v>
       </c>
-      <c r="I22" s="123"/>
-      <c r="J22" s="124"/>
+      <c r="I22" s="125"/>
+      <c r="J22" s="126"/>
       <c r="K22" s="118">
         <f>COUNTA(K11:K21)</f>
         <v>6</v>
@@ -3379,12 +3359,12 @@
     <mergeCell ref="H22:J22"/>
   </mergeCells>
   <conditionalFormatting sqref="K22:Q22">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>Q22="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11:Q21">
-    <cfRule type="expression" dxfId="18" priority="2">
+    <cfRule type="expression" dxfId="15" priority="2">
       <formula>Q11="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3394,7 +3374,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="H9:AL42"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -3420,39 +3400,39 @@
   </cols>
   <sheetData>
     <row r="9" spans="8:38" ht="45" customHeight="1">
-      <c r="H9" s="125" t="s">
+      <c r="H9" s="127" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="126"/>
-      <c r="J9" s="126"/>
-      <c r="K9" s="126"/>
-      <c r="L9" s="126"/>
-      <c r="M9" s="126"/>
-      <c r="N9" s="126"/>
-      <c r="O9" s="126"/>
-      <c r="P9" s="126"/>
-      <c r="Q9" s="126"/>
-      <c r="R9" s="126"/>
-      <c r="S9" s="126"/>
-      <c r="T9" s="126"/>
-      <c r="U9" s="126"/>
-      <c r="V9" s="126"/>
-      <c r="W9" s="126"/>
-      <c r="X9" s="126"/>
-      <c r="Y9" s="126"/>
-      <c r="Z9" s="126"/>
-      <c r="AA9" s="126"/>
-      <c r="AB9" s="126"/>
-      <c r="AC9" s="126"/>
-      <c r="AD9" s="126"/>
-      <c r="AE9" s="126"/>
-      <c r="AF9" s="126"/>
-      <c r="AG9" s="126"/>
-      <c r="AH9" s="126"/>
-      <c r="AI9" s="126"/>
-      <c r="AJ9" s="126"/>
-      <c r="AK9" s="126"/>
-      <c r="AL9" s="126"/>
+      <c r="I9" s="128"/>
+      <c r="J9" s="128"/>
+      <c r="K9" s="128"/>
+      <c r="L9" s="128"/>
+      <c r="M9" s="128"/>
+      <c r="N9" s="128"/>
+      <c r="O9" s="128"/>
+      <c r="P9" s="128"/>
+      <c r="Q9" s="128"/>
+      <c r="R9" s="128"/>
+      <c r="S9" s="128"/>
+      <c r="T9" s="128"/>
+      <c r="U9" s="128"/>
+      <c r="V9" s="128"/>
+      <c r="W9" s="128"/>
+      <c r="X9" s="128"/>
+      <c r="Y9" s="128"/>
+      <c r="Z9" s="128"/>
+      <c r="AA9" s="128"/>
+      <c r="AB9" s="128"/>
+      <c r="AC9" s="128"/>
+      <c r="AD9" s="128"/>
+      <c r="AE9" s="128"/>
+      <c r="AF9" s="128"/>
+      <c r="AG9" s="128"/>
+      <c r="AH9" s="128"/>
+      <c r="AI9" s="128"/>
+      <c r="AJ9" s="128"/>
+      <c r="AK9" s="128"/>
+      <c r="AL9" s="128"/>
     </row>
     <row r="10" spans="8:38" ht="30" customHeight="1">
       <c r="H10" s="89" t="s">
@@ -5132,11 +5112,11 @@
       </c>
     </row>
     <row r="42" spans="8:38" ht="15.75">
-      <c r="H42" s="127" t="s">
+      <c r="H42" s="129" t="s">
         <v>19</v>
       </c>
-      <c r="I42" s="127"/>
-      <c r="J42" s="127"/>
+      <c r="I42" s="129"/>
+      <c r="J42" s="129"/>
       <c r="K42" s="89">
         <f>COUNTA(K11:K41)</f>
         <v>6</v>
@@ -5250,12 +5230,12 @@
     <mergeCell ref="H42:J42"/>
   </mergeCells>
   <conditionalFormatting sqref="AL42">
-    <cfRule type="expression" dxfId="17" priority="10">
+    <cfRule type="expression" dxfId="14" priority="10">
       <formula>AU42="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11:AK41">
-    <cfRule type="expression" dxfId="16" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>K11&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5266,7 +5246,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AK45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -5301,66 +5281,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="146"/>
-      <c r="B1" s="147"/>
-      <c r="C1" s="148"/>
+      <c r="A1" s="133"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="135"/>
       <c r="D1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="128" t="s">
+      <c r="E1" s="147" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="128"/>
-      <c r="G1" s="128"/>
-      <c r="H1" s="128"/>
-      <c r="I1" s="128"/>
-      <c r="J1" s="128"/>
-      <c r="K1" s="128"/>
-      <c r="L1" s="129" t="s">
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="148" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="129"/>
-      <c r="N1" s="129"/>
-      <c r="O1" s="129"/>
-      <c r="P1" s="129"/>
-      <c r="Q1" s="129"/>
-      <c r="R1" s="129"/>
-      <c r="S1" s="130" t="s">
+      <c r="M1" s="148"/>
+      <c r="N1" s="148"/>
+      <c r="O1" s="148"/>
+      <c r="P1" s="148"/>
+      <c r="Q1" s="148"/>
+      <c r="R1" s="148"/>
+      <c r="S1" s="149" t="s">
         <v>39</v>
       </c>
-      <c r="T1" s="130"/>
-      <c r="U1" s="131" t="s">
+      <c r="T1" s="149"/>
+      <c r="U1" s="150" t="s">
         <v>40</v>
       </c>
-      <c r="V1" s="132"/>
-      <c r="W1" s="132"/>
-      <c r="X1" s="132"/>
-      <c r="Y1" s="133"/>
-      <c r="Z1" s="134" t="s">
+      <c r="V1" s="151"/>
+      <c r="W1" s="151"/>
+      <c r="X1" s="151"/>
+      <c r="Y1" s="152"/>
+      <c r="Z1" s="153" t="s">
         <v>41</v>
       </c>
-      <c r="AA1" s="134"/>
-      <c r="AB1" s="134"/>
-      <c r="AC1" s="134"/>
-      <c r="AD1" s="134"/>
-      <c r="AE1" s="135" t="s">
+      <c r="AA1" s="153"/>
+      <c r="AB1" s="153"/>
+      <c r="AC1" s="153"/>
+      <c r="AD1" s="153"/>
+      <c r="AE1" s="142" t="s">
         <v>42</v>
       </c>
-      <c r="AF1" s="135"/>
-      <c r="AG1" s="135"/>
-      <c r="AH1" s="136" t="s">
+      <c r="AF1" s="142"/>
+      <c r="AG1" s="142"/>
+      <c r="AH1" s="143" t="s">
         <v>43</v>
       </c>
-      <c r="AI1" s="136"/>
-      <c r="AJ1" s="136"/>
-      <c r="AK1" s="143" t="s">
+      <c r="AI1" s="143"/>
+      <c r="AJ1" s="143"/>
+      <c r="AK1" s="130" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:37" s="2" customFormat="1" ht="30" customHeight="1">
-      <c r="A2" s="149"/>
-      <c r="B2" s="150"/>
-      <c r="C2" s="151"/>
+      <c r="A2" s="136"/>
+      <c r="B2" s="137"/>
+      <c r="C2" s="138"/>
       <c r="D2" s="5" t="s">
         <v>44</v>
       </c>
@@ -5454,7 +5434,7 @@
       <c r="AH2" s="55"/>
       <c r="AI2" s="55"/>
       <c r="AJ2" s="55"/>
-      <c r="AK2" s="144"/>
+      <c r="AK2" s="131"/>
     </row>
     <row r="3" spans="1:37">
       <c r="A3" s="13" t="s">
@@ -5565,7 +5545,7 @@
       <c r="AJ3" s="56">
         <v>2</v>
       </c>
-      <c r="AK3" s="145"/>
+      <c r="AK3" s="132"/>
     </row>
     <row r="4" spans="1:37">
       <c r="A4" s="20">
@@ -7616,12 +7596,12 @@
       </c>
     </row>
     <row r="35" spans="1:37" ht="30" customHeight="1">
-      <c r="A35" s="137" t="s">
+      <c r="A35" s="144" t="s">
         <v>77</v>
       </c>
-      <c r="B35" s="138"/>
-      <c r="C35" s="138"/>
-      <c r="D35" s="139"/>
+      <c r="B35" s="145"/>
+      <c r="C35" s="145"/>
+      <c r="D35" s="146"/>
       <c r="E35" s="52">
         <f>COUNTA(E4:E34)</f>
         <v>14</v>
@@ -7753,84 +7733,84 @@
       <c r="AK35" s="29"/>
     </row>
     <row r="36" spans="1:37" ht="30" customHeight="1">
-      <c r="AG36" s="140" t="s">
+      <c r="AG36" s="139" t="s">
         <v>78</v>
       </c>
-      <c r="AH36" s="141"/>
-      <c r="AI36" s="141"/>
-      <c r="AJ36" s="142"/>
+      <c r="AH36" s="140"/>
+      <c r="AI36" s="140"/>
+      <c r="AJ36" s="141"/>
       <c r="AK36" s="53">
         <f>ROUND(AVERAGE(AK4:AK34),0)</f>
         <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:37" ht="30" customHeight="1">
-      <c r="AG37" s="140" t="s">
+      <c r="AG37" s="139" t="s">
         <v>79</v>
       </c>
-      <c r="AH37" s="141"/>
-      <c r="AI37" s="141"/>
-      <c r="AJ37" s="142"/>
+      <c r="AH37" s="140"/>
+      <c r="AI37" s="140"/>
+      <c r="AJ37" s="141"/>
       <c r="AK37" s="53">
         <f>MAX(AK4:AK34)</f>
         <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:37" ht="30" customHeight="1">
-      <c r="AG38" s="140" t="s">
+      <c r="AG38" s="139" t="s">
         <v>80</v>
       </c>
-      <c r="AH38" s="141"/>
-      <c r="AI38" s="141"/>
-      <c r="AJ38" s="142"/>
+      <c r="AH38" s="140"/>
+      <c r="AI38" s="140"/>
+      <c r="AJ38" s="141"/>
       <c r="AK38" s="53">
         <f>MIN(AK4:AK34)</f>
         <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:37" ht="30" customHeight="1">
-      <c r="AG39" s="140" t="s">
+      <c r="AG39" s="139" t="s">
         <v>81</v>
       </c>
-      <c r="AH39" s="141"/>
-      <c r="AI39" s="141"/>
-      <c r="AJ39" s="142"/>
+      <c r="AH39" s="140"/>
+      <c r="AI39" s="140"/>
+      <c r="AJ39" s="141"/>
       <c r="AK39" s="53">
         <f>COUNTIF(AK4:AK34,"&gt;"&amp;AK36)</f>
         <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:37" ht="30" customHeight="1">
-      <c r="AG40" s="140" t="s">
+      <c r="AG40" s="139" t="s">
         <v>82</v>
       </c>
-      <c r="AH40" s="141"/>
-      <c r="AI40" s="141"/>
-      <c r="AJ40" s="142"/>
+      <c r="AH40" s="140"/>
+      <c r="AI40" s="140"/>
+      <c r="AJ40" s="141"/>
       <c r="AK40" s="53">
         <f>COUNTIF(AK4:AK34,"&lt;"&amp;AK36)</f>
         <v>18</v>
       </c>
     </row>
     <row r="41" spans="1:37" ht="30" customHeight="1">
-      <c r="AG41" s="140" t="s">
+      <c r="AG41" s="139" t="s">
         <v>83</v>
       </c>
-      <c r="AH41" s="141"/>
-      <c r="AI41" s="141"/>
-      <c r="AJ41" s="142"/>
+      <c r="AH41" s="140"/>
+      <c r="AI41" s="140"/>
+      <c r="AJ41" s="141"/>
       <c r="AK41" s="53">
         <f>COUNTIF(AK4:AK34,"&gt;"&amp;20)</f>
         <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:37" ht="30" customHeight="1">
-      <c r="AG42" s="140" t="s">
+      <c r="AG42" s="139" t="s">
         <v>84</v>
       </c>
-      <c r="AH42" s="141"/>
-      <c r="AI42" s="141"/>
-      <c r="AJ42" s="142"/>
+      <c r="AH42" s="140"/>
+      <c r="AI42" s="140"/>
+      <c r="AJ42" s="141"/>
       <c r="AK42" s="53">
         <f>COUNTIF(AK4:AK34,"&lt;"&amp;20)</f>
         <v>21</v>
@@ -7841,11 +7821,6 @@
     <row r="45" spans="1:37" ht="30" customHeight="1"/>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="AK1:AK3"/>
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="AG38:AJ38"/>
-    <mergeCell ref="AG39:AJ39"/>
-    <mergeCell ref="AG40:AJ40"/>
     <mergeCell ref="AG41:AJ41"/>
     <mergeCell ref="AG42:AJ42"/>
     <mergeCell ref="AE1:AG1"/>
@@ -7858,39 +7833,44 @@
     <mergeCell ref="S1:T1"/>
     <mergeCell ref="U1:Y1"/>
     <mergeCell ref="Z1:AD1"/>
+    <mergeCell ref="AK1:AK3"/>
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="AG38:AJ38"/>
+    <mergeCell ref="AG39:AJ39"/>
+    <mergeCell ref="AG40:AJ40"/>
   </mergeCells>
   <conditionalFormatting sqref="L35:R35">
-    <cfRule type="expression" dxfId="15" priority="6">
+    <cfRule type="expression" dxfId="12" priority="6">
       <formula>L35="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S35:T35">
-    <cfRule type="expression" dxfId="14" priority="5">
+    <cfRule type="expression" dxfId="11" priority="5">
       <formula>S35="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U35:Y35">
-    <cfRule type="expression" dxfId="13" priority="4">
+    <cfRule type="expression" dxfId="10" priority="4">
       <formula>U35="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z35:AD35">
-    <cfRule type="expression" dxfId="12" priority="3">
+    <cfRule type="expression" dxfId="9" priority="3">
       <formula>Z35="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE35:AG35">
-    <cfRule type="expression" dxfId="11" priority="2">
+    <cfRule type="expression" dxfId="8" priority="2">
       <formula>AE35="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH35:AJ35">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>AH35="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:AJ34">
-    <cfRule type="expression" dxfId="9" priority="7">
+    <cfRule type="expression" dxfId="6" priority="7">
       <formula>E4="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7901,7 +7881,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AK44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -7935,66 +7915,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="146"/>
-      <c r="B1" s="147"/>
-      <c r="C1" s="148"/>
+      <c r="A1" s="133"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="135"/>
       <c r="D1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="128" t="s">
+      <c r="E1" s="147" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="128"/>
-      <c r="G1" s="128"/>
-      <c r="H1" s="128"/>
-      <c r="I1" s="128"/>
-      <c r="J1" s="128"/>
-      <c r="K1" s="128"/>
-      <c r="L1" s="129" t="s">
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="148" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="129"/>
-      <c r="N1" s="129"/>
-      <c r="O1" s="129"/>
-      <c r="P1" s="129"/>
-      <c r="Q1" s="129"/>
-      <c r="R1" s="152" t="s">
+      <c r="M1" s="148"/>
+      <c r="N1" s="148"/>
+      <c r="O1" s="148"/>
+      <c r="P1" s="148"/>
+      <c r="Q1" s="148"/>
+      <c r="R1" s="154" t="s">
         <v>39</v>
       </c>
-      <c r="S1" s="153"/>
-      <c r="T1" s="154"/>
-      <c r="U1" s="131" t="s">
+      <c r="S1" s="155"/>
+      <c r="T1" s="156"/>
+      <c r="U1" s="150" t="s">
         <v>40</v>
       </c>
-      <c r="V1" s="132"/>
-      <c r="W1" s="132"/>
-      <c r="X1" s="132"/>
-      <c r="Y1" s="133"/>
-      <c r="Z1" s="134" t="s">
+      <c r="V1" s="151"/>
+      <c r="W1" s="151"/>
+      <c r="X1" s="151"/>
+      <c r="Y1" s="152"/>
+      <c r="Z1" s="153" t="s">
         <v>41</v>
       </c>
-      <c r="AA1" s="134"/>
-      <c r="AB1" s="134"/>
-      <c r="AC1" s="134"/>
-      <c r="AD1" s="134"/>
-      <c r="AE1" s="135" t="s">
+      <c r="AA1" s="153"/>
+      <c r="AB1" s="153"/>
+      <c r="AC1" s="153"/>
+      <c r="AD1" s="153"/>
+      <c r="AE1" s="142" t="s">
         <v>42</v>
       </c>
-      <c r="AF1" s="135"/>
-      <c r="AG1" s="135"/>
-      <c r="AH1" s="136" t="s">
+      <c r="AF1" s="142"/>
+      <c r="AG1" s="142"/>
+      <c r="AH1" s="143" t="s">
         <v>43</v>
       </c>
-      <c r="AI1" s="136"/>
-      <c r="AJ1" s="136"/>
-      <c r="AK1" s="143" t="s">
+      <c r="AI1" s="143"/>
+      <c r="AJ1" s="143"/>
+      <c r="AK1" s="130" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:37" s="2" customFormat="1" ht="45" customHeight="1">
-      <c r="A2" s="149"/>
-      <c r="B2" s="150"/>
-      <c r="C2" s="151"/>
+      <c r="A2" s="136"/>
+      <c r="B2" s="137"/>
+      <c r="C2" s="138"/>
       <c r="D2" s="5" t="s">
         <v>44</v>
       </c>
@@ -8090,7 +8070,7 @@
       </c>
       <c r="AI2" s="55"/>
       <c r="AJ2" s="55"/>
-      <c r="AK2" s="144"/>
+      <c r="AK2" s="131"/>
     </row>
     <row r="3" spans="1:37">
       <c r="A3" s="13" t="s">
@@ -8201,7 +8181,7 @@
       <c r="AJ3" s="56">
         <v>1</v>
       </c>
-      <c r="AK3" s="145"/>
+      <c r="AK3" s="132"/>
     </row>
     <row r="4" spans="1:37">
       <c r="A4" s="20">
@@ -9958,12 +9938,12 @@
       </c>
     </row>
     <row r="34" spans="1:37" ht="30" customHeight="1">
-      <c r="A34" s="137" t="s">
+      <c r="A34" s="144" t="s">
         <v>77</v>
       </c>
-      <c r="B34" s="138"/>
-      <c r="C34" s="138"/>
-      <c r="D34" s="139"/>
+      <c r="B34" s="145"/>
+      <c r="C34" s="145"/>
+      <c r="D34" s="146"/>
       <c r="E34" s="52">
         <f t="shared" ref="E34:AJ34" si="1">COUNTA(E4:E33)</f>
         <v>2</v>
@@ -10095,84 +10075,84 @@
       <c r="AK34" s="29"/>
     </row>
     <row r="35" spans="1:37" ht="30" customHeight="1">
-      <c r="AG35" s="140" t="s">
+      <c r="AG35" s="139" t="s">
         <v>78</v>
       </c>
-      <c r="AH35" s="141"/>
-      <c r="AI35" s="141"/>
-      <c r="AJ35" s="142"/>
+      <c r="AH35" s="140"/>
+      <c r="AI35" s="140"/>
+      <c r="AJ35" s="141"/>
       <c r="AK35" s="53">
         <f>ROUND(AVERAGE(AK4:AK33),0)</f>
         <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:37" ht="30" customHeight="1">
-      <c r="AG36" s="140" t="s">
+      <c r="AG36" s="139" t="s">
         <v>79</v>
       </c>
-      <c r="AH36" s="141"/>
-      <c r="AI36" s="141"/>
-      <c r="AJ36" s="142"/>
+      <c r="AH36" s="140"/>
+      <c r="AI36" s="140"/>
+      <c r="AJ36" s="141"/>
       <c r="AK36" s="53">
         <f>MAX(AK4:AK33)</f>
         <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:37" ht="30" customHeight="1">
-      <c r="AG37" s="140" t="s">
+      <c r="AG37" s="139" t="s">
         <v>80</v>
       </c>
-      <c r="AH37" s="141"/>
-      <c r="AI37" s="141"/>
-      <c r="AJ37" s="142"/>
+      <c r="AH37" s="140"/>
+      <c r="AI37" s="140"/>
+      <c r="AJ37" s="141"/>
       <c r="AK37" s="53">
         <f>MIN(AK4:AK33)</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:37" ht="30" customHeight="1">
-      <c r="AG38" s="140" t="s">
+      <c r="AG38" s="139" t="s">
         <v>81</v>
       </c>
-      <c r="AH38" s="141"/>
-      <c r="AI38" s="141"/>
-      <c r="AJ38" s="142"/>
+      <c r="AH38" s="140"/>
+      <c r="AI38" s="140"/>
+      <c r="AJ38" s="141"/>
       <c r="AK38" s="53">
         <f>COUNTIF(AK4:AK33,"&gt;"&amp;AK35)</f>
         <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:37" ht="30" customHeight="1">
-      <c r="AG39" s="140" t="s">
+      <c r="AG39" s="139" t="s">
         <v>82</v>
       </c>
-      <c r="AH39" s="141"/>
-      <c r="AI39" s="141"/>
-      <c r="AJ39" s="142"/>
+      <c r="AH39" s="140"/>
+      <c r="AI39" s="140"/>
+      <c r="AJ39" s="141"/>
       <c r="AK39" s="53">
         <f>COUNTIF(AK4:AK33,"&lt;"&amp;AK35)</f>
         <v>14</v>
       </c>
     </row>
     <row r="40" spans="1:37" ht="30" customHeight="1">
-      <c r="AG40" s="140" t="s">
+      <c r="AG40" s="139" t="s">
         <v>83</v>
       </c>
-      <c r="AH40" s="141"/>
-      <c r="AI40" s="141"/>
-      <c r="AJ40" s="142"/>
+      <c r="AH40" s="140"/>
+      <c r="AI40" s="140"/>
+      <c r="AJ40" s="141"/>
       <c r="AK40" s="53">
         <f>COUNTIF(AK4:AK33,"&gt;"&amp;20)</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:37" ht="30" customHeight="1">
-      <c r="AG41" s="140" t="s">
+      <c r="AG41" s="139" t="s">
         <v>84</v>
       </c>
-      <c r="AH41" s="141"/>
-      <c r="AI41" s="141"/>
-      <c r="AJ41" s="142"/>
+      <c r="AH41" s="140"/>
+      <c r="AI41" s="140"/>
+      <c r="AJ41" s="141"/>
       <c r="AK41" s="53">
         <f>COUNTIF(AK4:AK33,"&lt;"&amp;20)</f>
         <v>30</v>
@@ -10183,11 +10163,6 @@
     <row r="44" spans="1:37" ht="30" customHeight="1"/>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="AK1:AK3"/>
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="AG37:AJ37"/>
-    <mergeCell ref="AG38:AJ38"/>
-    <mergeCell ref="AG39:AJ39"/>
     <mergeCell ref="AG40:AJ40"/>
     <mergeCell ref="AG41:AJ41"/>
     <mergeCell ref="AE1:AG1"/>
@@ -10200,29 +10175,34 @@
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:Y1"/>
     <mergeCell ref="Z1:AD1"/>
+    <mergeCell ref="AK1:AK3"/>
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="AG37:AJ37"/>
+    <mergeCell ref="AG38:AJ38"/>
+    <mergeCell ref="AG39:AJ39"/>
   </mergeCells>
   <conditionalFormatting sqref="R34:T34">
-    <cfRule type="expression" dxfId="8" priority="5">
+    <cfRule type="expression" dxfId="5" priority="5">
       <formula>R34="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U34:Y34">
-    <cfRule type="expression" dxfId="7" priority="4">
+    <cfRule type="expression" dxfId="4" priority="4">
       <formula>U34="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z34:AD34">
-    <cfRule type="expression" dxfId="6" priority="3">
+    <cfRule type="expression" dxfId="3" priority="3">
       <formula>Z34="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE34:AG34">
-    <cfRule type="expression" dxfId="5" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>AE34="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH34:AJ34">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>AH34="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10233,7 +10213,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AK27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -10267,64 +10247,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="146"/>
-      <c r="B1" s="147"/>
-      <c r="C1" s="148"/>
+      <c r="A1" s="133"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="135"/>
       <c r="D1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="128" t="s">
+      <c r="E1" s="147" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="128"/>
-      <c r="G1" s="128"/>
-      <c r="H1" s="128"/>
-      <c r="I1" s="128"/>
-      <c r="J1" s="128"/>
-      <c r="K1" s="128"/>
-      <c r="L1" s="129" t="s">
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="148" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="129"/>
-      <c r="N1" s="129"/>
-      <c r="O1" s="129"/>
-      <c r="P1" s="129"/>
-      <c r="Q1" s="129"/>
-      <c r="R1" s="155" t="s">
+      <c r="M1" s="148"/>
+      <c r="N1" s="148"/>
+      <c r="O1" s="148"/>
+      <c r="P1" s="148"/>
+      <c r="Q1" s="148"/>
+      <c r="R1" s="160" t="s">
         <v>39</v>
       </c>
-      <c r="S1" s="156"/>
-      <c r="T1" s="157"/>
-      <c r="U1" s="131" t="s">
+      <c r="S1" s="161"/>
+      <c r="T1" s="162"/>
+      <c r="U1" s="150" t="s">
         <v>40</v>
       </c>
-      <c r="V1" s="132"/>
-      <c r="W1" s="132"/>
-      <c r="X1" s="132"/>
-      <c r="Y1" s="133"/>
-      <c r="Z1" s="134" t="s">
+      <c r="V1" s="151"/>
+      <c r="W1" s="151"/>
+      <c r="X1" s="151"/>
+      <c r="Y1" s="152"/>
+      <c r="Z1" s="153" t="s">
         <v>41</v>
       </c>
-      <c r="AA1" s="134"/>
-      <c r="AB1" s="134"/>
-      <c r="AC1" s="134"/>
-      <c r="AD1" s="158" t="s">
+      <c r="AA1" s="153"/>
+      <c r="AB1" s="153"/>
+      <c r="AC1" s="153"/>
+      <c r="AD1" s="157" t="s">
         <v>92</v>
       </c>
-      <c r="AE1" s="159"/>
-      <c r="AF1" s="159"/>
-      <c r="AG1" s="159"/>
-      <c r="AH1" s="159"/>
-      <c r="AI1" s="159"/>
-      <c r="AJ1" s="160"/>
-      <c r="AK1" s="143" t="s">
+      <c r="AE1" s="158"/>
+      <c r="AF1" s="158"/>
+      <c r="AG1" s="158"/>
+      <c r="AH1" s="158"/>
+      <c r="AI1" s="158"/>
+      <c r="AJ1" s="159"/>
+      <c r="AK1" s="130" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:37" s="2" customFormat="1" ht="70.5" customHeight="1">
-      <c r="A2" s="149"/>
-      <c r="B2" s="150"/>
-      <c r="C2" s="151"/>
+      <c r="A2" s="136"/>
+      <c r="B2" s="137"/>
+      <c r="C2" s="138"/>
       <c r="D2" s="5" t="s">
         <v>44</v>
       </c>
@@ -10424,7 +10404,7 @@
       <c r="AJ2" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="AK2" s="144"/>
+      <c r="AK2" s="131"/>
     </row>
     <row r="3" spans="1:37">
       <c r="A3" s="13" t="s">
@@ -10535,7 +10515,7 @@
       <c r="AJ3" s="19">
         <v>1</v>
       </c>
-      <c r="AK3" s="145"/>
+      <c r="AK3" s="132"/>
     </row>
     <row r="4" spans="1:37">
       <c r="A4" s="20">
@@ -10962,10 +10942,10 @@
       <c r="F10" s="23"/>
       <c r="G10" s="23"/>
       <c r="H10" s="23"/>
-      <c r="I10" s="161" t="s">
-        <v>12</v>
-      </c>
-      <c r="J10" s="161" t="s">
+      <c r="I10" s="119" t="s">
+        <v>12</v>
+      </c>
+      <c r="J10" s="119" t="s">
         <v>12</v>
       </c>
       <c r="K10" s="23"/>
@@ -10985,12 +10965,16 @@
       <c r="Y10" s="26"/>
       <c r="Z10" s="27"/>
       <c r="AA10" s="27"/>
-      <c r="AB10" s="27"/>
-      <c r="AC10" s="27"/>
-      <c r="AD10" s="162" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE10" s="162" t="s">
+      <c r="AB10" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC10" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD10" s="120" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE10" s="120" t="s">
         <v>12</v>
       </c>
       <c r="AF10" s="28"/>
@@ -11000,7 +10984,7 @@
       <c r="AJ10" s="28"/>
       <c r="AK10" s="29">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -11018,7 +11002,9 @@
       </c>
       <c r="E11" s="43"/>
       <c r="F11" s="43"/>
-      <c r="G11" s="43"/>
+      <c r="G11" s="43" t="s">
+        <v>12</v>
+      </c>
       <c r="H11" s="43"/>
       <c r="I11" s="43"/>
       <c r="J11" s="43"/>
@@ -11040,7 +11026,9 @@
       <c r="Z11" s="47"/>
       <c r="AA11" s="47"/>
       <c r="AB11" s="47"/>
-      <c r="AC11" s="47"/>
+      <c r="AC11" s="47" t="s">
+        <v>12</v>
+      </c>
       <c r="AD11" s="48"/>
       <c r="AE11" s="48"/>
       <c r="AF11" s="48"/>
@@ -11050,7 +11038,7 @@
       <c r="AJ11" s="48"/>
       <c r="AK11" s="49">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -11068,13 +11056,19 @@
       </c>
       <c r="E12" s="23"/>
       <c r="F12" s="23"/>
-      <c r="G12" s="23"/>
+      <c r="G12" s="23" t="s">
+        <v>12</v>
+      </c>
       <c r="H12" s="23"/>
       <c r="I12" s="23"/>
       <c r="J12" s="23"/>
       <c r="K12" s="23"/>
-      <c r="L12" s="24"/>
-      <c r="M12" s="24"/>
+      <c r="L12" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="M12" s="24" t="s">
+        <v>12</v>
+      </c>
       <c r="N12" s="24"/>
       <c r="O12" s="24"/>
       <c r="P12" s="24"/>
@@ -11082,7 +11076,9 @@
       <c r="R12" s="40"/>
       <c r="S12" s="40"/>
       <c r="T12" s="40"/>
-      <c r="U12" s="26"/>
+      <c r="U12" s="26" t="s">
+        <v>12</v>
+      </c>
       <c r="V12" s="26"/>
       <c r="W12" s="26"/>
       <c r="X12" s="26"/>
@@ -11090,17 +11086,23 @@
       <c r="Z12" s="27"/>
       <c r="AA12" s="27"/>
       <c r="AB12" s="27"/>
-      <c r="AC12" s="27"/>
+      <c r="AC12" s="27" t="s">
+        <v>12</v>
+      </c>
       <c r="AD12" s="28"/>
-      <c r="AE12" s="28"/>
+      <c r="AE12" s="28" t="s">
+        <v>12</v>
+      </c>
       <c r="AF12" s="28"/>
       <c r="AG12" s="28"/>
-      <c r="AH12" s="28"/>
+      <c r="AH12" s="28" t="s">
+        <v>12</v>
+      </c>
       <c r="AI12" s="28"/>
       <c r="AJ12" s="28"/>
       <c r="AK12" s="29">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -11116,15 +11118,25 @@
       <c r="D13" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
+      <c r="E13" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="23" t="s">
+        <v>12</v>
+      </c>
       <c r="H13" s="23"/>
       <c r="I13" s="23"/>
       <c r="J13" s="23"/>
       <c r="K13" s="23"/>
-      <c r="L13" s="24"/>
-      <c r="M13" s="24"/>
+      <c r="L13" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="M13" s="24" t="s">
+        <v>12</v>
+      </c>
       <c r="N13" s="24"/>
       <c r="O13" s="24"/>
       <c r="P13" s="24"/>
@@ -11142,15 +11154,21 @@
       <c r="AB13" s="27"/>
       <c r="AC13" s="27"/>
       <c r="AD13" s="28"/>
-      <c r="AE13" s="28"/>
+      <c r="AE13" s="28" t="s">
+        <v>12</v>
+      </c>
       <c r="AF13" s="28"/>
       <c r="AG13" s="28"/>
-      <c r="AH13" s="28"/>
+      <c r="AH13" s="28" t="s">
+        <v>12</v>
+      </c>
       <c r="AI13" s="28"/>
-      <c r="AJ13" s="28"/>
+      <c r="AJ13" s="28" t="s">
+        <v>12</v>
+      </c>
       <c r="AK13" s="29">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -11168,16 +11186,30 @@
       </c>
       <c r="E14" s="23"/>
       <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="23"/>
-      <c r="J14" s="23"/>
-      <c r="K14" s="23"/>
+      <c r="G14" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="I14" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="J14" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="K14" s="23" t="s">
+        <v>12</v>
+      </c>
       <c r="L14" s="24"/>
-      <c r="M14" s="24"/>
+      <c r="M14" s="24" t="s">
+        <v>12</v>
+      </c>
       <c r="N14" s="24"/>
       <c r="O14" s="24"/>
-      <c r="P14" s="24"/>
+      <c r="P14" s="24" t="s">
+        <v>12</v>
+      </c>
       <c r="Q14" s="24"/>
       <c r="R14" s="40"/>
       <c r="S14" s="40"/>
@@ -11191,16 +11223,24 @@
       <c r="AA14" s="27"/>
       <c r="AB14" s="27"/>
       <c r="AC14" s="27"/>
-      <c r="AD14" s="28"/>
-      <c r="AE14" s="28"/>
+      <c r="AD14" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE14" s="28" t="s">
+        <v>12</v>
+      </c>
       <c r="AF14" s="28"/>
       <c r="AG14" s="28"/>
-      <c r="AH14" s="28"/>
+      <c r="AH14" s="28" t="s">
+        <v>12</v>
+      </c>
       <c r="AI14" s="28"/>
-      <c r="AJ14" s="28"/>
+      <c r="AJ14" s="28" t="s">
+        <v>12</v>
+      </c>
       <c r="AK14" s="29">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -11304,47 +11344,47 @@
       </c>
     </row>
     <row r="17" spans="1:37" ht="30" customHeight="1">
-      <c r="A17" s="137" t="s">
+      <c r="A17" s="144" t="s">
         <v>77</v>
       </c>
-      <c r="B17" s="138"/>
-      <c r="C17" s="138"/>
-      <c r="D17" s="139"/>
+      <c r="B17" s="145"/>
+      <c r="C17" s="145"/>
+      <c r="D17" s="146"/>
       <c r="E17" s="52">
         <f t="shared" ref="E17:AJ17" si="1">COUNTA(E4:E16)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" s="52">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G17" s="52">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H17" s="52">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" s="52">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J17" s="52">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K17" s="52">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="24">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M17" s="24">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N17" s="24">
         <f t="shared" si="1"/>
@@ -11356,7 +11396,7 @@
       </c>
       <c r="P17" s="24">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="24">
         <f t="shared" si="1"/>
@@ -11376,7 +11416,7 @@
       </c>
       <c r="U17" s="26">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="26">
         <f t="shared" si="1"/>
@@ -11404,19 +11444,19 @@
       </c>
       <c r="AB17" s="27">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC17" s="27">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AD17" s="28">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE17" s="28">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AF17" s="28">
         <f t="shared" si="1"/>
@@ -11428,7 +11468,7 @@
       </c>
       <c r="AH17" s="28">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AI17" s="28">
         <f t="shared" si="1"/>
@@ -11436,92 +11476,92 @@
       </c>
       <c r="AJ17" s="28">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK17" s="29"/>
     </row>
     <row r="18" spans="1:37" ht="30" customHeight="1">
-      <c r="AG18" s="140" t="s">
+      <c r="AG18" s="139" t="s">
         <v>78</v>
       </c>
-      <c r="AH18" s="141"/>
-      <c r="AI18" s="141"/>
-      <c r="AJ18" s="142"/>
+      <c r="AH18" s="140"/>
+      <c r="AI18" s="140"/>
+      <c r="AJ18" s="141"/>
       <c r="AK18" s="53">
         <f>ROUND(AVERAGE(AK4:AK16),0)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:37" ht="30" customHeight="1">
-      <c r="AG19" s="140" t="s">
+      <c r="AG19" s="139" t="s">
         <v>79</v>
       </c>
-      <c r="AH19" s="141"/>
-      <c r="AI19" s="141"/>
-      <c r="AJ19" s="142"/>
+      <c r="AH19" s="140"/>
+      <c r="AI19" s="140"/>
+      <c r="AJ19" s="141"/>
       <c r="AK19" s="53">
         <f>MAX(AK4:AK16)</f>
         <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:37" ht="30" customHeight="1">
-      <c r="AG20" s="140" t="s">
+      <c r="AG20" s="139" t="s">
         <v>80</v>
       </c>
-      <c r="AH20" s="141"/>
-      <c r="AI20" s="141"/>
-      <c r="AJ20" s="142"/>
+      <c r="AH20" s="140"/>
+      <c r="AI20" s="140"/>
+      <c r="AJ20" s="141"/>
       <c r="AK20" s="53">
         <f>MIN(AK4:AK16)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:37" ht="30" customHeight="1">
-      <c r="AG21" s="140" t="s">
+      <c r="AG21" s="139" t="s">
         <v>81</v>
       </c>
-      <c r="AH21" s="141"/>
-      <c r="AI21" s="141"/>
-      <c r="AJ21" s="142"/>
+      <c r="AH21" s="140"/>
+      <c r="AI21" s="140"/>
+      <c r="AJ21" s="141"/>
       <c r="AK21" s="53">
         <f>COUNTIF(AK4:AK16,"&gt;"&amp;AK18)</f>
         <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:37" ht="30" customHeight="1">
-      <c r="AG22" s="140" t="s">
+      <c r="AG22" s="139" t="s">
         <v>82</v>
       </c>
-      <c r="AH22" s="141"/>
-      <c r="AI22" s="141"/>
-      <c r="AJ22" s="142"/>
+      <c r="AH22" s="140"/>
+      <c r="AI22" s="140"/>
+      <c r="AJ22" s="141"/>
       <c r="AK22" s="53">
         <f>COUNTIF(AK4:AK16,"&lt;"&amp;AK18)</f>
         <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:37" ht="30" customHeight="1">
-      <c r="AG23" s="140" t="s">
-        <v>83</v>
-      </c>
-      <c r="AH23" s="141"/>
-      <c r="AI23" s="141"/>
-      <c r="AJ23" s="142"/>
+      <c r="AG23" s="139" t="s">
+        <v>101</v>
+      </c>
+      <c r="AH23" s="140"/>
+      <c r="AI23" s="140"/>
+      <c r="AJ23" s="141"/>
       <c r="AK23" s="53">
-        <f>COUNTIF(AK4:AK16,"&gt;"&amp;20)</f>
-        <v>0</v>
+        <f>COUNTIF(AK4:AK16,"&gt;"&amp;10)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:37" ht="30" customHeight="1">
-      <c r="AG24" s="140" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH24" s="141"/>
-      <c r="AI24" s="141"/>
-      <c r="AJ24" s="142"/>
+      <c r="AG24" s="139" t="s">
+        <v>102</v>
+      </c>
+      <c r="AH24" s="140"/>
+      <c r="AI24" s="140"/>
+      <c r="AJ24" s="141"/>
       <c r="AK24" s="53">
-        <f>COUNTIF(AK4:AK16,"&lt;"&amp;20)</f>
-        <v>13</v>
+        <f>COUNTIF(AK4:AK16,"&lt;"&amp;10)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:37" ht="30" customHeight="1"/>
@@ -11529,12 +11569,6 @@
     <row r="27" spans="1:37" ht="30" customHeight="1"/>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="AG21:AJ21"/>
-    <mergeCell ref="AG22:AJ22"/>
-    <mergeCell ref="AG23:AJ23"/>
-    <mergeCell ref="AG24:AJ24"/>
-    <mergeCell ref="AK1:AK3"/>
-    <mergeCell ref="AD1:AJ1"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="AG18:AJ18"/>
     <mergeCell ref="AG19:AJ19"/>
@@ -11545,9 +11579,15 @@
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:Y1"/>
     <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="AG21:AJ21"/>
+    <mergeCell ref="AG22:AJ22"/>
+    <mergeCell ref="AG23:AJ23"/>
+    <mergeCell ref="AG24:AJ24"/>
+    <mergeCell ref="AK1:AK3"/>
+    <mergeCell ref="AD1:AJ1"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:AJ16">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>E4="+"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Другое/2026/study_chart.xlsx
+++ b/Другое/2026/study_chart.xlsx
@@ -881,7 +881,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1027" uniqueCount="103">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -1228,10 +1228,10 @@
     <t>Конспектирование прочитанных произведений</t>
   </si>
   <si>
-    <t>Количество дней больше 10</t>
+    <t>Количество дней меньше 10</t>
   </si>
   <si>
-    <t>Количество дней меньше 10</t>
+    <t>Количество дней больше либо равно 10</t>
   </si>
 </sst>
 </file>
@@ -11215,14 +11215,22 @@
       <c r="S14" s="40"/>
       <c r="T14" s="40"/>
       <c r="U14" s="26"/>
-      <c r="V14" s="26"/>
+      <c r="V14" s="26" t="s">
+        <v>12</v>
+      </c>
       <c r="W14" s="26"/>
-      <c r="X14" s="26"/>
+      <c r="X14" s="26" t="s">
+        <v>12</v>
+      </c>
       <c r="Y14" s="26"/>
       <c r="Z14" s="27"/>
       <c r="AA14" s="27"/>
-      <c r="AB14" s="27"/>
-      <c r="AC14" s="27"/>
+      <c r="AB14" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC14" s="27" t="s">
+        <v>12</v>
+      </c>
       <c r="AD14" s="28" t="s">
         <v>12</v>
       </c>
@@ -11240,7 +11248,7 @@
       </c>
       <c r="AK14" s="29">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -11258,20 +11266,32 @@
       </c>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="G15" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" s="23" t="s">
+        <v>12</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
-      <c r="L15" s="24"/>
-      <c r="M15" s="24"/>
+      <c r="L15" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="M15" s="24" t="s">
+        <v>12</v>
+      </c>
       <c r="N15" s="24"/>
-      <c r="O15" s="24"/>
+      <c r="O15" s="24" t="s">
+        <v>12</v>
+      </c>
       <c r="P15" s="24"/>
       <c r="Q15" s="24"/>
       <c r="R15" s="40"/>
       <c r="S15" s="40"/>
-      <c r="T15" s="40"/>
+      <c r="T15" s="40" t="s">
+        <v>12</v>
+      </c>
       <c r="U15" s="26"/>
       <c r="V15" s="26"/>
       <c r="W15" s="26"/>
@@ -11281,16 +11301,24 @@
       <c r="AA15" s="27"/>
       <c r="AB15" s="27"/>
       <c r="AC15" s="27"/>
-      <c r="AD15" s="28"/>
-      <c r="AE15" s="28"/>
-      <c r="AF15" s="28"/>
+      <c r="AD15" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE15" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF15" s="28" t="s">
+        <v>12</v>
+      </c>
       <c r="AG15" s="28"/>
-      <c r="AH15" s="28"/>
+      <c r="AH15" s="28" t="s">
+        <v>12</v>
+      </c>
       <c r="AI15" s="28"/>
       <c r="AJ15" s="28"/>
       <c r="AK15" s="29">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -11360,11 +11388,11 @@
       </c>
       <c r="G17" s="52">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H17" s="52">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" s="52">
         <f t="shared" si="1"/>
@@ -11380,11 +11408,11 @@
       </c>
       <c r="L17" s="24">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M17" s="24">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N17" s="24">
         <f t="shared" si="1"/>
@@ -11392,7 +11420,7 @@
       </c>
       <c r="O17" s="24">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P17" s="24">
         <f t="shared" si="1"/>
@@ -11412,7 +11440,7 @@
       </c>
       <c r="T17" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U17" s="26">
         <f t="shared" si="1"/>
@@ -11420,7 +11448,7 @@
       </c>
       <c r="V17" s="26">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W17" s="26">
         <f t="shared" si="1"/>
@@ -11428,7 +11456,7 @@
       </c>
       <c r="X17" s="26">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y17" s="26">
         <f t="shared" si="1"/>
@@ -11444,23 +11472,23 @@
       </c>
       <c r="AB17" s="27">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC17" s="27">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD17" s="28">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE17" s="28">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF17" s="28">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG17" s="28">
         <f t="shared" si="1"/>
@@ -11468,7 +11496,7 @@
       </c>
       <c r="AH17" s="28">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI17" s="28">
         <f t="shared" si="1"/>
@@ -11489,7 +11517,7 @@
       <c r="AJ18" s="141"/>
       <c r="AK18" s="53">
         <f>ROUND(AVERAGE(AK4:AK16),0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:37" ht="30" customHeight="1">
@@ -11501,7 +11529,7 @@
       <c r="AJ19" s="141"/>
       <c r="AK19" s="53">
         <f>MAX(AK4:AK16)</f>
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:37" ht="30" customHeight="1">
@@ -11542,26 +11570,26 @@
     </row>
     <row r="23" spans="1:37" ht="30" customHeight="1">
       <c r="AG23" s="139" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AH23" s="140"/>
       <c r="AI23" s="140"/>
       <c r="AJ23" s="141"/>
       <c r="AK23" s="53">
-        <f>COUNTIF(AK4:AK16,"&gt;"&amp;10)</f>
-        <v>3</v>
+        <f>COUNTIF(AK4:AK16,"&gt;="&amp;10)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:37" ht="30" customHeight="1">
       <c r="AG24" s="139" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AH24" s="140"/>
       <c r="AI24" s="140"/>
       <c r="AJ24" s="141"/>
       <c r="AK24" s="53">
         <f>COUNTIF(AK4:AK16,"&lt;"&amp;10)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:37" ht="30" customHeight="1"/>
